--- a/grupos/1BV - Estadisticos 20231.xlsx
+++ b/grupos/1BV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="170">
   <si>
     <t>Materia</t>
   </si>
@@ -59,9 +59,6 @@
     <t>Nombre</t>
   </si>
   <si>
-    <t>ALCANTARA GUZMAN ANGEL DAVID</t>
-  </si>
-  <si>
     <t>ALVAREZ BAEZ CLAUDIA RUBI</t>
   </si>
   <si>
@@ -251,9 +248,6 @@
     <t>ALVAREZ</t>
   </si>
   <si>
-    <t>ALCANTARA</t>
-  </si>
-  <si>
     <t>CASTRO</t>
   </si>
   <si>
@@ -353,9 +347,6 @@
     <t>BAEZ</t>
   </si>
   <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
     <t>BERMUDEZ</t>
   </si>
   <si>
@@ -429,9 +420,6 @@
   </si>
   <si>
     <t>CLAUDIA RUBI</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
   </si>
   <si>
     <t>YAMILETH</t>
@@ -901,7 +889,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -1045,10 +1033,10 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>6</v>
@@ -1060,10 +1048,10 @@
         <v>5</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -1108,10 +1096,10 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y4">
         <v>6</v>
@@ -1123,10 +1111,10 @@
         <v>5</v>
       </c>
       <c r="AB4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC4">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1137,22 +1125,22 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>-1</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -1200,22 +1188,22 @@
         <v>5</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z5">
         <v>-1</v>
       </c>
       <c r="AA5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1226,16 +1214,16 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>-1</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -1289,16 +1277,16 @@
         <v>5</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z6">
         <v>-1</v>
       </c>
       <c r="AA6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB6">
         <v>5</v>
@@ -1312,10 +1300,10 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1324,13 +1312,13 @@
         <v>-1</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G7">
         <v>5</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -1375,10 +1363,10 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>6</v>
@@ -1387,13 +1375,13 @@
         <v>-1</v>
       </c>
       <c r="AA7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB7">
         <v>5</v>
       </c>
       <c r="AC7">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1401,25 +1389,25 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8">
         <v>8</v>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E8">
         <v>-1</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1464,25 +1452,25 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>8</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z8">
         <v>-1</v>
       </c>
       <c r="AA8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB8">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AC8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1490,19 +1478,19 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9">
         <v>8</v>
       </c>
       <c r="D9">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E9">
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G9">
         <v>9</v>
@@ -1553,19 +1541,19 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>8</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z9">
         <v>-1</v>
       </c>
       <c r="AA9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB9">
         <v>9</v>
@@ -1579,22 +1567,22 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10">
         <v>-1</v>
       </c>
       <c r="F10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G10">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H10">
         <v>6</v>
@@ -1642,10 +1630,10 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y10">
         <v>5</v>
@@ -1654,10 +1642,10 @@
         <v>-1</v>
       </c>
       <c r="AA10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB10">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC10">
         <v>6</v>
@@ -1668,13 +1656,13 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E11">
         <v>-1</v>
@@ -1683,7 +1671,7 @@
         <v>5</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H11">
         <v>6</v>
@@ -1731,13 +1719,13 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z11">
         <v>-1</v>
@@ -1746,7 +1734,7 @@
         <v>5</v>
       </c>
       <c r="AB11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC11">
         <v>6</v>
@@ -1760,19 +1748,19 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E12">
         <v>-1</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H12">
         <v>6</v>
@@ -1823,19 +1811,19 @@
         <v>7</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z12">
         <v>-1</v>
       </c>
       <c r="AA12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC12">
         <v>6</v>
@@ -1849,7 +1837,7 @@
         <v>7</v>
       </c>
       <c r="C13">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D13">
         <v>6</v>
@@ -1858,7 +1846,7 @@
         <v>-1</v>
       </c>
       <c r="F13">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G13">
         <v>6</v>
@@ -1912,7 +1900,7 @@
         <v>7</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y13">
         <v>6</v>
@@ -1921,7 +1909,7 @@
         <v>-1</v>
       </c>
       <c r="AA13">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AB13">
         <v>6</v>
@@ -1935,10 +1923,10 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14">
         <v>6</v>
@@ -1947,10 +1935,10 @@
         <v>-1</v>
       </c>
       <c r="F14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H14">
         <v>6</v>
@@ -1998,10 +1986,10 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>6</v>
@@ -2010,10 +1998,10 @@
         <v>-1</v>
       </c>
       <c r="AA14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AB14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC14">
         <v>6</v>
@@ -2024,10 +2012,10 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D15">
         <v>6</v>
@@ -2036,10 +2024,10 @@
         <v>-1</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H15">
         <v>6</v>
@@ -2087,10 +2075,10 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>6</v>
@@ -2099,10 +2087,10 @@
         <v>-1</v>
       </c>
       <c r="AA15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AB15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC15">
         <v>6</v>
@@ -2113,25 +2101,25 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C16">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E16">
         <v>-1</v>
       </c>
       <c r="F16">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -2176,25 +2164,25 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z16">
         <v>-1</v>
       </c>
       <c r="AA16">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AB16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC16">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2202,25 +2190,25 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17">
         <v>-1</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -2265,25 +2253,25 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z17">
         <v>-1</v>
       </c>
       <c r="AA17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2291,22 +2279,22 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D18">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E18">
         <v>-1</v>
       </c>
       <c r="F18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H18">
         <v>6</v>
@@ -2354,22 +2342,22 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z18">
         <v>-1</v>
       </c>
       <c r="AA18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC18">
         <v>6</v>
@@ -2380,19 +2368,19 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C19">
         <v>6</v>
       </c>
       <c r="D19">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E19">
         <v>-1</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -2443,19 +2431,19 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>6</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z19">
         <v>-1</v>
       </c>
       <c r="AA19">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AB19">
         <v>5</v>
@@ -2472,7 +2460,7 @@
         <v>7</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D20">
         <v>6</v>
@@ -2481,13 +2469,13 @@
         <v>-1</v>
       </c>
       <c r="F20">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G20">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2535,7 +2523,7 @@
         <v>7</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2544,13 +2532,13 @@
         <v>-1</v>
       </c>
       <c r="AA20">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AB20">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC20">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2558,10 +2546,10 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C21">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D21">
         <v>6</v>
@@ -2570,10 +2558,10 @@
         <v>-1</v>
       </c>
       <c r="F21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G21">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H21">
         <v>5</v>
@@ -2621,10 +2609,10 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Y21">
         <v>6</v>
@@ -2633,10 +2621,10 @@
         <v>-1</v>
       </c>
       <c r="AA21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB21">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC21">
         <v>5</v>
@@ -2647,22 +2635,22 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E22">
         <v>-1</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G22">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H22">
         <v>5</v>
@@ -2710,22 +2698,22 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z22">
         <v>-1</v>
       </c>
       <c r="AA22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB22">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AC22">
         <v>5</v>
@@ -2736,13 +2724,13 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E23">
         <v>-1</v>
@@ -2751,7 +2739,7 @@
         <v>6</v>
       </c>
       <c r="G23">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H23">
         <v>5</v>
@@ -2799,13 +2787,13 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z23">
         <v>-1</v>
@@ -2814,7 +2802,7 @@
         <v>6</v>
       </c>
       <c r="AB23">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC23">
         <v>5</v>
@@ -2825,25 +2813,25 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E24">
         <v>-1</v>
       </c>
       <c r="F24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -2888,25 +2876,25 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z24">
         <v>-1</v>
       </c>
       <c r="AA24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC24">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2917,73 +2905,73 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25">
+        <v>6</v>
+      </c>
+      <c r="E25">
+        <v>-1</v>
+      </c>
+      <c r="F25">
+        <v>5</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+      <c r="H25">
+        <v>6</v>
+      </c>
+      <c r="I25">
+        <v>-1</v>
+      </c>
+      <c r="J25">
+        <v>-1</v>
+      </c>
+      <c r="K25">
+        <v>-1</v>
+      </c>
+      <c r="L25">
+        <v>-1</v>
+      </c>
+      <c r="M25">
+        <v>-1</v>
+      </c>
+      <c r="N25">
+        <v>-1</v>
+      </c>
+      <c r="O25">
+        <v>-1</v>
+      </c>
+      <c r="P25">
+        <v>-1</v>
+      </c>
+      <c r="Q25">
+        <v>-1</v>
+      </c>
+      <c r="R25">
+        <v>-1</v>
+      </c>
+      <c r="S25">
+        <v>-1</v>
+      </c>
+      <c r="T25">
+        <v>-1</v>
+      </c>
+      <c r="U25">
+        <v>-1</v>
+      </c>
+      <c r="V25">
+        <v>-1</v>
+      </c>
+      <c r="W25">
+        <v>6</v>
+      </c>
+      <c r="X25">
         <v>7</v>
       </c>
-      <c r="E25">
-        <v>-1</v>
-      </c>
-      <c r="F25">
-        <v>5</v>
-      </c>
-      <c r="G25">
-        <v>10</v>
-      </c>
-      <c r="H25">
-        <v>6</v>
-      </c>
-      <c r="I25">
-        <v>-1</v>
-      </c>
-      <c r="J25">
-        <v>-1</v>
-      </c>
-      <c r="K25">
-        <v>-1</v>
-      </c>
-      <c r="L25">
-        <v>-1</v>
-      </c>
-      <c r="M25">
-        <v>-1</v>
-      </c>
-      <c r="N25">
-        <v>-1</v>
-      </c>
-      <c r="O25">
-        <v>-1</v>
-      </c>
-      <c r="P25">
-        <v>-1</v>
-      </c>
-      <c r="Q25">
-        <v>-1</v>
-      </c>
-      <c r="R25">
-        <v>-1</v>
-      </c>
-      <c r="S25">
-        <v>-1</v>
-      </c>
-      <c r="T25">
-        <v>-1</v>
-      </c>
-      <c r="U25">
-        <v>-1</v>
-      </c>
-      <c r="V25">
-        <v>-1</v>
-      </c>
-      <c r="W25">
-        <v>6</v>
-      </c>
-      <c r="X25">
-        <v>6</v>
-      </c>
       <c r="Y25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z25">
         <v>-1</v>
@@ -2992,7 +2980,7 @@
         <v>5</v>
       </c>
       <c r="AB25">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC25">
         <v>6</v>
@@ -3003,19 +2991,19 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C26">
         <v>7</v>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E26">
         <v>-1</v>
       </c>
       <c r="F26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G26">
         <v>5</v>
@@ -3066,19 +3054,19 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>7</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z26">
         <v>-1</v>
       </c>
       <c r="AA26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB26">
         <v>5</v>
@@ -3095,16 +3083,16 @@
         <v>7</v>
       </c>
       <c r="C27">
+        <v>9</v>
+      </c>
+      <c r="D27">
+        <v>6</v>
+      </c>
+      <c r="E27">
+        <v>-1</v>
+      </c>
+      <c r="F27">
         <v>7</v>
-      </c>
-      <c r="D27">
-        <v>7</v>
-      </c>
-      <c r="E27">
-        <v>-1</v>
-      </c>
-      <c r="F27">
-        <v>6</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -3158,16 +3146,16 @@
         <v>7</v>
       </c>
       <c r="X27">
+        <v>9</v>
+      </c>
+      <c r="Y27">
+        <v>6</v>
+      </c>
+      <c r="Z27">
+        <v>-1</v>
+      </c>
+      <c r="AA27">
         <v>7</v>
-      </c>
-      <c r="Y27">
-        <v>7</v>
-      </c>
-      <c r="Z27">
-        <v>-1</v>
-      </c>
-      <c r="AA27">
-        <v>6</v>
       </c>
       <c r="AB27">
         <v>5</v>
@@ -3181,10 +3169,10 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C28">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D28">
         <v>6</v>
@@ -3193,7 +3181,7 @@
         <v>-1</v>
       </c>
       <c r="F28">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G28">
         <v>5</v>
@@ -3244,10 +3232,10 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X28">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Y28">
         <v>6</v>
@@ -3256,7 +3244,7 @@
         <v>-1</v>
       </c>
       <c r="AA28">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB28">
         <v>5</v>
@@ -3270,22 +3258,22 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C29">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E29">
         <v>-1</v>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H29">
         <v>6</v>
@@ -3333,22 +3321,22 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X29">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z29">
         <v>-1</v>
       </c>
       <c r="AA29">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC29">
         <v>6</v>
@@ -3359,25 +3347,25 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C30">
         <v>8</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E30">
         <v>-1</v>
       </c>
       <c r="F30">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I30">
         <v>-1</v>
@@ -3422,25 +3410,25 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X30">
         <v>8</v>
       </c>
       <c r="Y30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z30">
         <v>-1</v>
       </c>
       <c r="AA30">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC30">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3448,25 +3436,25 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E31">
         <v>-1</v>
       </c>
       <c r="F31">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -3511,25 +3499,25 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z31">
         <v>-1</v>
       </c>
       <c r="AA31">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC31">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3537,19 +3525,19 @@
         <v>41</v>
       </c>
       <c r="B32">
+        <v>9</v>
+      </c>
+      <c r="C32">
+        <v>10</v>
+      </c>
+      <c r="D32">
         <v>7</v>
       </c>
-      <c r="C32">
+      <c r="E32">
+        <v>-1</v>
+      </c>
+      <c r="F32">
         <v>9</v>
-      </c>
-      <c r="D32">
-        <v>5</v>
-      </c>
-      <c r="E32">
-        <v>-1</v>
-      </c>
-      <c r="F32">
-        <v>8</v>
       </c>
       <c r="G32">
         <v>10</v>
@@ -3600,19 +3588,19 @@
         <v>-1</v>
       </c>
       <c r="W32">
+        <v>9</v>
+      </c>
+      <c r="X32">
+        <v>10</v>
+      </c>
+      <c r="Y32">
         <v>7</v>
       </c>
-      <c r="X32">
+      <c r="Z32">
+        <v>-1</v>
+      </c>
+      <c r="AA32">
         <v>9</v>
-      </c>
-      <c r="Y32">
-        <v>5</v>
-      </c>
-      <c r="Z32">
-        <v>-1</v>
-      </c>
-      <c r="AA32">
-        <v>8</v>
       </c>
       <c r="AB32">
         <v>10</v>
@@ -3626,85 +3614,85 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D33">
+        <v>4</v>
+      </c>
+      <c r="E33">
+        <v>-1</v>
+      </c>
+      <c r="F33">
+        <v>5</v>
+      </c>
+      <c r="G33">
+        <v>5</v>
+      </c>
+      <c r="H33">
+        <v>6</v>
+      </c>
+      <c r="I33">
+        <v>-1</v>
+      </c>
+      <c r="J33">
+        <v>-1</v>
+      </c>
+      <c r="K33">
+        <v>-1</v>
+      </c>
+      <c r="L33">
+        <v>-1</v>
+      </c>
+      <c r="M33">
+        <v>-1</v>
+      </c>
+      <c r="N33">
+        <v>-1</v>
+      </c>
+      <c r="O33">
+        <v>-1</v>
+      </c>
+      <c r="P33">
+        <v>-1</v>
+      </c>
+      <c r="Q33">
+        <v>-1</v>
+      </c>
+      <c r="R33">
+        <v>-1</v>
+      </c>
+      <c r="S33">
+        <v>-1</v>
+      </c>
+      <c r="T33">
+        <v>-1</v>
+      </c>
+      <c r="U33">
+        <v>-1</v>
+      </c>
+      <c r="V33">
+        <v>-1</v>
+      </c>
+      <c r="W33">
+        <v>5</v>
+      </c>
+      <c r="X33">
         <v>7</v>
       </c>
-      <c r="E33">
-        <v>-1</v>
-      </c>
-      <c r="F33">
-        <v>9</v>
-      </c>
-      <c r="G33">
-        <v>10</v>
-      </c>
-      <c r="H33">
-        <v>6</v>
-      </c>
-      <c r="I33">
-        <v>-1</v>
-      </c>
-      <c r="J33">
-        <v>-1</v>
-      </c>
-      <c r="K33">
-        <v>-1</v>
-      </c>
-      <c r="L33">
-        <v>-1</v>
-      </c>
-      <c r="M33">
-        <v>-1</v>
-      </c>
-      <c r="N33">
-        <v>-1</v>
-      </c>
-      <c r="O33">
-        <v>-1</v>
-      </c>
-      <c r="P33">
-        <v>-1</v>
-      </c>
-      <c r="Q33">
-        <v>-1</v>
-      </c>
-      <c r="R33">
-        <v>-1</v>
-      </c>
-      <c r="S33">
-        <v>-1</v>
-      </c>
-      <c r="T33">
-        <v>-1</v>
-      </c>
-      <c r="U33">
-        <v>-1</v>
-      </c>
-      <c r="V33">
-        <v>-1</v>
-      </c>
-      <c r="W33">
-        <v>9</v>
-      </c>
-      <c r="X33">
-        <v>10</v>
-      </c>
       <c r="Y33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z33">
         <v>-1</v>
       </c>
       <c r="AA33">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AB33">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC33">
         <v>6</v>
@@ -3715,20 +3703,20 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C34">
+        <v>9</v>
+      </c>
+      <c r="D34">
+        <v>6</v>
+      </c>
+      <c r="E34">
+        <v>-1</v>
+      </c>
+      <c r="F34">
         <v>7</v>
       </c>
-      <c r="D34">
-        <v>4</v>
-      </c>
-      <c r="E34">
-        <v>-1</v>
-      </c>
-      <c r="F34">
-        <v>5</v>
-      </c>
       <c r="G34">
         <v>5</v>
       </c>
@@ -3778,19 +3766,19 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X34">
+        <v>9</v>
+      </c>
+      <c r="Y34">
+        <v>6</v>
+      </c>
+      <c r="Z34">
+        <v>-1</v>
+      </c>
+      <c r="AA34">
         <v>7</v>
-      </c>
-      <c r="Y34">
-        <v>5</v>
-      </c>
-      <c r="Z34">
-        <v>-1</v>
-      </c>
-      <c r="AA34">
-        <v>5</v>
       </c>
       <c r="AB34">
         <v>5</v>
@@ -3807,7 +3795,7 @@
         <v>7</v>
       </c>
       <c r="C35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D35">
         <v>6</v>
@@ -3816,10 +3804,10 @@
         <v>-1</v>
       </c>
       <c r="F35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H35">
         <v>6</v>
@@ -3870,7 +3858,7 @@
         <v>7</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y35">
         <v>6</v>
@@ -3879,10 +3867,10 @@
         <v>-1</v>
       </c>
       <c r="AA35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC35">
         <v>6</v>
@@ -3893,22 +3881,22 @@
         <v>45</v>
       </c>
       <c r="B36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E36">
         <v>-1</v>
       </c>
       <c r="F36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H36">
         <v>6</v>
@@ -3956,22 +3944,22 @@
         <v>-1</v>
       </c>
       <c r="W36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z36">
         <v>-1</v>
       </c>
       <c r="AA36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC36">
         <v>6</v>
@@ -3982,22 +3970,22 @@
         <v>46</v>
       </c>
       <c r="B37">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C37">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E37">
         <v>-1</v>
       </c>
       <c r="F37">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H37">
         <v>6</v>
@@ -4045,22 +4033,22 @@
         <v>-1</v>
       </c>
       <c r="W37">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X37">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y37">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z37">
         <v>-1</v>
       </c>
       <c r="AA37">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC37">
         <v>6</v>
@@ -4071,19 +4059,19 @@
         <v>47</v>
       </c>
       <c r="B38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C38">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E38">
         <v>-1</v>
       </c>
       <c r="F38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G38">
         <v>6</v>
@@ -4134,19 +4122,19 @@
         <v>-1</v>
       </c>
       <c r="W38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X38">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z38">
         <v>-1</v>
       </c>
       <c r="AA38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB38">
         <v>6</v>
@@ -4160,22 +4148,22 @@
         <v>48</v>
       </c>
       <c r="B39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C39">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D39">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E39">
         <v>-1</v>
       </c>
       <c r="F39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H39">
         <v>6</v>
@@ -4223,22 +4211,22 @@
         <v>-1</v>
       </c>
       <c r="W39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X39">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z39">
         <v>-1</v>
       </c>
       <c r="AA39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC39">
         <v>6</v>
@@ -4255,7 +4243,7 @@
         <v>5</v>
       </c>
       <c r="D40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E40">
         <v>-1</v>
@@ -4264,10 +4252,10 @@
         <v>5</v>
       </c>
       <c r="G40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -4318,7 +4306,7 @@
         <v>5</v>
       </c>
       <c r="Y40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z40">
         <v>-1</v>
@@ -4327,10 +4315,10 @@
         <v>5</v>
       </c>
       <c r="AB40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC40">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:29">
@@ -4338,10 +4326,10 @@
         <v>50</v>
       </c>
       <c r="B41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D41">
         <v>6</v>
@@ -4350,10 +4338,10 @@
         <v>-1</v>
       </c>
       <c r="F41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H41">
         <v>5</v>
@@ -4401,10 +4389,10 @@
         <v>-1</v>
       </c>
       <c r="W41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y41">
         <v>6</v>
@@ -4413,101 +4401,12 @@
         <v>-1</v>
       </c>
       <c r="AA41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC41">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:29">
-      <c r="A42" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B42">
-        <v>6</v>
-      </c>
-      <c r="C42">
-        <v>7</v>
-      </c>
-      <c r="D42">
-        <v>6</v>
-      </c>
-      <c r="E42">
-        <v>-1</v>
-      </c>
-      <c r="F42">
-        <v>6</v>
-      </c>
-      <c r="G42">
-        <v>5</v>
-      </c>
-      <c r="H42">
-        <v>5</v>
-      </c>
-      <c r="I42">
-        <v>-1</v>
-      </c>
-      <c r="J42">
-        <v>-1</v>
-      </c>
-      <c r="K42">
-        <v>-1</v>
-      </c>
-      <c r="L42">
-        <v>-1</v>
-      </c>
-      <c r="M42">
-        <v>-1</v>
-      </c>
-      <c r="N42">
-        <v>-1</v>
-      </c>
-      <c r="O42">
-        <v>-1</v>
-      </c>
-      <c r="P42">
-        <v>-1</v>
-      </c>
-      <c r="Q42">
-        <v>-1</v>
-      </c>
-      <c r="R42">
-        <v>-1</v>
-      </c>
-      <c r="S42">
-        <v>-1</v>
-      </c>
-      <c r="T42">
-        <v>-1</v>
-      </c>
-      <c r="U42">
-        <v>-1</v>
-      </c>
-      <c r="V42">
-        <v>-1</v>
-      </c>
-      <c r="W42">
-        <v>6</v>
-      </c>
-      <c r="X42">
-        <v>7</v>
-      </c>
-      <c r="Y42">
-        <v>6</v>
-      </c>
-      <c r="Z42">
-        <v>-1</v>
-      </c>
-      <c r="AA42">
-        <v>6</v>
-      </c>
-      <c r="AB42">
-        <v>5</v>
-      </c>
-      <c r="AC42">
         <v>5</v>
       </c>
     </row>
@@ -4524,40 +4423,43 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S42"/>
+  <dimension ref="A1:V41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:22">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-      <c r="N1" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
+      <c r="P1" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
-    </row>
-    <row r="2" spans="1:19">
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -4571,57 +4473,66 @@
         <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="P2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="S2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:22">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:22">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -4629,58 +4540,67 @@
         <v>80</v>
       </c>
       <c r="C4">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="D4">
-        <v>95.8</v>
+        <v>91.7</v>
       </c>
       <c r="E4">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>100</v>
       </c>
       <c r="G4">
-        <v>68.2</v>
+        <v>100</v>
       </c>
       <c r="H4">
+        <v>59.1</v>
+      </c>
+      <c r="I4">
         <v>80</v>
       </c>
-      <c r="I4">
-        <v>100</v>
-      </c>
       <c r="J4">
-        <v>95.8</v>
+        <v>66.7</v>
       </c>
       <c r="K4">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="L4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>68.2</v>
+        <v>100</v>
       </c>
       <c r="N4">
+        <v>100</v>
+      </c>
+      <c r="O4">
+        <v>59.1</v>
+      </c>
+      <c r="P4">
         <v>80</v>
       </c>
-      <c r="O4">
-        <v>100</v>
-      </c>
-      <c r="P4">
-        <v>95.8</v>
-      </c>
       <c r="Q4">
-        <v>90</v>
+        <v>66.7</v>
       </c>
       <c r="R4">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="S4">
-        <v>68.2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>100</v>
+      </c>
+      <c r="U4">
+        <v>100</v>
+      </c>
+      <c r="V4">
+        <v>59.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -4688,58 +4608,67 @@
         <v>80</v>
       </c>
       <c r="C5">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="D5">
-        <v>91.7</v>
+        <v>79.2</v>
       </c>
       <c r="E5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <v>100</v>
       </c>
       <c r="G5">
-        <v>59.1</v>
+        <v>93.8</v>
       </c>
       <c r="H5">
+        <v>68.2</v>
+      </c>
+      <c r="I5">
         <v>80</v>
       </c>
-      <c r="I5">
-        <v>66.7</v>
-      </c>
       <c r="J5">
-        <v>91.7</v>
+        <v>100</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>79.2</v>
       </c>
       <c r="L5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>59.1</v>
+        <v>100</v>
       </c>
       <c r="N5">
+        <v>93.8</v>
+      </c>
+      <c r="O5">
+        <v>68.2</v>
+      </c>
+      <c r="P5">
         <v>80</v>
       </c>
-      <c r="O5">
-        <v>66.7</v>
-      </c>
-      <c r="P5">
-        <v>91.7</v>
-      </c>
       <c r="Q5">
         <v>100</v>
       </c>
       <c r="R5">
-        <v>100</v>
+        <v>79.2</v>
       </c>
       <c r="S5">
-        <v>59.1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>100</v>
+      </c>
+      <c r="U5">
+        <v>93.8</v>
+      </c>
+      <c r="V5">
+        <v>68.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -4750,60 +4679,69 @@
         <v>100</v>
       </c>
       <c r="D6">
-        <v>79.2</v>
+        <v>95.8</v>
       </c>
       <c r="E6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F6">
+        <v>90</v>
+      </c>
+      <c r="G6">
         <v>93.8</v>
       </c>
-      <c r="G6">
-        <v>68.2</v>
-      </c>
       <c r="H6">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="I6">
         <v>80</v>
       </c>
-      <c r="I6">
-        <v>100</v>
-      </c>
       <c r="J6">
-        <v>79.2</v>
+        <v>100</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>90</v>
+      </c>
+      <c r="N6">
         <v>93.8</v>
       </c>
-      <c r="M6">
-        <v>68.2</v>
-      </c>
-      <c r="N6">
+      <c r="O6">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="P6">
         <v>80</v>
       </c>
-      <c r="O6">
-        <v>100</v>
-      </c>
-      <c r="P6">
-        <v>79.2</v>
-      </c>
       <c r="Q6">
         <v>100</v>
       </c>
       <c r="R6">
+        <v>95.8</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>90</v>
+      </c>
+      <c r="U6">
         <v>93.8</v>
       </c>
-      <c r="S6">
-        <v>68.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19">
+      <c r="V6">
+        <v>86.40000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B7">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -4812,57 +4750,66 @@
         <v>95.8</v>
       </c>
       <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>100</v>
+      </c>
+      <c r="G7">
+        <v>93.8</v>
+      </c>
+      <c r="H7">
+        <v>68.2</v>
+      </c>
+      <c r="I7">
         <v>90</v>
       </c>
-      <c r="F7">
+      <c r="J7">
+        <v>100</v>
+      </c>
+      <c r="K7">
+        <v>95.8</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>100</v>
+      </c>
+      <c r="N7">
         <v>93.8</v>
       </c>
-      <c r="G7">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="H7">
-        <v>80</v>
-      </c>
-      <c r="I7">
-        <v>100</v>
-      </c>
-      <c r="J7">
+      <c r="O7">
+        <v>68.2</v>
+      </c>
+      <c r="P7">
+        <v>90</v>
+      </c>
+      <c r="Q7">
+        <v>100</v>
+      </c>
+      <c r="R7">
         <v>95.8</v>
       </c>
-      <c r="K7">
-        <v>90</v>
-      </c>
-      <c r="L7">
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>100</v>
+      </c>
+      <c r="U7">
         <v>93.8</v>
       </c>
-      <c r="M7">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="N7">
-        <v>80</v>
-      </c>
-      <c r="O7">
-        <v>100</v>
-      </c>
-      <c r="P7">
-        <v>95.8</v>
-      </c>
-      <c r="Q7">
-        <v>90</v>
-      </c>
-      <c r="R7">
-        <v>93.8</v>
-      </c>
-      <c r="S7">
-        <v>86.40000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19">
+      <c r="V7">
+        <v>68.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B8">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -4871,229 +4818,265 @@
         <v>95.8</v>
       </c>
       <c r="E8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="G8">
-        <v>68.2</v>
+        <v>100</v>
       </c>
       <c r="H8">
-        <v>90</v>
+        <v>81.8</v>
       </c>
       <c r="I8">
         <v>100</v>
       </c>
       <c r="J8">
+        <v>100</v>
+      </c>
+      <c r="K8">
         <v>95.8</v>
       </c>
-      <c r="K8">
-        <v>100</v>
-      </c>
       <c r="L8">
-        <v>93.8</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>68.2</v>
+        <v>100</v>
       </c>
       <c r="N8">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="O8">
-        <v>100</v>
+        <v>81.8</v>
       </c>
       <c r="P8">
+        <v>100</v>
+      </c>
+      <c r="Q8">
+        <v>100</v>
+      </c>
+      <c r="R8">
         <v>95.8</v>
       </c>
-      <c r="Q8">
-        <v>100</v>
-      </c>
-      <c r="R8">
-        <v>93.8</v>
-      </c>
       <c r="S8">
-        <v>68.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>100</v>
+      </c>
+      <c r="U8">
+        <v>100</v>
+      </c>
+      <c r="V8">
+        <v>81.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C9">
         <v>100</v>
       </c>
       <c r="D9">
-        <v>95.8</v>
+        <v>91.7</v>
       </c>
       <c r="E9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F9">
         <v>100</v>
       </c>
       <c r="G9">
+        <v>100</v>
+      </c>
+      <c r="H9">
         <v>81.8</v>
       </c>
-      <c r="H9">
-        <v>100</v>
-      </c>
       <c r="I9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J9">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="L9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M9">
+        <v>100</v>
+      </c>
+      <c r="N9">
+        <v>100</v>
+      </c>
+      <c r="O9">
         <v>81.8</v>
       </c>
-      <c r="N9">
-        <v>100</v>
-      </c>
-      <c r="O9">
-        <v>100</v>
-      </c>
       <c r="P9">
-        <v>95.8</v>
+        <v>90</v>
       </c>
       <c r="Q9">
         <v>100</v>
       </c>
       <c r="R9">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>100</v>
+      </c>
+      <c r="U9">
+        <v>100</v>
+      </c>
+      <c r="V9">
         <v>81.8</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:22">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B10">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C10">
         <v>100</v>
       </c>
       <c r="D10">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="E10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G10">
-        <v>81.8</v>
+        <v>100</v>
       </c>
       <c r="H10">
-        <v>90</v>
+        <v>72.7</v>
       </c>
       <c r="I10">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J10">
-        <v>91.7</v>
+        <v>100</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>81.8</v>
+        <v>80</v>
       </c>
       <c r="N10">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="O10">
-        <v>100</v>
+        <v>72.7</v>
       </c>
       <c r="P10">
-        <v>91.7</v>
+        <v>80</v>
       </c>
       <c r="Q10">
         <v>100</v>
       </c>
       <c r="R10">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="S10">
-        <v>81.8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>80</v>
+      </c>
+      <c r="U10">
+        <v>100</v>
+      </c>
+      <c r="V10">
+        <v>72.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B11">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C11">
         <v>100</v>
       </c>
       <c r="D11">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="E11">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F11">
         <v>100</v>
       </c>
       <c r="G11">
-        <v>72.7</v>
+        <v>100</v>
       </c>
       <c r="H11">
-        <v>80</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I11">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J11">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="K11">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>72.7</v>
+        <v>100</v>
       </c>
       <c r="N11">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="O11">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="P11">
-        <v>95.8</v>
+        <v>90</v>
       </c>
       <c r="Q11">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R11">
         <v>100</v>
       </c>
       <c r="S11">
-        <v>72.7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>100</v>
+      </c>
+      <c r="U11">
+        <v>100</v>
+      </c>
+      <c r="V11">
+        <v>86.40000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
@@ -5104,55 +5087,64 @@
         <v>100</v>
       </c>
       <c r="D12">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="E12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <v>100</v>
       </c>
       <c r="G12">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H12">
+        <v>81.8</v>
+      </c>
+      <c r="I12">
         <v>90</v>
       </c>
-      <c r="I12">
-        <v>100</v>
-      </c>
       <c r="J12">
         <v>100</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M12">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="N12">
+        <v>100</v>
+      </c>
+      <c r="O12">
+        <v>81.8</v>
+      </c>
+      <c r="P12">
         <v>90</v>
       </c>
-      <c r="O12">
-        <v>100</v>
-      </c>
-      <c r="P12">
-        <v>100</v>
-      </c>
       <c r="Q12">
         <v>100</v>
       </c>
       <c r="R12">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="S12">
-        <v>86.40000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>100</v>
+      </c>
+      <c r="U12">
+        <v>100</v>
+      </c>
+      <c r="V12">
+        <v>81.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
@@ -5163,119 +5155,137 @@
         <v>100</v>
       </c>
       <c r="D13">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="E13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>100</v>
       </c>
       <c r="G13">
+        <v>100</v>
+      </c>
+      <c r="H13">
         <v>81.8</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>90</v>
       </c>
-      <c r="I13">
-        <v>100</v>
-      </c>
       <c r="J13">
-        <v>91.7</v>
+        <v>100</v>
       </c>
       <c r="K13">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="L13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M13">
+        <v>100</v>
+      </c>
+      <c r="N13">
+        <v>100</v>
+      </c>
+      <c r="O13">
         <v>81.8</v>
       </c>
-      <c r="N13">
+      <c r="P13">
         <v>90</v>
       </c>
-      <c r="O13">
-        <v>100</v>
-      </c>
-      <c r="P13">
-        <v>91.7</v>
-      </c>
       <c r="Q13">
         <v>100</v>
       </c>
       <c r="R13">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>100</v>
+      </c>
+      <c r="U13">
+        <v>100</v>
+      </c>
+      <c r="V13">
         <v>81.8</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:22">
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B14">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C14">
         <v>100</v>
       </c>
       <c r="D14">
-        <v>95.8</v>
+        <v>91.7</v>
       </c>
       <c r="E14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G14">
+        <v>100</v>
+      </c>
+      <c r="H14">
         <v>81.8</v>
       </c>
-      <c r="H14">
-        <v>90</v>
-      </c>
       <c r="I14">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J14">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="K14">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="L14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M14">
+        <v>80</v>
+      </c>
+      <c r="N14">
+        <v>100</v>
+      </c>
+      <c r="O14">
         <v>81.8</v>
       </c>
-      <c r="N14">
-        <v>90</v>
-      </c>
-      <c r="O14">
-        <v>100</v>
-      </c>
       <c r="P14">
-        <v>95.8</v>
+        <v>80</v>
       </c>
       <c r="Q14">
         <v>100</v>
       </c>
       <c r="R14">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>80</v>
+      </c>
+      <c r="U14">
+        <v>100</v>
+      </c>
+      <c r="V14">
         <v>81.8</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:22">
       <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B15">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -5284,57 +5294,66 @@
         <v>91.7</v>
       </c>
       <c r="E15">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <v>100</v>
       </c>
       <c r="G15">
-        <v>81.8</v>
+        <v>100</v>
       </c>
       <c r="H15">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I15">
         <v>100</v>
       </c>
       <c r="J15">
+        <v>100</v>
+      </c>
+      <c r="K15">
         <v>91.7</v>
       </c>
-      <c r="K15">
-        <v>80</v>
-      </c>
       <c r="L15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>81.8</v>
+        <v>100</v>
       </c>
       <c r="N15">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="O15">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P15">
+        <v>100</v>
+      </c>
+      <c r="Q15">
+        <v>100</v>
+      </c>
+      <c r="R15">
         <v>91.7</v>
       </c>
-      <c r="Q15">
-        <v>80</v>
-      </c>
-      <c r="R15">
-        <v>100</v>
-      </c>
       <c r="S15">
-        <v>81.8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>100</v>
+      </c>
+      <c r="U15">
+        <v>100</v>
+      </c>
+      <c r="V15">
+        <v>90.90000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
       <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B16">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -5343,52 +5362,61 @@
         <v>91.7</v>
       </c>
       <c r="E16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>100</v>
       </c>
       <c r="G16">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J16">
+        <v>100</v>
+      </c>
+      <c r="K16">
         <v>91.7</v>
       </c>
-      <c r="K16">
-        <v>100</v>
-      </c>
       <c r="L16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M16">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="N16">
         <v>100</v>
       </c>
       <c r="O16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P16">
+        <v>80</v>
+      </c>
+      <c r="Q16">
+        <v>100</v>
+      </c>
+      <c r="R16">
         <v>91.7</v>
       </c>
-      <c r="Q16">
-        <v>100</v>
-      </c>
-      <c r="R16">
-        <v>100</v>
-      </c>
       <c r="S16">
-        <v>90.90000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>100</v>
+      </c>
+      <c r="U16">
+        <v>100</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
@@ -5402,52 +5430,61 @@
         <v>91.7</v>
       </c>
       <c r="E17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>100</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17">
+        <v>77.3</v>
+      </c>
+      <c r="I17">
         <v>80</v>
       </c>
-      <c r="I17">
-        <v>100</v>
-      </c>
       <c r="J17">
+        <v>100</v>
+      </c>
+      <c r="K17">
         <v>91.7</v>
       </c>
-      <c r="K17">
-        <v>100</v>
-      </c>
       <c r="L17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N17">
+        <v>100</v>
+      </c>
+      <c r="O17">
+        <v>77.3</v>
+      </c>
+      <c r="P17">
         <v>80</v>
       </c>
-      <c r="O17">
-        <v>100</v>
-      </c>
-      <c r="P17">
+      <c r="Q17">
+        <v>100</v>
+      </c>
+      <c r="R17">
         <v>91.7</v>
       </c>
-      <c r="Q17">
-        <v>100</v>
-      </c>
-      <c r="R17">
-        <v>100</v>
-      </c>
       <c r="S17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:19">
+      <c r="T17">
+        <v>100</v>
+      </c>
+      <c r="U17">
+        <v>100</v>
+      </c>
+      <c r="V17">
+        <v>77.3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
@@ -5458,60 +5495,69 @@
         <v>100</v>
       </c>
       <c r="D18">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="E18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F18">
         <v>100</v>
       </c>
       <c r="G18">
-        <v>77.3</v>
+        <v>100</v>
       </c>
       <c r="H18">
+        <v>68.2</v>
+      </c>
+      <c r="I18">
         <v>80</v>
       </c>
-      <c r="I18">
-        <v>100</v>
-      </c>
       <c r="J18">
-        <v>91.7</v>
+        <v>100</v>
       </c>
       <c r="K18">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="L18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>77.3</v>
+        <v>100</v>
       </c>
       <c r="N18">
+        <v>100</v>
+      </c>
+      <c r="O18">
+        <v>68.2</v>
+      </c>
+      <c r="P18">
         <v>80</v>
       </c>
-      <c r="O18">
-        <v>100</v>
-      </c>
-      <c r="P18">
-        <v>91.7</v>
-      </c>
       <c r="Q18">
         <v>100</v>
       </c>
       <c r="R18">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="S18">
-        <v>77.3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>100</v>
+      </c>
+      <c r="U18">
+        <v>100</v>
+      </c>
+      <c r="V18">
+        <v>68.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B19">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -5520,52 +5566,61 @@
         <v>95.8</v>
       </c>
       <c r="E19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G19">
-        <v>68.2</v>
+        <v>87.5</v>
       </c>
       <c r="H19">
-        <v>80</v>
+        <v>81.8</v>
       </c>
       <c r="I19">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J19">
+        <v>100</v>
+      </c>
+      <c r="K19">
         <v>95.8</v>
       </c>
-      <c r="K19">
-        <v>100</v>
-      </c>
       <c r="L19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M19">
-        <v>68.2</v>
+        <v>90</v>
       </c>
       <c r="N19">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="O19">
-        <v>100</v>
+        <v>81.8</v>
       </c>
       <c r="P19">
+        <v>90</v>
+      </c>
+      <c r="Q19">
+        <v>100</v>
+      </c>
+      <c r="R19">
         <v>95.8</v>
       </c>
-      <c r="Q19">
-        <v>100</v>
-      </c>
-      <c r="R19">
-        <v>100</v>
-      </c>
       <c r="S19">
-        <v>68.2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>90</v>
+      </c>
+      <c r="U19">
+        <v>87.5</v>
+      </c>
+      <c r="V19">
+        <v>81.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
@@ -5576,114 +5631,132 @@
         <v>100</v>
       </c>
       <c r="D20">
-        <v>95.8</v>
+        <v>91.7</v>
       </c>
       <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>80</v>
+      </c>
+      <c r="G20">
+        <v>100</v>
+      </c>
+      <c r="H20">
+        <v>68.2</v>
+      </c>
+      <c r="I20">
         <v>90</v>
       </c>
-      <c r="F20">
-        <v>87.5</v>
-      </c>
-      <c r="G20">
-        <v>81.8</v>
-      </c>
-      <c r="H20">
+      <c r="J20">
+        <v>100</v>
+      </c>
+      <c r="K20">
+        <v>91.7</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>80</v>
+      </c>
+      <c r="N20">
+        <v>100</v>
+      </c>
+      <c r="O20">
+        <v>68.2</v>
+      </c>
+      <c r="P20">
         <v>90</v>
       </c>
-      <c r="I20">
-        <v>100</v>
-      </c>
-      <c r="J20">
-        <v>95.8</v>
-      </c>
-      <c r="K20">
-        <v>90</v>
-      </c>
-      <c r="L20">
-        <v>87.5</v>
-      </c>
-      <c r="M20">
-        <v>81.8</v>
-      </c>
-      <c r="N20">
-        <v>90</v>
-      </c>
-      <c r="O20">
-        <v>100</v>
-      </c>
-      <c r="P20">
-        <v>95.8</v>
-      </c>
       <c r="Q20">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R20">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="S20">
-        <v>81.8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>80</v>
+      </c>
+      <c r="U20">
+        <v>100</v>
+      </c>
+      <c r="V20">
+        <v>68.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B21">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C21">
         <v>100</v>
       </c>
       <c r="D21">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>100</v>
+      </c>
+      <c r="G21">
+        <v>87.5</v>
+      </c>
+      <c r="H21">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="I21">
         <v>80</v>
       </c>
-      <c r="F21">
-        <v>100</v>
-      </c>
-      <c r="G21">
-        <v>68.2</v>
-      </c>
-      <c r="H21">
-        <v>90</v>
-      </c>
-      <c r="I21">
-        <v>100</v>
-      </c>
       <c r="J21">
-        <v>91.7</v>
+        <v>100</v>
       </c>
       <c r="K21">
+        <v>95.8</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>100</v>
+      </c>
+      <c r="N21">
+        <v>87.5</v>
+      </c>
+      <c r="O21">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="P21">
         <v>80</v>
       </c>
-      <c r="L21">
-        <v>100</v>
-      </c>
-      <c r="M21">
-        <v>68.2</v>
-      </c>
-      <c r="N21">
-        <v>90</v>
-      </c>
-      <c r="O21">
-        <v>100</v>
-      </c>
-      <c r="P21">
-        <v>91.7</v>
-      </c>
       <c r="Q21">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R21">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="S21">
-        <v>68.2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>100</v>
+      </c>
+      <c r="U21">
+        <v>87.5</v>
+      </c>
+      <c r="V21">
+        <v>86.40000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
@@ -5694,55 +5767,64 @@
         <v>100</v>
       </c>
       <c r="D22">
-        <v>95.8</v>
+        <v>91.7</v>
       </c>
       <c r="E22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="G22">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H22">
+        <v>81.8</v>
+      </c>
+      <c r="I22">
         <v>80</v>
       </c>
-      <c r="I22">
-        <v>100</v>
-      </c>
       <c r="J22">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="L22">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="N22">
+        <v>100</v>
+      </c>
+      <c r="O22">
+        <v>81.8</v>
+      </c>
+      <c r="P22">
         <v>80</v>
       </c>
-      <c r="O22">
-        <v>100</v>
-      </c>
-      <c r="P22">
-        <v>95.8</v>
-      </c>
       <c r="Q22">
         <v>100</v>
       </c>
       <c r="R22">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="S22">
-        <v>86.40000000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>100</v>
+      </c>
+      <c r="U22">
+        <v>100</v>
+      </c>
+      <c r="V22">
+        <v>81.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
       <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
@@ -5753,55 +5835,64 @@
         <v>100</v>
       </c>
       <c r="D23">
-        <v>91.7</v>
+        <v>83.3</v>
       </c>
       <c r="E23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <v>100</v>
       </c>
       <c r="G23">
-        <v>81.8</v>
+        <v>93.8</v>
       </c>
       <c r="H23">
+        <v>36.4</v>
+      </c>
+      <c r="I23">
         <v>80</v>
       </c>
-      <c r="I23">
-        <v>100</v>
-      </c>
       <c r="J23">
-        <v>91.7</v>
+        <v>100</v>
       </c>
       <c r="K23">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="L23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M23">
-        <v>81.8</v>
+        <v>100</v>
       </c>
       <c r="N23">
+        <v>93.8</v>
+      </c>
+      <c r="O23">
+        <v>36.4</v>
+      </c>
+      <c r="P23">
         <v>80</v>
       </c>
-      <c r="O23">
-        <v>100</v>
-      </c>
-      <c r="P23">
-        <v>91.7</v>
-      </c>
       <c r="Q23">
         <v>100</v>
       </c>
       <c r="R23">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="S23">
-        <v>81.8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>100</v>
+      </c>
+      <c r="U23">
+        <v>93.8</v>
+      </c>
+      <c r="V23">
+        <v>36.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24" s="1" t="s">
         <v>33</v>
       </c>
@@ -5812,55 +5903,64 @@
         <v>100</v>
       </c>
       <c r="D24">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="E24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>93.8</v>
+        <v>90</v>
       </c>
       <c r="G24">
-        <v>36.4</v>
+        <v>100</v>
       </c>
       <c r="H24">
+        <v>81.8</v>
+      </c>
+      <c r="I24">
         <v>80</v>
       </c>
-      <c r="I24">
-        <v>100</v>
-      </c>
       <c r="J24">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="K24">
         <v>100</v>
       </c>
       <c r="L24">
-        <v>93.8</v>
+        <v>0</v>
       </c>
       <c r="M24">
-        <v>36.4</v>
+        <v>90</v>
       </c>
       <c r="N24">
+        <v>100</v>
+      </c>
+      <c r="O24">
+        <v>81.8</v>
+      </c>
+      <c r="P24">
         <v>80</v>
       </c>
-      <c r="O24">
-        <v>100</v>
-      </c>
-      <c r="P24">
-        <v>83.3</v>
-      </c>
       <c r="Q24">
         <v>100</v>
       </c>
       <c r="R24">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="S24">
-        <v>36.4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>90</v>
+      </c>
+      <c r="U24">
+        <v>100</v>
+      </c>
+      <c r="V24">
+        <v>81.8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
       <c r="A25" s="1" t="s">
         <v>34</v>
       </c>
@@ -5871,114 +5971,132 @@
         <v>100</v>
       </c>
       <c r="D25">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="E25">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F25">
         <v>100</v>
       </c>
       <c r="G25">
-        <v>81.8</v>
+        <v>93.8</v>
       </c>
       <c r="H25">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="I25">
         <v>80</v>
       </c>
-      <c r="I25">
-        <v>100</v>
-      </c>
       <c r="J25">
         <v>100</v>
       </c>
       <c r="K25">
-        <v>90</v>
+        <v>95.8</v>
       </c>
       <c r="L25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M25">
-        <v>81.8</v>
+        <v>100</v>
       </c>
       <c r="N25">
+        <v>93.8</v>
+      </c>
+      <c r="O25">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="P25">
         <v>80</v>
       </c>
-      <c r="O25">
-        <v>100</v>
-      </c>
-      <c r="P25">
-        <v>100</v>
-      </c>
       <c r="Q25">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R25">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="S25">
-        <v>81.8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>100</v>
+      </c>
+      <c r="U25">
+        <v>93.8</v>
+      </c>
+      <c r="V25">
+        <v>86.40000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B26">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C26">
         <v>100</v>
       </c>
       <c r="D26">
-        <v>95.8</v>
+        <v>91.7</v>
       </c>
       <c r="E26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F26">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="G26">
-        <v>86.40000000000001</v>
+        <v>31.3</v>
       </c>
       <c r="H26">
-        <v>80</v>
+        <v>72.7</v>
       </c>
       <c r="I26">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J26">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="K26">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="L26">
-        <v>93.8</v>
+        <v>0</v>
       </c>
       <c r="M26">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="N26">
-        <v>80</v>
+        <v>31.3</v>
       </c>
       <c r="O26">
-        <v>100</v>
+        <v>72.7</v>
       </c>
       <c r="P26">
-        <v>95.8</v>
+        <v>90</v>
       </c>
       <c r="Q26">
         <v>100</v>
       </c>
       <c r="R26">
-        <v>93.8</v>
+        <v>91.7</v>
       </c>
       <c r="S26">
-        <v>86.40000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>100</v>
+      </c>
+      <c r="U26">
+        <v>31.3</v>
+      </c>
+      <c r="V26">
+        <v>72.7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27" s="1" t="s">
         <v>36</v>
       </c>
@@ -5989,119 +6107,137 @@
         <v>100</v>
       </c>
       <c r="D27">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="E27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>31.3</v>
+        <v>100</v>
       </c>
       <c r="G27">
-        <v>72.7</v>
+        <v>93.8</v>
       </c>
       <c r="H27">
+        <v>81.8</v>
+      </c>
+      <c r="I27">
         <v>90</v>
       </c>
-      <c r="I27">
-        <v>100</v>
-      </c>
       <c r="J27">
-        <v>91.7</v>
+        <v>100</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="L27">
-        <v>31.3</v>
+        <v>0</v>
       </c>
       <c r="M27">
-        <v>72.7</v>
+        <v>100</v>
       </c>
       <c r="N27">
+        <v>93.8</v>
+      </c>
+      <c r="O27">
+        <v>81.8</v>
+      </c>
+      <c r="P27">
         <v>90</v>
       </c>
-      <c r="O27">
-        <v>100</v>
-      </c>
-      <c r="P27">
-        <v>91.7</v>
-      </c>
       <c r="Q27">
         <v>100</v>
       </c>
       <c r="R27">
-        <v>31.3</v>
+        <v>95.8</v>
       </c>
       <c r="S27">
-        <v>72.7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>100</v>
+      </c>
+      <c r="U27">
+        <v>93.8</v>
+      </c>
+      <c r="V27">
+        <v>81.8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B28">
+        <v>80</v>
+      </c>
+      <c r="C28">
+        <v>100</v>
+      </c>
+      <c r="D28">
+        <v>91.7</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
         <v>90</v>
       </c>
-      <c r="C28">
-        <v>100</v>
-      </c>
-      <c r="D28">
-        <v>95.8</v>
-      </c>
-      <c r="E28">
-        <v>100</v>
-      </c>
-      <c r="F28">
+      <c r="G28">
         <v>93.8</v>
       </c>
-      <c r="G28">
-        <v>81.8</v>
-      </c>
       <c r="H28">
+        <v>100</v>
+      </c>
+      <c r="I28">
+        <v>80</v>
+      </c>
+      <c r="J28">
+        <v>100</v>
+      </c>
+      <c r="K28">
+        <v>91.7</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
         <v>90</v>
       </c>
-      <c r="I28">
-        <v>100</v>
-      </c>
-      <c r="J28">
-        <v>95.8</v>
-      </c>
-      <c r="K28">
-        <v>100</v>
-      </c>
-      <c r="L28">
+      <c r="N28">
         <v>93.8</v>
       </c>
-      <c r="M28">
-        <v>81.8</v>
-      </c>
-      <c r="N28">
+      <c r="O28">
+        <v>100</v>
+      </c>
+      <c r="P28">
+        <v>80</v>
+      </c>
+      <c r="Q28">
+        <v>100</v>
+      </c>
+      <c r="R28">
+        <v>91.7</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
         <v>90</v>
       </c>
-      <c r="O28">
-        <v>100</v>
-      </c>
-      <c r="P28">
-        <v>95.8</v>
-      </c>
-      <c r="Q28">
-        <v>100</v>
-      </c>
-      <c r="R28">
+      <c r="U28">
         <v>93.8</v>
       </c>
-      <c r="S28">
-        <v>81.8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19">
+      <c r="V28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B29">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C29">
         <v>100</v>
@@ -6110,99 +6246,108 @@
         <v>91.7</v>
       </c>
       <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>100</v>
+      </c>
+      <c r="G29">
+        <v>100</v>
+      </c>
+      <c r="H29">
+        <v>81.8</v>
+      </c>
+      <c r="I29">
         <v>90</v>
       </c>
-      <c r="F29">
-        <v>93.8</v>
-      </c>
-      <c r="G29">
-        <v>100</v>
-      </c>
-      <c r="H29">
-        <v>80</v>
-      </c>
-      <c r="I29">
-        <v>100</v>
-      </c>
       <c r="J29">
+        <v>100</v>
+      </c>
+      <c r="K29">
         <v>91.7</v>
       </c>
-      <c r="K29">
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>100</v>
+      </c>
+      <c r="N29">
+        <v>100</v>
+      </c>
+      <c r="O29">
+        <v>81.8</v>
+      </c>
+      <c r="P29">
         <v>90</v>
       </c>
-      <c r="L29">
-        <v>93.8</v>
-      </c>
-      <c r="M29">
-        <v>100</v>
-      </c>
-      <c r="N29">
-        <v>80</v>
-      </c>
-      <c r="O29">
-        <v>100</v>
-      </c>
-      <c r="P29">
+      <c r="Q29">
+        <v>100</v>
+      </c>
+      <c r="R29">
         <v>91.7</v>
       </c>
-      <c r="Q29">
-        <v>90</v>
-      </c>
-      <c r="R29">
-        <v>93.8</v>
-      </c>
       <c r="S29">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>100</v>
+      </c>
+      <c r="U29">
+        <v>100</v>
+      </c>
+      <c r="V29">
+        <v>81.8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B30">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C30">
         <v>100</v>
       </c>
       <c r="D30">
-        <v>91.7</v>
+        <v>100</v>
       </c>
       <c r="E30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F30">
         <v>100</v>
       </c>
       <c r="G30">
+        <v>100</v>
+      </c>
+      <c r="H30">
         <v>81.8</v>
       </c>
-      <c r="H30">
-        <v>90</v>
-      </c>
       <c r="I30">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J30">
-        <v>91.7</v>
+        <v>100</v>
       </c>
       <c r="K30">
         <v>100</v>
       </c>
       <c r="L30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M30">
+        <v>100</v>
+      </c>
+      <c r="N30">
+        <v>100</v>
+      </c>
+      <c r="O30">
         <v>81.8</v>
       </c>
-      <c r="N30">
-        <v>90</v>
-      </c>
-      <c r="O30">
-        <v>100</v>
-      </c>
       <c r="P30">
-        <v>91.7</v>
+        <v>80</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -6211,116 +6356,134 @@
         <v>100</v>
       </c>
       <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>100</v>
+      </c>
+      <c r="U30">
+        <v>100</v>
+      </c>
+      <c r="V30">
         <v>81.8</v>
       </c>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:22">
       <c r="A31" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B31">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C31">
         <v>100</v>
       </c>
       <c r="D31">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="E31">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F31">
         <v>100</v>
       </c>
       <c r="G31">
+        <v>100</v>
+      </c>
+      <c r="H31">
         <v>81.8</v>
       </c>
-      <c r="H31">
-        <v>80</v>
-      </c>
       <c r="I31">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J31">
         <v>100</v>
       </c>
       <c r="K31">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="L31">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M31">
+        <v>100</v>
+      </c>
+      <c r="N31">
+        <v>100</v>
+      </c>
+      <c r="O31">
         <v>81.8</v>
       </c>
-      <c r="N31">
-        <v>80</v>
-      </c>
-      <c r="O31">
-        <v>100</v>
-      </c>
       <c r="P31">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q31">
         <v>100</v>
       </c>
       <c r="R31">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>100</v>
+      </c>
+      <c r="U31">
+        <v>100</v>
+      </c>
+      <c r="V31">
         <v>81.8</v>
       </c>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:22">
       <c r="A32" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B32">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C32">
         <v>100</v>
       </c>
       <c r="D32">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="E32">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F32">
         <v>100</v>
       </c>
       <c r="G32">
+        <v>100</v>
+      </c>
+      <c r="H32">
         <v>81.8</v>
       </c>
-      <c r="H32">
-        <v>90</v>
-      </c>
       <c r="I32">
         <v>100</v>
       </c>
       <c r="J32">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="K32">
         <v>100</v>
       </c>
       <c r="L32">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M32">
+        <v>100</v>
+      </c>
+      <c r="N32">
+        <v>100</v>
+      </c>
+      <c r="O32">
         <v>81.8</v>
       </c>
-      <c r="N32">
-        <v>90</v>
-      </c>
-      <c r="O32">
-        <v>100</v>
-      </c>
       <c r="P32">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="Q32">
         <v>100</v>
@@ -6329,128 +6492,155 @@
         <v>100</v>
       </c>
       <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>100</v>
+      </c>
+      <c r="U32">
+        <v>100</v>
+      </c>
+      <c r="V32">
         <v>81.8</v>
       </c>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:22">
       <c r="A33" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B33">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C33">
         <v>100</v>
       </c>
       <c r="D33">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="E33">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G33">
+        <v>93.8</v>
+      </c>
+      <c r="H33">
         <v>81.8</v>
       </c>
-      <c r="H33">
-        <v>100</v>
-      </c>
       <c r="I33">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J33">
         <v>100</v>
       </c>
       <c r="K33">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="L33">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M33">
+        <v>80</v>
+      </c>
+      <c r="N33">
+        <v>93.8</v>
+      </c>
+      <c r="O33">
         <v>81.8</v>
       </c>
-      <c r="N33">
-        <v>100</v>
-      </c>
-      <c r="O33">
-        <v>100</v>
-      </c>
       <c r="P33">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q33">
         <v>100</v>
       </c>
       <c r="R33">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>80</v>
+      </c>
+      <c r="U33">
+        <v>93.8</v>
+      </c>
+      <c r="V33">
         <v>81.8</v>
       </c>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:22">
       <c r="A34" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B34">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C34">
         <v>100</v>
       </c>
       <c r="D34">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="E34">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F34">
+        <v>100</v>
+      </c>
+      <c r="G34">
         <v>93.8</v>
       </c>
-      <c r="G34">
-        <v>81.8</v>
-      </c>
       <c r="H34">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I34">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J34">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="K34">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>100</v>
+      </c>
+      <c r="N34">
         <v>93.8</v>
       </c>
-      <c r="M34">
-        <v>81.8</v>
-      </c>
-      <c r="N34">
-        <v>80</v>
-      </c>
       <c r="O34">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P34">
-        <v>87.5</v>
+        <v>90</v>
       </c>
       <c r="Q34">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R34">
+        <v>100</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>100</v>
+      </c>
+      <c r="U34">
         <v>93.8</v>
       </c>
-      <c r="S34">
-        <v>81.8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19">
+      <c r="V34">
+        <v>90.90000000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22">
       <c r="A35" s="1" t="s">
         <v>44</v>
       </c>
@@ -6461,60 +6651,69 @@
         <v>100</v>
       </c>
       <c r="D35">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="E35">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F35">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="G35">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H35">
+        <v>81.8</v>
+      </c>
+      <c r="I35">
         <v>90</v>
       </c>
-      <c r="I35">
-        <v>100</v>
-      </c>
       <c r="J35">
         <v>100</v>
       </c>
       <c r="K35">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="L35">
-        <v>93.8</v>
+        <v>0</v>
       </c>
       <c r="M35">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="N35">
+        <v>100</v>
+      </c>
+      <c r="O35">
+        <v>81.8</v>
+      </c>
+      <c r="P35">
         <v>90</v>
       </c>
-      <c r="O35">
-        <v>100</v>
-      </c>
-      <c r="P35">
-        <v>100</v>
-      </c>
       <c r="Q35">
         <v>100</v>
       </c>
       <c r="R35">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="S35">
-        <v>90.90000000000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>100</v>
+      </c>
+      <c r="U35">
+        <v>100</v>
+      </c>
+      <c r="V35">
+        <v>81.8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22">
       <c r="A36" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B36">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C36">
         <v>100</v>
@@ -6523,57 +6722,66 @@
         <v>95.8</v>
       </c>
       <c r="E36">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F36">
         <v>100</v>
       </c>
       <c r="G36">
+        <v>100</v>
+      </c>
+      <c r="H36">
         <v>81.8</v>
       </c>
-      <c r="H36">
-        <v>90</v>
-      </c>
       <c r="I36">
         <v>100</v>
       </c>
       <c r="J36">
+        <v>100</v>
+      </c>
+      <c r="K36">
         <v>95.8</v>
       </c>
-      <c r="K36">
-        <v>100</v>
-      </c>
       <c r="L36">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M36">
+        <v>100</v>
+      </c>
+      <c r="N36">
+        <v>100</v>
+      </c>
+      <c r="O36">
         <v>81.8</v>
       </c>
-      <c r="N36">
-        <v>90</v>
-      </c>
-      <c r="O36">
-        <v>100</v>
-      </c>
       <c r="P36">
+        <v>100</v>
+      </c>
+      <c r="Q36">
+        <v>100</v>
+      </c>
+      <c r="R36">
         <v>95.8</v>
       </c>
-      <c r="Q36">
-        <v>100</v>
-      </c>
-      <c r="R36">
-        <v>100</v>
-      </c>
       <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>100</v>
+      </c>
+      <c r="U36">
+        <v>100</v>
+      </c>
+      <c r="V36">
         <v>81.8</v>
       </c>
     </row>
-    <row r="37" spans="1:19">
+    <row r="37" spans="1:22">
       <c r="A37" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B37">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C37">
         <v>100</v>
@@ -6582,170 +6790,197 @@
         <v>95.8</v>
       </c>
       <c r="E37">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F37">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G37">
+        <v>100</v>
+      </c>
+      <c r="H37">
         <v>81.8</v>
       </c>
-      <c r="H37">
-        <v>100</v>
-      </c>
       <c r="I37">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J37">
+        <v>100</v>
+      </c>
+      <c r="K37">
         <v>95.8</v>
       </c>
-      <c r="K37">
-        <v>100</v>
-      </c>
       <c r="L37">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M37">
+        <v>90</v>
+      </c>
+      <c r="N37">
+        <v>100</v>
+      </c>
+      <c r="O37">
         <v>81.8</v>
       </c>
-      <c r="N37">
-        <v>100</v>
-      </c>
-      <c r="O37">
-        <v>100</v>
-      </c>
       <c r="P37">
+        <v>80</v>
+      </c>
+      <c r="Q37">
+        <v>100</v>
+      </c>
+      <c r="R37">
         <v>95.8</v>
       </c>
-      <c r="Q37">
-        <v>100</v>
-      </c>
-      <c r="R37">
-        <v>100</v>
-      </c>
       <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>90</v>
+      </c>
+      <c r="U37">
+        <v>100</v>
+      </c>
+      <c r="V37">
         <v>81.8</v>
       </c>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:22">
       <c r="A38" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B38">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C38">
         <v>100</v>
       </c>
       <c r="D38">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>100</v>
+      </c>
+      <c r="G38">
+        <v>100</v>
+      </c>
+      <c r="H38">
+        <v>81.8</v>
+      </c>
+      <c r="I38">
         <v>90</v>
       </c>
-      <c r="F38">
-        <v>100</v>
-      </c>
-      <c r="G38">
+      <c r="J38">
+        <v>100</v>
+      </c>
+      <c r="K38">
+        <v>100</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>100</v>
+      </c>
+      <c r="N38">
+        <v>100</v>
+      </c>
+      <c r="O38">
         <v>81.8</v>
       </c>
-      <c r="H38">
-        <v>80</v>
-      </c>
-      <c r="I38">
-        <v>100</v>
-      </c>
-      <c r="J38">
-        <v>95.8</v>
-      </c>
-      <c r="K38">
+      <c r="P38">
         <v>90</v>
       </c>
-      <c r="L38">
-        <v>100</v>
-      </c>
-      <c r="M38">
+      <c r="Q38">
+        <v>100</v>
+      </c>
+      <c r="R38">
+        <v>100</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>100</v>
+      </c>
+      <c r="U38">
+        <v>100</v>
+      </c>
+      <c r="V38">
         <v>81.8</v>
       </c>
-      <c r="N38">
-        <v>80</v>
-      </c>
-      <c r="O38">
-        <v>100</v>
-      </c>
-      <c r="P38">
-        <v>95.8</v>
-      </c>
-      <c r="Q38">
-        <v>90</v>
-      </c>
-      <c r="R38">
-        <v>100</v>
-      </c>
-      <c r="S38">
-        <v>81.8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19">
+    </row>
+    <row r="39" spans="1:22">
       <c r="A39" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B39">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C39">
         <v>100</v>
       </c>
       <c r="D39">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="E39">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F39">
         <v>100</v>
       </c>
       <c r="G39">
-        <v>81.8</v>
+        <v>93.8</v>
       </c>
       <c r="H39">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I39">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J39">
         <v>100</v>
       </c>
       <c r="K39">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="L39">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M39">
-        <v>81.8</v>
+        <v>100</v>
       </c>
       <c r="N39">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="O39">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P39">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q39">
         <v>100</v>
       </c>
       <c r="R39">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="S39">
-        <v>81.8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>100</v>
+      </c>
+      <c r="U39">
+        <v>93.8</v>
+      </c>
+      <c r="V39">
+        <v>90.90000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22">
       <c r="A40" s="1" t="s">
         <v>49</v>
       </c>
@@ -6756,55 +6991,64 @@
         <v>100</v>
       </c>
       <c r="D40">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="E40">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>93.8</v>
+        <v>90</v>
       </c>
       <c r="G40">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H40">
+        <v>77.3</v>
+      </c>
+      <c r="I40">
         <v>80</v>
       </c>
-      <c r="I40">
-        <v>100</v>
-      </c>
       <c r="J40">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="K40">
         <v>100</v>
       </c>
       <c r="L40">
-        <v>93.8</v>
+        <v>0</v>
       </c>
       <c r="M40">
-        <v>90.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="N40">
+        <v>100</v>
+      </c>
+      <c r="O40">
+        <v>77.3</v>
+      </c>
+      <c r="P40">
         <v>80</v>
       </c>
-      <c r="O40">
-        <v>100</v>
-      </c>
-      <c r="P40">
-        <v>95.8</v>
-      </c>
       <c r="Q40">
         <v>100</v>
       </c>
       <c r="R40">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="S40">
-        <v>90.90000000000001</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>90</v>
+      </c>
+      <c r="U40">
+        <v>100</v>
+      </c>
+      <c r="V40">
+        <v>77.3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22">
       <c r="A41" s="1" t="s">
         <v>50</v>
       </c>
@@ -6818,115 +7062,65 @@
         <v>100</v>
       </c>
       <c r="E41">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F41">
         <v>100</v>
       </c>
       <c r="G41">
-        <v>77.3</v>
+        <v>93.8</v>
       </c>
       <c r="H41">
+        <v>72.7</v>
+      </c>
+      <c r="I41">
         <v>80</v>
       </c>
-      <c r="I41">
-        <v>100</v>
-      </c>
       <c r="J41">
         <v>100</v>
       </c>
       <c r="K41">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="L41">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M41">
-        <v>77.3</v>
+        <v>100</v>
       </c>
       <c r="N41">
+        <v>93.8</v>
+      </c>
+      <c r="O41">
+        <v>72.7</v>
+      </c>
+      <c r="P41">
         <v>80</v>
       </c>
-      <c r="O41">
-        <v>100</v>
-      </c>
-      <c r="P41">
-        <v>100</v>
-      </c>
       <c r="Q41">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R41">
         <v>100</v>
       </c>
       <c r="S41">
-        <v>77.3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19">
-      <c r="A42" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B42">
-        <v>80</v>
-      </c>
-      <c r="C42">
-        <v>100</v>
-      </c>
-      <c r="D42">
-        <v>100</v>
-      </c>
-      <c r="E42">
-        <v>100</v>
-      </c>
-      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>100</v>
+      </c>
+      <c r="U41">
         <v>93.8</v>
       </c>
-      <c r="G42">
-        <v>72.7</v>
-      </c>
-      <c r="H42">
-        <v>80</v>
-      </c>
-      <c r="I42">
-        <v>100</v>
-      </c>
-      <c r="J42">
-        <v>100</v>
-      </c>
-      <c r="K42">
-        <v>100</v>
-      </c>
-      <c r="L42">
-        <v>93.8</v>
-      </c>
-      <c r="M42">
-        <v>72.7</v>
-      </c>
-      <c r="N42">
-        <v>80</v>
-      </c>
-      <c r="O42">
-        <v>100</v>
-      </c>
-      <c r="P42">
-        <v>100</v>
-      </c>
-      <c r="Q42">
-        <v>100</v>
-      </c>
-      <c r="R42">
-        <v>93.8</v>
-      </c>
-      <c r="S42">
+      <c r="V41">
         <v>72.7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="N1:S1"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="P1:V1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6947,31 +7141,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -6979,10 +7173,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -6997,7 +7191,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J2" s="2">
         <v>100</v>
@@ -7008,22 +7202,22 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E3">
         <v>18</v>
       </c>
       <c r="F3" s="2">
-        <v>53.8</v>
+        <v>52.6</v>
       </c>
       <c r="G3" s="2">
-        <v>46.2</v>
+        <v>47.4</v>
       </c>
       <c r="H3">
         <v>6.4</v>
@@ -7040,22 +7234,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C4">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4">
         <v>23</v>
       </c>
       <c r="E4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F4" s="2">
-        <v>59</v>
+        <v>60.5</v>
       </c>
       <c r="G4" s="2">
-        <v>41</v>
+        <v>39.5</v>
       </c>
       <c r="H4">
         <v>6.3</v>
@@ -7072,22 +7266,22 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E5">
         <v>12</v>
       </c>
       <c r="F5" s="2">
-        <v>69.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>30.8</v>
+        <v>31.6</v>
       </c>
       <c r="H5">
         <v>6.3</v>
@@ -7104,22 +7298,22 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C6">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E6">
         <v>11</v>
       </c>
       <c r="F6" s="2">
-        <v>71.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>28.2</v>
+        <v>28.9</v>
       </c>
       <c r="H6">
         <v>6</v>
@@ -7136,22 +7330,22 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C7">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E7">
         <v>10</v>
       </c>
       <c r="F7" s="2">
-        <v>74.40000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="G7" s="2">
-        <v>25.6</v>
+        <v>26.3</v>
       </c>
       <c r="H7">
         <v>5.7</v>
@@ -7168,22 +7362,22 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C8">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D8">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E8">
         <v>9</v>
       </c>
       <c r="F8" s="2">
-        <v>76.90000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="G8" s="2">
-        <v>23.1</v>
+        <v>23.7</v>
       </c>
       <c r="H8">
         <v>6.9</v>
@@ -7197,10 +7391,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -7222,7 +7416,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7231,16 +7425,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -7254,779 +7448,759 @@
         <v>23330051920214</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>23330051920213</v>
+        <v>23330051920226</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>23330051920226</v>
+        <v>23330051920215</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>23330051920215</v>
+        <v>23330051920227</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>23330051920227</v>
+        <v>23330051920237</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>23330051920237</v>
+        <v>23330051920216</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>23330051920216</v>
+        <v>23330051920242</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="D8" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>23330051920242</v>
+        <v>23330051920240</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>23330051920240</v>
+        <v>23330051920244</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>23330051920244</v>
+        <v>23330051920248</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="D11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>23330051920248</v>
+        <v>23330051920250</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>23330051920250</v>
+        <v>23330051920191</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D13" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>23330051920191</v>
+        <v>23330051920333</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>23330051920333</v>
+        <v>23330051920252</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>23330051920252</v>
+        <v>23330051920254</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="D16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>23330051920254</v>
+        <v>23330051920239</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D17" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>23330051920239</v>
+        <v>23330051920328</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D18" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>23330051920328</v>
+        <v>23330051920256</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D19" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>23330051920256</v>
+        <v>23330051920357</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="D20" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>23330051920357</v>
+        <v>23330051920360</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="D21" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>23330051920360</v>
+        <v>23330051920257</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>23330051920257</v>
+        <v>23330051920344</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="D23" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>23330051920344</v>
+        <v>23330051920260</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D24" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>23330051920260</v>
+        <v>23330051920262</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D25" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>23330051920262</v>
+        <v>23330051920330</v>
       </c>
       <c r="B26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="D26" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>23330051920330</v>
+        <v>23330051920266</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="D27" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>23330051920266</v>
+        <v>23330051920269</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>23330051920269</v>
+        <v>23330051920272</v>
       </c>
       <c r="B29" t="s">
         <v>97</v>
       </c>
       <c r="C29" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D29" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>23330051920272</v>
+        <v>23330051920270</v>
       </c>
       <c r="B30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="D30" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>23330051920270</v>
+        <v>23330051920207</v>
       </c>
       <c r="B31" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C31" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D31" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>23330051920207</v>
+        <v>23330051920274</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="D32" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>23330051920274</v>
+        <v>23330051920327</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C33" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>23330051920327</v>
+        <v>23330051920276</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D34" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>23330051920276</v>
+        <v>23330051920275</v>
       </c>
       <c r="B35" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s">
-        <v>88</v>
+        <v>130</v>
       </c>
       <c r="D35" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>23330051920275</v>
+        <v>23330051920278</v>
       </c>
       <c r="B36" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D36" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>23330051920278</v>
+        <v>23330051920277</v>
       </c>
       <c r="B37" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C37" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D37" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>23330051920277</v>
+        <v>23330051920279</v>
       </c>
       <c r="B38" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C38" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="D38" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>23330051920279</v>
+        <v>23330051920280</v>
       </c>
       <c r="B39" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C39" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="D39" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>23330051920280</v>
-      </c>
-      <c r="B40" t="s">
-        <v>109</v>
-      </c>
-      <c r="C40" t="s">
-        <v>91</v>
-      </c>
-      <c r="D40" t="s">
-        <v>173</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -8036,7 +8210,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8045,22 +8219,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -8068,206 +8242,206 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920213</v>
+        <v>23330051920237</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D2" t="s">
         <v>137</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920213</v>
+        <v>23330051920237</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D3" t="s">
         <v>137</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920237</v>
+        <v>23330051920242</v>
       </c>
       <c r="B4" t="s">
         <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920237</v>
+        <v>23330051920242</v>
       </c>
       <c r="B5" t="s">
         <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920242</v>
+        <v>23330051920244</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920242</v>
+        <v>23330051920244</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920244</v>
+        <v>23330051920248</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="D8" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920244</v>
+        <v>23330051920248</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="D9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>65</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920248</v>
+        <v>23330051920254</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
         <v>118</v>
       </c>
       <c r="D10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G10">
         <v>-1</v>
@@ -8275,22 +8449,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920248</v>
+        <v>23330051920254</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
         <v>118</v>
       </c>
       <c r="D11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -8298,22 +8472,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920254</v>
+        <v>23330051920328</v>
       </c>
       <c r="B12" t="s">
         <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D12" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G12">
         <v>-1</v>
@@ -8321,22 +8495,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920254</v>
+        <v>23330051920328</v>
       </c>
       <c r="B13" t="s">
         <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -8344,22 +8518,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920328</v>
+        <v>23330051920357</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G14">
         <v>-1</v>
@@ -8367,22 +8541,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920328</v>
+        <v>23330051920357</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>123</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -8390,22 +8564,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920357</v>
+        <v>23330051920257</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="D16" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G16">
         <v>-1</v>
@@ -8413,22 +8587,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920357</v>
+        <v>23330051920257</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -8436,22 +8610,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920257</v>
+        <v>23330051920344</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="D18" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G18">
         <v>-1</v>
@@ -8459,22 +8633,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920257</v>
+        <v>23330051920344</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="D19" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -8482,22 +8656,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920344</v>
+        <v>23330051920262</v>
       </c>
       <c r="B20" t="s">
         <v>94</v>
       </c>
       <c r="C20" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D20" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G20">
         <v>-1</v>
@@ -8505,22 +8679,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920344</v>
+        <v>23330051920262</v>
       </c>
       <c r="B21" t="s">
         <v>94</v>
       </c>
       <c r="C21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -8528,59 +8702,59 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920262</v>
+        <v>23330051920330</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C22" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="D22" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F22" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920262</v>
+        <v>23330051920330</v>
       </c>
       <c r="B23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="D23" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G23">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920330</v>
+        <v>23330051920270</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D24" t="s">
         <v>161</v>
@@ -8589,7 +8763,7 @@
         <v>7</v>
       </c>
       <c r="F24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G24">
         <v>5</v>
@@ -8597,13 +8771,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920330</v>
+        <v>23330051920270</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D25" t="s">
         <v>161</v>
@@ -8612,7 +8786,7 @@
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G25">
         <v>-1</v>
@@ -8620,160 +8794,160 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920270</v>
+        <v>23330051920207</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D26" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E26" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="G26">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>23330051920270</v>
+        <v>23330051920207</v>
       </c>
       <c r="B27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C27" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D27" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E27" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
         <v>65</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>23330051920207</v>
+        <v>23330051920276</v>
       </c>
       <c r="B28" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C28" t="s">
         <v>86</v>
       </c>
       <c r="D28" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F28" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>23330051920207</v>
+        <v>23330051920276</v>
       </c>
       <c r="B29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C29" t="s">
         <v>86</v>
       </c>
       <c r="D29" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G29">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>23330051920276</v>
+        <v>23330051920275</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C30" t="s">
-        <v>88</v>
+        <v>130</v>
       </c>
       <c r="D30" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E30" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="G30">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>23330051920276</v>
+        <v>23330051920275</v>
       </c>
       <c r="B31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C31" t="s">
-        <v>88</v>
+        <v>130</v>
       </c>
       <c r="D31" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E31" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>23330051920275</v>
+        <v>23330051920227</v>
       </c>
       <c r="B32" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C32" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="D32" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G32">
         <v>-1</v>
@@ -8781,45 +8955,45 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>23330051920275</v>
+        <v>23330051920240</v>
       </c>
       <c r="B33" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="C33" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="D33" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="E33" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G33">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>23330051920227</v>
+        <v>23330051920250</v>
       </c>
       <c r="B34" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C34" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D34" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G34">
         <v>-1</v>
@@ -8827,22 +9001,22 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>23330051920240</v>
+        <v>23330051920333</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C35" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="D35" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G35">
         <v>-1</v>
@@ -8850,22 +9024,22 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>23330051920250</v>
+        <v>23330051920272</v>
       </c>
       <c r="B36" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C36" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="D36" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G36">
         <v>-1</v>
@@ -8873,22 +9047,22 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>23330051920333</v>
+        <v>23330051920327</v>
       </c>
       <c r="B37" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="C37" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D37" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G37">
         <v>-1</v>
@@ -8896,70 +9070,24 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>23330051920272</v>
+        <v>23330051920277</v>
       </c>
       <c r="B38" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C38" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D38" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>23330051920327</v>
-      </c>
-      <c r="B39" t="s">
-        <v>103</v>
-      </c>
-      <c r="C39" t="s">
-        <v>99</v>
-      </c>
-      <c r="D39" t="s">
-        <v>141</v>
-      </c>
-      <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>65</v>
-      </c>
-      <c r="G39">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>23330051920277</v>
-      </c>
-      <c r="B40" t="s">
-        <v>107</v>
-      </c>
-      <c r="C40" t="s">
-        <v>135</v>
-      </c>
-      <c r="D40" t="s">
-        <v>171</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>65</v>
-      </c>
-      <c r="G40">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/1BV - Estadisticos 20231.xlsx
+++ b/grupos/1BV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="128">
   <si>
     <t>Materia</t>
   </si>
@@ -59,6 +59,9 @@
     <t>Nombre</t>
   </si>
   <si>
+    <t>ALCANTARA GUZMAN ANGEL DAVID</t>
+  </si>
+  <si>
     <t>ALVAREZ BAEZ CLAUDIA RUBI</t>
   </si>
   <si>
@@ -212,24 +215,24 @@
     <t>Recursos socioemocionales I</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
     <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -245,289 +248,160 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MOSCOSO</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>ALCANTARA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
+    <t>FERRER</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
     <t>ALVAREZ</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CALVA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>FUENTES</t>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
-    <t>MOSCOSO</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>REAL</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>XICALHUA</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>BERMUDEZ</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>FERRER</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>SOSA</t>
-  </si>
-  <si>
-    <t>DAMIAN</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>CANDELARIO</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>CUAQUEHUA</t>
-  </si>
-  <si>
-    <t>RANGEL</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>VOTTE</t>
-  </si>
-  <si>
     <t>MONTERROSAS</t>
   </si>
   <si>
-    <t>VALERIO</t>
-  </si>
-  <si>
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>CLAUDIA RUBI</t>
-  </si>
-  <si>
     <t>YAMILETH</t>
   </si>
   <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>INGRID ISABEL</t>
+    <t>MIGUEL ENRIQUE</t>
+  </si>
+  <si>
+    <t>GISELA GUADALUPE</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>BRISSIA SINAHI</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
   </si>
   <si>
     <t>VANESA</t>
   </si>
   <si>
-    <t>ANGEL JESUS</t>
+    <t>ANGEL ABRAHAM</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
   </si>
   <si>
     <t>VALERY MIRANDA</t>
   </si>
   <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
     <t>LUZ YESENIA</t>
   </si>
   <si>
-    <t>VIVIANA JOSELIN</t>
-  </si>
-  <si>
-    <t>ANDREA</t>
-  </si>
-  <si>
-    <t>DIEGO DE JESUS</t>
-  </si>
-  <si>
-    <t>SILVANA</t>
-  </si>
-  <si>
-    <t>XIMENA ISABEL</t>
-  </si>
-  <si>
-    <t>MIGUEL ENRIQUE</t>
-  </si>
-  <si>
-    <t>NURIA BELEN</t>
-  </si>
-  <si>
-    <t>GISELA GUADALUPE</t>
-  </si>
-  <si>
-    <t>DANNA PAOLA</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>AXEL GABRIEL</t>
-  </si>
-  <si>
     <t>BRISEIDA</t>
   </si>
   <si>
-    <t>BRISSIA SINAHI</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>JENNIFER</t>
-  </si>
-  <si>
     <t>ANA KAREN</t>
   </si>
   <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>GAEL ARMANDO</t>
-  </si>
-  <si>
-    <t>SAMANTHA BETHANY</t>
-  </si>
-  <si>
     <t>MARIA FERNANDA</t>
   </si>
   <si>
     <t>DORIAN</t>
   </si>
   <si>
-    <t>IASI MILAGROS</t>
-  </si>
-  <si>
     <t>VICTORIA VIANNEY</t>
   </si>
   <si>
     <t>ANEL</t>
   </si>
   <si>
-    <t>OSCAR ALEXANDER</t>
-  </si>
-  <si>
     <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>VIANEY SAMARI</t>
-  </si>
-  <si>
-    <t>ANGEL ABRAHAM</t>
   </si>
 </sst>
 </file>
@@ -889,7 +763,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC41"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -1033,34 +907,34 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4">
         <v>6</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F4">
         <v>5</v>
       </c>
       <c r="G4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>-1</v>
@@ -1096,25 +970,25 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>6</v>
       </c>
       <c r="Z4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA4">
         <v>5</v>
       </c>
       <c r="AB4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1125,31 +999,31 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>-1</v>
@@ -1185,7 +1059,7 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>6</v>
@@ -1194,16 +1068,16 @@
         <v>5</v>
       </c>
       <c r="Z5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC5">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1214,16 +1088,16 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -1232,13 +1106,13 @@
         <v>6</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>-1</v>
@@ -1274,19 +1148,19 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB6">
         <v>5</v>
@@ -1300,34 +1174,34 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7">
         <v>8</v>
       </c>
-      <c r="D7">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>-1</v>
-      </c>
-      <c r="F7">
-        <v>8</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>-1</v>
-      </c>
       <c r="J7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>-1</v>
@@ -1366,22 +1240,22 @@
         <v>7</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y7">
         <v>6</v>
       </c>
       <c r="Z7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB7">
         <v>5</v>
       </c>
       <c r="AC7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1389,34 +1263,34 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8">
         <v>8</v>
       </c>
       <c r="D8">
+        <v>6</v>
+      </c>
+      <c r="E8">
+        <v>7</v>
+      </c>
+      <c r="F8">
         <v>8</v>
       </c>
-      <c r="E8">
-        <v>-1</v>
-      </c>
-      <c r="F8">
-        <v>9</v>
-      </c>
       <c r="G8">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
         <v>-1</v>
@@ -1455,22 +1329,22 @@
         <v>8</v>
       </c>
       <c r="X8">
+        <v>7</v>
+      </c>
+      <c r="Y8">
+        <v>6</v>
+      </c>
+      <c r="Z8">
+        <v>7</v>
+      </c>
+      <c r="AA8">
         <v>8</v>
       </c>
-      <c r="Y8">
-        <v>8</v>
-      </c>
-      <c r="Z8">
-        <v>-1</v>
-      </c>
-      <c r="AA8">
-        <v>9</v>
-      </c>
       <c r="AB8">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1478,19 +1352,19 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9">
         <v>8</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G9">
         <v>9</v>
@@ -1499,13 +1373,13 @@
         <v>6</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
         <v>-1</v>
@@ -1541,19 +1415,19 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X9">
+        <v>7</v>
+      </c>
+      <c r="Y9">
+        <v>7</v>
+      </c>
+      <c r="Z9">
         <v>8</v>
       </c>
-      <c r="Y9">
-        <v>5</v>
-      </c>
-      <c r="Z9">
-        <v>-1</v>
-      </c>
       <c r="AA9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AB9">
         <v>9</v>
@@ -1567,34 +1441,34 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H10">
         <v>6</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>-1</v>
@@ -1630,22 +1504,22 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>5</v>
       </c>
       <c r="Z10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB10">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AC10">
         <v>6</v>
@@ -1656,34 +1530,34 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C11">
+        <v>6</v>
+      </c>
+      <c r="D11">
+        <v>4</v>
+      </c>
+      <c r="E11">
+        <v>5</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+      <c r="H11">
+        <v>6</v>
+      </c>
+      <c r="I11">
         <v>9</v>
       </c>
-      <c r="D11">
-        <v>7</v>
-      </c>
-      <c r="E11">
-        <v>-1</v>
-      </c>
-      <c r="F11">
-        <v>5</v>
-      </c>
-      <c r="G11">
-        <v>10</v>
-      </c>
-      <c r="H11">
-        <v>6</v>
-      </c>
-      <c r="I11">
-        <v>-1</v>
-      </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
         <v>-1</v>
@@ -1722,19 +1596,19 @@
         <v>7</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA11">
         <v>5</v>
       </c>
       <c r="AB11">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC11">
         <v>6</v>
@@ -1748,31 +1622,31 @@
         <v>7</v>
       </c>
       <c r="C12">
+        <v>9</v>
+      </c>
+      <c r="D12">
+        <v>7</v>
+      </c>
+      <c r="E12">
+        <v>6</v>
+      </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
+      <c r="G12">
+        <v>10</v>
+      </c>
+      <c r="H12">
+        <v>6</v>
+      </c>
+      <c r="I12">
+        <v>5</v>
+      </c>
+      <c r="J12">
         <v>8</v>
       </c>
-      <c r="D12">
-        <v>6</v>
-      </c>
-      <c r="E12">
-        <v>-1</v>
-      </c>
-      <c r="F12">
-        <v>6</v>
-      </c>
-      <c r="G12">
-        <v>6</v>
-      </c>
-      <c r="H12">
-        <v>6</v>
-      </c>
-      <c r="I12">
-        <v>-1</v>
-      </c>
-      <c r="J12">
-        <v>-1</v>
-      </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
         <v>-1</v>
@@ -1808,22 +1682,22 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC12">
         <v>6</v>
@@ -1837,31 +1711,31 @@
         <v>7</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D13">
         <v>6</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F13">
+        <v>6</v>
+      </c>
+      <c r="G13">
+        <v>6</v>
+      </c>
+      <c r="H13">
+        <v>6</v>
+      </c>
+      <c r="I13">
+        <v>8</v>
+      </c>
+      <c r="J13">
         <v>9</v>
       </c>
-      <c r="G13">
-        <v>6</v>
-      </c>
-      <c r="H13">
-        <v>6</v>
-      </c>
-      <c r="I13">
-        <v>-1</v>
-      </c>
-      <c r="J13">
-        <v>-1</v>
-      </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1897,19 +1771,19 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>6</v>
       </c>
       <c r="Z13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA13">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AB13">
         <v>6</v>
@@ -1923,34 +1797,34 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <v>6</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H14">
         <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -1986,22 +1860,22 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AB14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC14">
         <v>6</v>
@@ -2012,34 +1886,34 @@
         <v>24</v>
       </c>
       <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+      <c r="D15">
+        <v>6</v>
+      </c>
+      <c r="E15">
+        <v>5</v>
+      </c>
+      <c r="F15">
+        <v>6</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15">
+        <v>6</v>
+      </c>
+      <c r="I15">
         <v>8</v>
       </c>
-      <c r="C15">
-        <v>8</v>
-      </c>
-      <c r="D15">
-        <v>6</v>
-      </c>
-      <c r="E15">
-        <v>-1</v>
-      </c>
-      <c r="F15">
-        <v>9</v>
-      </c>
-      <c r="G15">
-        <v>6</v>
-      </c>
-      <c r="H15">
-        <v>6</v>
-      </c>
-      <c r="I15">
-        <v>-1</v>
-      </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>-1</v>
@@ -2075,22 +1949,22 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AB15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC15">
         <v>6</v>
@@ -2101,34 +1975,34 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
         <v>-1</v>
@@ -2164,25 +2038,25 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA16">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AB16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC16">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2190,34 +2064,34 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <v>-1</v>
@@ -2259,19 +2133,19 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC17">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2279,34 +2153,34 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H18">
         <v>6</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
         <v>-1</v>
@@ -2342,22 +2216,22 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC18">
         <v>6</v>
@@ -2368,19 +2242,19 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C19">
         <v>6</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F19">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -2389,13 +2263,13 @@
         <v>6</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
         <v>-1</v>
@@ -2431,19 +2305,19 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA19">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AB19">
         <v>5</v>
@@ -2460,31 +2334,31 @@
         <v>7</v>
       </c>
       <c r="C20">
+        <v>6</v>
+      </c>
+      <c r="D20">
+        <v>6</v>
+      </c>
+      <c r="E20">
+        <v>7</v>
+      </c>
+      <c r="F20">
         <v>9</v>
       </c>
-      <c r="D20">
-        <v>6</v>
-      </c>
-      <c r="E20">
-        <v>-1</v>
-      </c>
-      <c r="F20">
-        <v>6</v>
-      </c>
       <c r="G20">
+        <v>5</v>
+      </c>
+      <c r="H20">
+        <v>6</v>
+      </c>
+      <c r="I20">
+        <v>5</v>
+      </c>
+      <c r="J20">
         <v>8</v>
       </c>
-      <c r="H20">
-        <v>5</v>
-      </c>
-      <c r="I20">
-        <v>-1</v>
-      </c>
-      <c r="J20">
-        <v>-1</v>
-      </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -2520,25 +2394,25 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X20">
+        <v>7</v>
+      </c>
+      <c r="Y20">
+        <v>5</v>
+      </c>
+      <c r="Z20">
+        <v>7</v>
+      </c>
+      <c r="AA20">
         <v>9</v>
       </c>
-      <c r="Y20">
-        <v>6</v>
-      </c>
-      <c r="Z20">
-        <v>-1</v>
-      </c>
-      <c r="AA20">
-        <v>6</v>
-      </c>
       <c r="AB20">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC20">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2546,34 +2420,34 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C21">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D21">
         <v>6</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G21">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H21">
         <v>5</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>-1</v>
@@ -2609,22 +2483,22 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X21">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB21">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC21">
         <v>5</v>
@@ -2635,34 +2509,34 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G22">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H22">
         <v>5</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
         <v>-1</v>
@@ -2698,22 +2572,22 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB22">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC22">
         <v>5</v>
@@ -2724,34 +2598,34 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F23">
         <v>6</v>
       </c>
       <c r="G23">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H23">
         <v>5</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>-1</v>
@@ -2787,22 +2661,22 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA23">
         <v>6</v>
       </c>
       <c r="AB23">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AC23">
         <v>5</v>
@@ -2813,34 +2687,34 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G24">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L24">
         <v>-1</v>
@@ -2876,25 +2750,25 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB24">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC24">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2905,31 +2779,31 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F25">
         <v>5</v>
       </c>
       <c r="G25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H25">
         <v>6</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
         <v>-1</v>
@@ -2965,22 +2839,22 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>7</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA25">
         <v>5</v>
       </c>
       <c r="AB25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC25">
         <v>6</v>
@@ -2991,19 +2865,19 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C26">
         <v>7</v>
       </c>
       <c r="D26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G26">
         <v>5</v>
@@ -3012,13 +2886,13 @@
         <v>6</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L26">
         <v>-1</v>
@@ -3054,19 +2928,19 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB26">
         <v>5</v>
@@ -3083,31 +2957,31 @@
         <v>7</v>
       </c>
       <c r="C27">
+        <v>7</v>
+      </c>
+      <c r="D27">
+        <v>7</v>
+      </c>
+      <c r="E27">
+        <v>5</v>
+      </c>
+      <c r="F27">
+        <v>6</v>
+      </c>
+      <c r="G27">
+        <v>5</v>
+      </c>
+      <c r="H27">
+        <v>6</v>
+      </c>
+      <c r="I27">
         <v>9</v>
       </c>
-      <c r="D27">
-        <v>6</v>
-      </c>
-      <c r="E27">
-        <v>-1</v>
-      </c>
-      <c r="F27">
-        <v>7</v>
-      </c>
-      <c r="G27">
-        <v>5</v>
-      </c>
-      <c r="H27">
-        <v>6</v>
-      </c>
-      <c r="I27">
-        <v>-1</v>
-      </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
         <v>-1</v>
@@ -3143,19 +3017,19 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB27">
         <v>5</v>
@@ -3169,19 +3043,19 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D28">
         <v>6</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G28">
         <v>5</v>
@@ -3190,13 +3064,13 @@
         <v>6</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L28">
         <v>-1</v>
@@ -3235,16 +3109,16 @@
         <v>5</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB28">
         <v>5</v>
@@ -3258,34 +3132,34 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C29">
+        <v>5</v>
+      </c>
+      <c r="D29">
+        <v>6</v>
+      </c>
+      <c r="E29">
+        <v>5</v>
+      </c>
+      <c r="F29">
+        <v>5</v>
+      </c>
+      <c r="G29">
+        <v>5</v>
+      </c>
+      <c r="H29">
+        <v>6</v>
+      </c>
+      <c r="I29">
         <v>8</v>
       </c>
-      <c r="D29">
-        <v>5</v>
-      </c>
-      <c r="E29">
-        <v>-1</v>
-      </c>
-      <c r="F29">
-        <v>8</v>
-      </c>
-      <c r="G29">
-        <v>7</v>
-      </c>
-      <c r="H29">
-        <v>6</v>
-      </c>
-      <c r="I29">
-        <v>-1</v>
-      </c>
       <c r="J29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
         <v>-1</v>
@@ -3324,19 +3198,19 @@
         <v>7</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA29">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC29">
         <v>6</v>
@@ -3347,34 +3221,34 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C30">
         <v>8</v>
       </c>
       <c r="D30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F30">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
         <v>-1</v>
@@ -3410,25 +3284,25 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X30">
+        <v>7</v>
+      </c>
+      <c r="Y30">
+        <v>5</v>
+      </c>
+      <c r="Z30">
+        <v>9</v>
+      </c>
+      <c r="AA30">
         <v>8</v>
       </c>
-      <c r="Y30">
-        <v>6</v>
-      </c>
-      <c r="Z30">
-        <v>-1</v>
-      </c>
-      <c r="AA30">
-        <v>5</v>
-      </c>
       <c r="AB30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC30">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3436,34 +3310,34 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F31">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L31">
         <v>-1</v>
@@ -3502,22 +3376,22 @@
         <v>7</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>5</v>
       </c>
       <c r="Z31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA31">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC31">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3525,19 +3399,19 @@
         <v>41</v>
       </c>
       <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32">
         <v>9</v>
       </c>
-      <c r="C32">
-        <v>10</v>
-      </c>
       <c r="D32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G32">
         <v>10</v>
@@ -3546,13 +3420,13 @@
         <v>6</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L32">
         <v>-1</v>
@@ -3591,16 +3465,16 @@
         <v>9</v>
       </c>
       <c r="X32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB32">
         <v>10</v>
@@ -3614,34 +3488,34 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D33">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F33">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G33">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H33">
         <v>6</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
         <v>-1</v>
@@ -3677,22 +3551,22 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y33">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA33">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AB33">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC33">
         <v>6</v>
@@ -3703,19 +3577,19 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C34">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D34">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G34">
         <v>5</v>
@@ -3724,13 +3598,13 @@
         <v>6</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L34">
         <v>-1</v>
@@ -3766,19 +3640,19 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB34">
         <v>5</v>
@@ -3795,31 +3669,31 @@
         <v>7</v>
       </c>
       <c r="C35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D35">
         <v>6</v>
       </c>
       <c r="E35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H35">
         <v>6</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L35">
         <v>-1</v>
@@ -3858,19 +3732,19 @@
         <v>7</v>
       </c>
       <c r="X35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y35">
         <v>6</v>
       </c>
       <c r="Z35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC35">
         <v>6</v>
@@ -3881,34 +3755,34 @@
         <v>45</v>
       </c>
       <c r="B36">
+        <v>7</v>
+      </c>
+      <c r="C36">
         <v>8</v>
       </c>
-      <c r="C36">
-        <v>9</v>
-      </c>
       <c r="D36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F36">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G36">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H36">
         <v>6</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L36">
         <v>-1</v>
@@ -3944,22 +3818,22 @@
         <v>-1</v>
       </c>
       <c r="W36">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X36">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y36">
         <v>5</v>
       </c>
       <c r="Z36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA36">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB36">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC36">
         <v>6</v>
@@ -3970,34 +3844,34 @@
         <v>46</v>
       </c>
       <c r="B37">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C37">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D37">
+        <v>5</v>
+      </c>
+      <c r="E37">
+        <v>7</v>
+      </c>
+      <c r="F37">
+        <v>10</v>
+      </c>
+      <c r="G37">
+        <v>10</v>
+      </c>
+      <c r="H37">
+        <v>6</v>
+      </c>
+      <c r="I37">
         <v>8</v>
       </c>
-      <c r="E37">
-        <v>-1</v>
-      </c>
-      <c r="F37">
-        <v>5</v>
-      </c>
-      <c r="G37">
-        <v>6</v>
-      </c>
-      <c r="H37">
-        <v>6</v>
-      </c>
-      <c r="I37">
-        <v>-1</v>
-      </c>
       <c r="J37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L37">
         <v>-1</v>
@@ -4033,22 +3907,22 @@
         <v>-1</v>
       </c>
       <c r="W37">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X37">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y37">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA37">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AB37">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC37">
         <v>6</v>
@@ -4059,19 +3933,19 @@
         <v>47</v>
       </c>
       <c r="B38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C38">
+        <v>6</v>
+      </c>
+      <c r="D38">
         <v>8</v>
       </c>
-      <c r="D38">
-        <v>7</v>
-      </c>
       <c r="E38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G38">
         <v>6</v>
@@ -4080,13 +3954,13 @@
         <v>6</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L38">
         <v>-1</v>
@@ -4125,16 +3999,16 @@
         <v>7</v>
       </c>
       <c r="X38">
+        <v>7</v>
+      </c>
+      <c r="Y38">
+        <v>7</v>
+      </c>
+      <c r="Z38">
         <v>8</v>
       </c>
-      <c r="Y38">
-        <v>7</v>
-      </c>
-      <c r="Z38">
-        <v>-1</v>
-      </c>
       <c r="AA38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB38">
         <v>6</v>
@@ -4148,34 +4022,34 @@
         <v>48</v>
       </c>
       <c r="B39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C39">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D39">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H39">
         <v>6</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L39">
         <v>-1</v>
@@ -4211,22 +4085,22 @@
         <v>-1</v>
       </c>
       <c r="W39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X39">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC39">
         <v>6</v>
@@ -4243,28 +4117,28 @@
         <v>5</v>
       </c>
       <c r="D40">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F40">
         <v>5</v>
       </c>
       <c r="G40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L40">
         <v>-1</v>
@@ -4300,25 +4174,25 @@
         <v>-1</v>
       </c>
       <c r="W40">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA40">
         <v>5</v>
       </c>
       <c r="AB40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC40">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:29">
@@ -4326,34 +4200,34 @@
         <v>50</v>
       </c>
       <c r="B41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D41">
         <v>6</v>
       </c>
       <c r="E41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H41">
         <v>5</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L41">
         <v>-1</v>
@@ -4389,24 +4263,113 @@
         <v>-1</v>
       </c>
       <c r="W41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC41">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:29">
+      <c r="A42" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42">
+        <v>6</v>
+      </c>
+      <c r="C42">
+        <v>7</v>
+      </c>
+      <c r="D42">
+        <v>6</v>
+      </c>
+      <c r="E42">
+        <v>6</v>
+      </c>
+      <c r="F42">
+        <v>6</v>
+      </c>
+      <c r="G42">
+        <v>5</v>
+      </c>
+      <c r="H42">
+        <v>5</v>
+      </c>
+      <c r="I42">
+        <v>10</v>
+      </c>
+      <c r="J42">
+        <v>7</v>
+      </c>
+      <c r="K42">
+        <v>6</v>
+      </c>
+      <c r="L42">
+        <v>-1</v>
+      </c>
+      <c r="M42">
+        <v>-1</v>
+      </c>
+      <c r="N42">
+        <v>-1</v>
+      </c>
+      <c r="O42">
+        <v>-1</v>
+      </c>
+      <c r="P42">
+        <v>-1</v>
+      </c>
+      <c r="Q42">
+        <v>-1</v>
+      </c>
+      <c r="R42">
+        <v>-1</v>
+      </c>
+      <c r="S42">
+        <v>-1</v>
+      </c>
+      <c r="T42">
+        <v>-1</v>
+      </c>
+      <c r="U42">
+        <v>-1</v>
+      </c>
+      <c r="V42">
+        <v>-1</v>
+      </c>
+      <c r="W42">
+        <v>8</v>
+      </c>
+      <c r="X42">
+        <v>7</v>
+      </c>
+      <c r="Y42">
+        <v>6</v>
+      </c>
+      <c r="Z42">
+        <v>6</v>
+      </c>
+      <c r="AA42">
+        <v>6</v>
+      </c>
+      <c r="AB42">
+        <v>5</v>
+      </c>
+      <c r="AC42">
         <v>5</v>
       </c>
     </row>
@@ -4423,7 +4386,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V41"/>
+  <dimension ref="A1:V42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -4432,7 +4395,7 @@
     <row r="1" spans="1:22">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -4441,7 +4404,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -4450,7 +4413,7 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -4540,64 +4503,64 @@
         <v>80</v>
       </c>
       <c r="C4">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="D4">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F4">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G4">
         <v>100</v>
       </c>
       <c r="H4">
-        <v>59.1</v>
+        <v>68.2</v>
       </c>
       <c r="I4">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J4">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="K4">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M4">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N4">
         <v>100</v>
       </c>
       <c r="O4">
-        <v>59.1</v>
+        <v>68.2</v>
       </c>
       <c r="P4">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q4">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="R4">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T4">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U4">
         <v>100</v>
       </c>
       <c r="V4">
-        <v>59.1</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -4608,64 +4571,64 @@
         <v>80</v>
       </c>
       <c r="C5">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="D5">
-        <v>79.2</v>
+        <v>91.7</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F5">
         <v>100</v>
       </c>
       <c r="G5">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>68.2</v>
+        <v>59.1</v>
       </c>
       <c r="I5">
         <v>80</v>
       </c>
       <c r="J5">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="K5">
-        <v>79.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M5">
         <v>100</v>
       </c>
       <c r="N5">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="O5">
-        <v>68.2</v>
+        <v>59.1</v>
       </c>
       <c r="P5">
         <v>80</v>
       </c>
       <c r="Q5">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="R5">
-        <v>79.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T5">
         <v>100</v>
       </c>
       <c r="U5">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="V5">
-        <v>68.2</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -4679,61 +4642,61 @@
         <v>100</v>
       </c>
       <c r="D6">
-        <v>95.8</v>
+        <v>79.2</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F6">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>93.8</v>
       </c>
       <c r="H6">
+        <v>68.2</v>
+      </c>
+      <c r="I6">
+        <v>90</v>
+      </c>
+      <c r="J6">
+        <v>100</v>
+      </c>
+      <c r="K6">
         <v>86.40000000000001</v>
       </c>
-      <c r="I6">
-        <v>80</v>
-      </c>
-      <c r="J6">
-        <v>100</v>
-      </c>
-      <c r="K6">
-        <v>95.8</v>
-      </c>
       <c r="L6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M6">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="N6">
         <v>93.8</v>
       </c>
       <c r="O6">
+        <v>68.2</v>
+      </c>
+      <c r="P6">
+        <v>90</v>
+      </c>
+      <c r="Q6">
+        <v>100</v>
+      </c>
+      <c r="R6">
         <v>86.40000000000001</v>
       </c>
-      <c r="P6">
-        <v>80</v>
-      </c>
-      <c r="Q6">
-        <v>100</v>
-      </c>
-      <c r="R6">
-        <v>95.8</v>
-      </c>
       <c r="S6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T6">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="U6">
         <v>93.8</v>
       </c>
       <c r="V6">
-        <v>86.40000000000001</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -4741,7 +4704,7 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -4750,58 +4713,58 @@
         <v>95.8</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="F7">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G7">
         <v>93.8</v>
       </c>
       <c r="H7">
-        <v>68.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I7">
+        <v>85</v>
+      </c>
+      <c r="J7">
+        <v>100</v>
+      </c>
+      <c r="K7">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="L7">
+        <v>87.5</v>
+      </c>
+      <c r="M7">
         <v>90</v>
-      </c>
-      <c r="J7">
-        <v>100</v>
-      </c>
-      <c r="K7">
-        <v>95.8</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>100</v>
       </c>
       <c r="N7">
         <v>93.8</v>
       </c>
       <c r="O7">
-        <v>68.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="P7">
+        <v>85</v>
+      </c>
+      <c r="Q7">
+        <v>100</v>
+      </c>
+      <c r="R7">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="S7">
+        <v>87.5</v>
+      </c>
+      <c r="T7">
         <v>90</v>
-      </c>
-      <c r="Q7">
-        <v>100</v>
-      </c>
-      <c r="R7">
-        <v>95.8</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>100</v>
       </c>
       <c r="U7">
         <v>93.8</v>
       </c>
       <c r="V7">
-        <v>68.2</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -4809,7 +4772,7 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -4818,58 +4781,58 @@
         <v>95.8</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F8">
         <v>100</v>
       </c>
       <c r="G8">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="H8">
-        <v>81.8</v>
+        <v>68.2</v>
       </c>
       <c r="I8">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J8">
         <v>100</v>
       </c>
       <c r="K8">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M8">
         <v>100</v>
       </c>
       <c r="N8">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="O8">
-        <v>81.8</v>
+        <v>68.2</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q8">
         <v>100</v>
       </c>
       <c r="R8">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T8">
         <v>100</v>
       </c>
       <c r="U8">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V8">
-        <v>81.8</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -4877,16 +4840,16 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C9">
         <v>100</v>
       </c>
       <c r="D9">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9">
         <v>100</v>
@@ -4898,16 +4861,16 @@
         <v>81.8</v>
       </c>
       <c r="I9">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J9">
         <v>100</v>
       </c>
       <c r="K9">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M9">
         <v>100</v>
@@ -4919,16 +4882,16 @@
         <v>81.8</v>
       </c>
       <c r="P9">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q9">
         <v>100</v>
       </c>
       <c r="R9">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T9">
         <v>100</v>
@@ -4945,67 +4908,67 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C10">
         <v>100</v>
       </c>
       <c r="D10">
-        <v>95.8</v>
+        <v>91.7</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F10">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G10">
         <v>100</v>
       </c>
       <c r="H10">
-        <v>72.7</v>
+        <v>81.8</v>
       </c>
       <c r="I10">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="J10">
         <v>100</v>
       </c>
       <c r="K10">
-        <v>95.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="N10">
         <v>100</v>
       </c>
       <c r="O10">
-        <v>72.7</v>
+        <v>81.8</v>
       </c>
       <c r="P10">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="Q10">
         <v>100</v>
       </c>
       <c r="R10">
-        <v>95.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T10">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="U10">
         <v>100</v>
       </c>
       <c r="V10">
-        <v>72.7</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -5013,67 +4976,67 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C11">
         <v>100</v>
       </c>
       <c r="D11">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F11">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G11">
         <v>100</v>
       </c>
       <c r="H11">
-        <v>86.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="I11">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="J11">
         <v>100</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M11">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N11">
         <v>100</v>
       </c>
       <c r="O11">
-        <v>86.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="P11">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="Q11">
         <v>100</v>
       </c>
       <c r="R11">
-        <v>100</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T11">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="U11">
         <v>100</v>
       </c>
       <c r="V11">
-        <v>86.40000000000001</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -5087,10 +5050,10 @@
         <v>100</v>
       </c>
       <c r="D12">
-        <v>91.7</v>
+        <v>100</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F12">
         <v>100</v>
@@ -5099,19 +5062,19 @@
         <v>100</v>
       </c>
       <c r="H12">
-        <v>81.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I12">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J12">
         <v>100</v>
       </c>
       <c r="K12">
-        <v>91.7</v>
+        <v>100</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M12">
         <v>100</v>
@@ -5120,19 +5083,19 @@
         <v>100</v>
       </c>
       <c r="O12">
-        <v>81.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="P12">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="Q12">
         <v>100</v>
       </c>
       <c r="R12">
-        <v>91.7</v>
+        <v>100</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T12">
         <v>100</v>
@@ -5141,7 +5104,7 @@
         <v>100</v>
       </c>
       <c r="V12">
-        <v>81.8</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -5155,10 +5118,10 @@
         <v>100</v>
       </c>
       <c r="D13">
-        <v>95.8</v>
+        <v>91.7</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F13">
         <v>100</v>
@@ -5176,10 +5139,10 @@
         <v>100</v>
       </c>
       <c r="K13">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M13">
         <v>100</v>
@@ -5197,10 +5160,10 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T13">
         <v>100</v>
@@ -5217,19 +5180,19 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C14">
         <v>100</v>
       </c>
       <c r="D14">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G14">
         <v>100</v>
@@ -5238,19 +5201,19 @@
         <v>81.8</v>
       </c>
       <c r="I14">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="J14">
         <v>100</v>
       </c>
       <c r="K14">
-        <v>91.7</v>
+        <v>93.2</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M14">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="N14">
         <v>100</v>
@@ -5259,19 +5222,19 @@
         <v>81.8</v>
       </c>
       <c r="P14">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="Q14">
         <v>100</v>
       </c>
       <c r="R14">
-        <v>91.7</v>
+        <v>93.2</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T14">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="U14">
         <v>100</v>
@@ -5285,7 +5248,7 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -5294,58 +5257,58 @@
         <v>91.7</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F15">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G15">
         <v>100</v>
       </c>
       <c r="H15">
-        <v>90.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="I15">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="J15">
         <v>100</v>
       </c>
       <c r="K15">
-        <v>91.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M15">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N15">
         <v>100</v>
       </c>
       <c r="O15">
-        <v>90.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="P15">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="Q15">
         <v>100</v>
       </c>
       <c r="R15">
-        <v>91.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="T15">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="U15">
         <v>100</v>
       </c>
       <c r="V15">
-        <v>90.90000000000001</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -5353,7 +5316,7 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -5362,7 +5325,7 @@
         <v>91.7</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16">
         <v>100</v>
@@ -5371,19 +5334,19 @@
         <v>100</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I16">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J16">
         <v>100</v>
       </c>
       <c r="K16">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M16">
         <v>100</v>
@@ -5392,19 +5355,19 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P16">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q16">
         <v>100</v>
       </c>
       <c r="R16">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T16">
         <v>100</v>
@@ -5413,7 +5376,7 @@
         <v>100</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -5430,16 +5393,16 @@
         <v>91.7</v>
       </c>
       <c r="E17">
+        <v>100</v>
+      </c>
+      <c r="F17">
+        <v>100</v>
+      </c>
+      <c r="G17">
+        <v>100</v>
+      </c>
+      <c r="H17">
         <v>0</v>
-      </c>
-      <c r="F17">
-        <v>100</v>
-      </c>
-      <c r="G17">
-        <v>100</v>
-      </c>
-      <c r="H17">
-        <v>77.3</v>
       </c>
       <c r="I17">
         <v>80</v>
@@ -5448,19 +5411,19 @@
         <v>100</v>
       </c>
       <c r="K17">
-        <v>91.7</v>
+        <v>79.5</v>
       </c>
       <c r="L17">
+        <v>100</v>
+      </c>
+      <c r="M17">
+        <v>100</v>
+      </c>
+      <c r="N17">
+        <v>100</v>
+      </c>
+      <c r="O17">
         <v>0</v>
-      </c>
-      <c r="M17">
-        <v>100</v>
-      </c>
-      <c r="N17">
-        <v>100</v>
-      </c>
-      <c r="O17">
-        <v>77.3</v>
       </c>
       <c r="P17">
         <v>80</v>
@@ -5469,19 +5432,19 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>91.7</v>
+        <v>79.5</v>
       </c>
       <c r="S17">
+        <v>100</v>
+      </c>
+      <c r="T17">
+        <v>100</v>
+      </c>
+      <c r="U17">
+        <v>100</v>
+      </c>
+      <c r="V17">
         <v>0</v>
-      </c>
-      <c r="T17">
-        <v>100</v>
-      </c>
-      <c r="U17">
-        <v>100</v>
-      </c>
-      <c r="V17">
-        <v>77.3</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -5495,10 +5458,10 @@
         <v>100</v>
       </c>
       <c r="D18">
-        <v>95.8</v>
+        <v>91.7</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18">
         <v>100</v>
@@ -5507,19 +5470,19 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>68.2</v>
+        <v>77.3</v>
       </c>
       <c r="I18">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J18">
         <v>100</v>
       </c>
       <c r="K18">
-        <v>95.8</v>
+        <v>93.2</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M18">
         <v>100</v>
@@ -5528,19 +5491,19 @@
         <v>100</v>
       </c>
       <c r="O18">
-        <v>68.2</v>
+        <v>77.3</v>
       </c>
       <c r="P18">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q18">
         <v>100</v>
       </c>
       <c r="R18">
-        <v>95.8</v>
+        <v>93.2</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T18">
         <v>100</v>
@@ -5549,7 +5512,7 @@
         <v>100</v>
       </c>
       <c r="V18">
-        <v>68.2</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -5557,7 +5520,7 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -5566,16 +5529,16 @@
         <v>95.8</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F19">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G19">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="H19">
-        <v>81.8</v>
+        <v>68.2</v>
       </c>
       <c r="I19">
         <v>90</v>
@@ -5584,19 +5547,19 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M19">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="N19">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="O19">
-        <v>81.8</v>
+        <v>68.2</v>
       </c>
       <c r="P19">
         <v>90</v>
@@ -5605,19 +5568,19 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T19">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="U19">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="V19">
-        <v>81.8</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -5631,61 +5594,61 @@
         <v>100</v>
       </c>
       <c r="D20">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="F20">
+        <v>90</v>
+      </c>
+      <c r="G20">
+        <v>87.5</v>
+      </c>
+      <c r="H20">
+        <v>81.8</v>
+      </c>
+      <c r="I20">
         <v>80</v>
       </c>
-      <c r="G20">
-        <v>100</v>
-      </c>
-      <c r="H20">
-        <v>68.2</v>
-      </c>
-      <c r="I20">
+      <c r="J20">
+        <v>100</v>
+      </c>
+      <c r="K20">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="L20">
+        <v>93.8</v>
+      </c>
+      <c r="M20">
         <v>90</v>
       </c>
-      <c r="J20">
-        <v>100</v>
-      </c>
-      <c r="K20">
-        <v>91.7</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
+      <c r="N20">
+        <v>87.5</v>
+      </c>
+      <c r="O20">
+        <v>81.8</v>
+      </c>
+      <c r="P20">
         <v>80</v>
       </c>
-      <c r="N20">
-        <v>100</v>
-      </c>
-      <c r="O20">
-        <v>68.2</v>
-      </c>
-      <c r="P20">
+      <c r="Q20">
+        <v>100</v>
+      </c>
+      <c r="R20">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="S20">
+        <v>93.8</v>
+      </c>
+      <c r="T20">
         <v>90</v>
       </c>
-      <c r="Q20">
-        <v>100</v>
-      </c>
-      <c r="R20">
-        <v>91.7</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>80</v>
-      </c>
       <c r="U20">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="V20">
-        <v>68.2</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -5693,67 +5656,67 @@
         <v>30</v>
       </c>
       <c r="B21">
+        <v>90</v>
+      </c>
+      <c r="C21">
+        <v>100</v>
+      </c>
+      <c r="D21">
+        <v>91.7</v>
+      </c>
+      <c r="E21">
+        <v>87.5</v>
+      </c>
+      <c r="F21">
         <v>80</v>
       </c>
-      <c r="C21">
-        <v>100</v>
-      </c>
-      <c r="D21">
-        <v>95.8</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>100</v>
-      </c>
       <c r="G21">
+        <v>100</v>
+      </c>
+      <c r="H21">
+        <v>68.2</v>
+      </c>
+      <c r="I21">
+        <v>95</v>
+      </c>
+      <c r="J21">
+        <v>100</v>
+      </c>
+      <c r="K21">
+        <v>93.2</v>
+      </c>
+      <c r="L21">
         <v>87.5</v>
       </c>
-      <c r="H21">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="I21">
+      <c r="M21">
         <v>80</v>
       </c>
-      <c r="J21">
-        <v>100</v>
-      </c>
-      <c r="K21">
-        <v>95.8</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>100</v>
-      </c>
       <c r="N21">
+        <v>100</v>
+      </c>
+      <c r="O21">
+        <v>68.2</v>
+      </c>
+      <c r="P21">
+        <v>95</v>
+      </c>
+      <c r="Q21">
+        <v>100</v>
+      </c>
+      <c r="R21">
+        <v>93.2</v>
+      </c>
+      <c r="S21">
         <v>87.5</v>
       </c>
-      <c r="O21">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="P21">
+      <c r="T21">
         <v>80</v>
       </c>
-      <c r="Q21">
-        <v>100</v>
-      </c>
-      <c r="R21">
-        <v>95.8</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>100</v>
-      </c>
       <c r="U21">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="V21">
-        <v>86.40000000000001</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -5767,19 +5730,19 @@
         <v>100</v>
       </c>
       <c r="D22">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22">
         <v>100</v>
       </c>
       <c r="G22">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="H22">
-        <v>81.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I22">
         <v>80</v>
@@ -5788,19 +5751,19 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>91.7</v>
+        <v>93.2</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22">
         <v>100</v>
       </c>
       <c r="N22">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="O22">
-        <v>81.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="P22">
         <v>80</v>
@@ -5809,19 +5772,19 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>91.7</v>
+        <v>93.2</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T22">
         <v>100</v>
       </c>
       <c r="U22">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="V22">
-        <v>81.8</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -5835,61 +5798,61 @@
         <v>100</v>
       </c>
       <c r="D23">
-        <v>83.3</v>
+        <v>91.7</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F23">
         <v>100</v>
       </c>
       <c r="G23">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="H23">
-        <v>36.4</v>
+        <v>81.8</v>
       </c>
       <c r="I23">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J23">
         <v>100</v>
       </c>
       <c r="K23">
-        <v>83.3</v>
+        <v>93.2</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M23">
         <v>100</v>
       </c>
       <c r="N23">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="O23">
-        <v>36.4</v>
+        <v>81.8</v>
       </c>
       <c r="P23">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q23">
         <v>100</v>
       </c>
       <c r="R23">
-        <v>83.3</v>
+        <v>93.2</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T23">
         <v>100</v>
       </c>
       <c r="U23">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="V23">
-        <v>36.4</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -5903,61 +5866,61 @@
         <v>100</v>
       </c>
       <c r="D24">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F24">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G24">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="H24">
-        <v>81.8</v>
+        <v>36.4</v>
       </c>
       <c r="I24">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J24">
         <v>100</v>
       </c>
       <c r="K24">
-        <v>100</v>
+        <v>45.5</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="M24">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="N24">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="O24">
-        <v>81.8</v>
+        <v>36.4</v>
       </c>
       <c r="P24">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q24">
         <v>100</v>
       </c>
       <c r="R24">
-        <v>100</v>
+        <v>45.5</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="T24">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="U24">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V24">
-        <v>81.8</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -5971,61 +5934,61 @@
         <v>100</v>
       </c>
       <c r="D25">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F25">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G25">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="H25">
-        <v>86.40000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="I25">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J25">
         <v>100</v>
       </c>
       <c r="K25">
-        <v>95.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M25">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N25">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="O25">
-        <v>86.40000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="P25">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q25">
         <v>100</v>
       </c>
       <c r="R25">
-        <v>95.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T25">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U25">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="V25">
-        <v>86.40000000000001</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -6033,25 +5996,25 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C26">
         <v>100</v>
       </c>
       <c r="D26">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F26">
         <v>100</v>
       </c>
       <c r="G26">
-        <v>31.3</v>
+        <v>93.8</v>
       </c>
       <c r="H26">
-        <v>72.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I26">
         <v>90</v>
@@ -6060,19 +6023,19 @@
         <v>100</v>
       </c>
       <c r="K26">
-        <v>91.7</v>
+        <v>93.2</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M26">
         <v>100</v>
       </c>
       <c r="N26">
-        <v>31.3</v>
+        <v>93.8</v>
       </c>
       <c r="O26">
-        <v>72.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="P26">
         <v>90</v>
@@ -6081,19 +6044,19 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>91.7</v>
+        <v>93.2</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T26">
         <v>100</v>
       </c>
       <c r="U26">
-        <v>31.3</v>
+        <v>93.8</v>
       </c>
       <c r="V26">
-        <v>72.7</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -6107,19 +6070,19 @@
         <v>100</v>
       </c>
       <c r="D27">
-        <v>95.8</v>
+        <v>91.7</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F27">
         <v>100</v>
       </c>
       <c r="G27">
-        <v>93.8</v>
+        <v>31.3</v>
       </c>
       <c r="H27">
-        <v>81.8</v>
+        <v>72.7</v>
       </c>
       <c r="I27">
         <v>90</v>
@@ -6128,19 +6091,19 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>95.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27">
         <v>100</v>
       </c>
       <c r="N27">
-        <v>93.8</v>
+        <v>31.3</v>
       </c>
       <c r="O27">
-        <v>81.8</v>
+        <v>72.7</v>
       </c>
       <c r="P27">
         <v>90</v>
@@ -6149,19 +6112,19 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>95.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T27">
         <v>100</v>
       </c>
       <c r="U27">
-        <v>93.8</v>
+        <v>31.3</v>
       </c>
       <c r="V27">
-        <v>81.8</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -6169,67 +6132,67 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C28">
         <v>100</v>
       </c>
       <c r="D28">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F28">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G28">
         <v>93.8</v>
       </c>
       <c r="H28">
-        <v>100</v>
+        <v>81.8</v>
       </c>
       <c r="I28">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="J28">
         <v>100</v>
       </c>
       <c r="K28">
-        <v>91.7</v>
+        <v>52.3</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M28">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="N28">
         <v>93.8</v>
       </c>
       <c r="O28">
-        <v>100</v>
+        <v>81.8</v>
       </c>
       <c r="P28">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="Q28">
         <v>100</v>
       </c>
       <c r="R28">
-        <v>91.7</v>
+        <v>52.3</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T28">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="U28">
         <v>93.8</v>
       </c>
       <c r="V28">
-        <v>100</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -6237,7 +6200,7 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C29">
         <v>100</v>
@@ -6246,16 +6209,16 @@
         <v>91.7</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F29">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G29">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="H29">
-        <v>81.8</v>
+        <v>100</v>
       </c>
       <c r="I29">
         <v>90</v>
@@ -6264,19 +6227,19 @@
         <v>100</v>
       </c>
       <c r="K29">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M29">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N29">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="O29">
-        <v>81.8</v>
+        <v>100</v>
       </c>
       <c r="P29">
         <v>90</v>
@@ -6285,19 +6248,19 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T29">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U29">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V29">
-        <v>81.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -6305,16 +6268,16 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C30">
         <v>100</v>
       </c>
       <c r="D30">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F30">
         <v>100</v>
@@ -6326,16 +6289,16 @@
         <v>81.8</v>
       </c>
       <c r="I30">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="J30">
         <v>100</v>
       </c>
       <c r="K30">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M30">
         <v>100</v>
@@ -6347,16 +6310,16 @@
         <v>81.8</v>
       </c>
       <c r="P30">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="Q30">
         <v>100</v>
       </c>
       <c r="R30">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T30">
         <v>100</v>
@@ -6373,16 +6336,16 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C31">
         <v>100</v>
       </c>
       <c r="D31">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F31">
         <v>100</v>
@@ -6394,16 +6357,16 @@
         <v>81.8</v>
       </c>
       <c r="I31">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J31">
         <v>100</v>
       </c>
       <c r="K31">
-        <v>95.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M31">
         <v>100</v>
@@ -6415,16 +6378,16 @@
         <v>81.8</v>
       </c>
       <c r="P31">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="Q31">
         <v>100</v>
       </c>
       <c r="R31">
-        <v>95.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T31">
         <v>100</v>
@@ -6441,16 +6404,16 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C32">
         <v>100</v>
       </c>
       <c r="D32">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F32">
         <v>100</v>
@@ -6462,16 +6425,16 @@
         <v>81.8</v>
       </c>
       <c r="I32">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J32">
         <v>100</v>
       </c>
       <c r="K32">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M32">
         <v>100</v>
@@ -6483,16 +6446,16 @@
         <v>81.8</v>
       </c>
       <c r="P32">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q32">
         <v>100</v>
       </c>
       <c r="R32">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T32">
         <v>100</v>
@@ -6509,64 +6472,64 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C33">
         <v>100</v>
       </c>
       <c r="D33">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F33">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G33">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="H33">
         <v>81.8</v>
       </c>
       <c r="I33">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J33">
         <v>100</v>
       </c>
       <c r="K33">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M33">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="N33">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="O33">
         <v>81.8</v>
       </c>
       <c r="P33">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q33">
         <v>100</v>
       </c>
       <c r="R33">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T33">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="U33">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="V33">
         <v>81.8</v>
@@ -6577,67 +6540,67 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C34">
         <v>100</v>
       </c>
       <c r="D34">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="F34">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G34">
         <v>93.8</v>
       </c>
       <c r="H34">
-        <v>90.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="I34">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="J34">
         <v>100</v>
       </c>
       <c r="K34">
-        <v>100</v>
+        <v>72.7</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="M34">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N34">
         <v>93.8</v>
       </c>
       <c r="O34">
-        <v>90.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="P34">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="Q34">
         <v>100</v>
       </c>
       <c r="R34">
-        <v>100</v>
+        <v>72.7</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="T34">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="U34">
         <v>93.8</v>
       </c>
       <c r="V34">
-        <v>90.90000000000001</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -6651,61 +6614,61 @@
         <v>100</v>
       </c>
       <c r="D35">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F35">
         <v>100</v>
       </c>
       <c r="G35">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="H35">
-        <v>81.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I35">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="J35">
         <v>100</v>
       </c>
       <c r="K35">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M35">
         <v>100</v>
       </c>
       <c r="N35">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="O35">
-        <v>81.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P35">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="Q35">
         <v>100</v>
       </c>
       <c r="R35">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T35">
         <v>100</v>
       </c>
       <c r="U35">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V35">
-        <v>81.8</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -6713,7 +6676,7 @@
         <v>45</v>
       </c>
       <c r="B36">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C36">
         <v>100</v>
@@ -6722,7 +6685,7 @@
         <v>95.8</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F36">
         <v>100</v>
@@ -6734,16 +6697,16 @@
         <v>81.8</v>
       </c>
       <c r="I36">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="J36">
         <v>100</v>
       </c>
       <c r="K36">
-        <v>95.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M36">
         <v>100</v>
@@ -6755,16 +6718,16 @@
         <v>81.8</v>
       </c>
       <c r="P36">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="Q36">
         <v>100</v>
       </c>
       <c r="R36">
-        <v>95.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T36">
         <v>100</v>
@@ -6781,7 +6744,7 @@
         <v>46</v>
       </c>
       <c r="B37">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C37">
         <v>100</v>
@@ -6790,10 +6753,10 @@
         <v>95.8</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F37">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G37">
         <v>100</v>
@@ -6802,19 +6765,19 @@
         <v>81.8</v>
       </c>
       <c r="I37">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="J37">
         <v>100</v>
       </c>
       <c r="K37">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M37">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="N37">
         <v>100</v>
@@ -6823,19 +6786,19 @@
         <v>81.8</v>
       </c>
       <c r="P37">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="Q37">
         <v>100</v>
       </c>
       <c r="R37">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T37">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="U37">
         <v>100</v>
@@ -6849,19 +6812,19 @@
         <v>47</v>
       </c>
       <c r="B38">
+        <v>80</v>
+      </c>
+      <c r="C38">
+        <v>100</v>
+      </c>
+      <c r="D38">
+        <v>95.8</v>
+      </c>
+      <c r="E38">
+        <v>100</v>
+      </c>
+      <c r="F38">
         <v>90</v>
-      </c>
-      <c r="C38">
-        <v>100</v>
-      </c>
-      <c r="D38">
-        <v>100</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-      <c r="F38">
-        <v>100</v>
       </c>
       <c r="G38">
         <v>100</v>
@@ -6876,13 +6839,13 @@
         <v>100</v>
       </c>
       <c r="K38">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M38">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N38">
         <v>100</v>
@@ -6897,13 +6860,13 @@
         <v>100</v>
       </c>
       <c r="R38">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T38">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U38">
         <v>100</v>
@@ -6917,67 +6880,67 @@
         <v>48</v>
       </c>
       <c r="B39">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C39">
         <v>100</v>
       </c>
       <c r="D39">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F39">
         <v>100</v>
       </c>
       <c r="G39">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="H39">
-        <v>90.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="I39">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="J39">
         <v>100</v>
       </c>
       <c r="K39">
-        <v>95.8</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M39">
         <v>100</v>
       </c>
       <c r="N39">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="O39">
-        <v>90.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="P39">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="Q39">
         <v>100</v>
       </c>
       <c r="R39">
-        <v>95.8</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T39">
         <v>100</v>
       </c>
       <c r="U39">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="V39">
-        <v>90.90000000000001</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -6991,61 +6954,61 @@
         <v>100</v>
       </c>
       <c r="D40">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F40">
+        <v>100</v>
+      </c>
+      <c r="G40">
+        <v>93.8</v>
+      </c>
+      <c r="H40">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="I40">
         <v>90</v>
       </c>
-      <c r="G40">
-        <v>100</v>
-      </c>
-      <c r="H40">
-        <v>77.3</v>
-      </c>
-      <c r="I40">
-        <v>80</v>
-      </c>
       <c r="J40">
         <v>100</v>
       </c>
       <c r="K40">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M40">
+        <v>100</v>
+      </c>
+      <c r="N40">
+        <v>93.8</v>
+      </c>
+      <c r="O40">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="P40">
         <v>90</v>
       </c>
-      <c r="N40">
-        <v>100</v>
-      </c>
-      <c r="O40">
-        <v>77.3</v>
-      </c>
-      <c r="P40">
-        <v>80</v>
-      </c>
       <c r="Q40">
         <v>100</v>
       </c>
       <c r="R40">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T40">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="U40">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V40">
-        <v>77.3</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -7062,57 +7025,125 @@
         <v>100</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F41">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G41">
+        <v>100</v>
+      </c>
+      <c r="H41">
+        <v>77.3</v>
+      </c>
+      <c r="I41">
+        <v>75</v>
+      </c>
+      <c r="J41">
+        <v>100</v>
+      </c>
+      <c r="K41">
+        <v>79.5</v>
+      </c>
+      <c r="L41">
+        <v>100</v>
+      </c>
+      <c r="M41">
+        <v>90</v>
+      </c>
+      <c r="N41">
+        <v>100</v>
+      </c>
+      <c r="O41">
+        <v>77.3</v>
+      </c>
+      <c r="P41">
+        <v>75</v>
+      </c>
+      <c r="Q41">
+        <v>100</v>
+      </c>
+      <c r="R41">
+        <v>79.5</v>
+      </c>
+      <c r="S41">
+        <v>100</v>
+      </c>
+      <c r="T41">
+        <v>90</v>
+      </c>
+      <c r="U41">
+        <v>100</v>
+      </c>
+      <c r="V41">
+        <v>77.3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22">
+      <c r="A42" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42">
+        <v>80</v>
+      </c>
+      <c r="C42">
+        <v>100</v>
+      </c>
+      <c r="D42">
+        <v>100</v>
+      </c>
+      <c r="E42">
+        <v>100</v>
+      </c>
+      <c r="F42">
+        <v>100</v>
+      </c>
+      <c r="G42">
         <v>93.8</v>
       </c>
-      <c r="H41">
+      <c r="H42">
         <v>72.7</v>
       </c>
-      <c r="I41">
-        <v>80</v>
-      </c>
-      <c r="J41">
-        <v>100</v>
-      </c>
-      <c r="K41">
-        <v>100</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <v>100</v>
-      </c>
-      <c r="N41">
+      <c r="I42">
+        <v>90</v>
+      </c>
+      <c r="J42">
+        <v>100</v>
+      </c>
+      <c r="K42">
+        <v>100</v>
+      </c>
+      <c r="L42">
+        <v>100</v>
+      </c>
+      <c r="M42">
+        <v>100</v>
+      </c>
+      <c r="N42">
         <v>93.8</v>
       </c>
-      <c r="O41">
+      <c r="O42">
         <v>72.7</v>
       </c>
-      <c r="P41">
-        <v>80</v>
-      </c>
-      <c r="Q41">
-        <v>100</v>
-      </c>
-      <c r="R41">
-        <v>100</v>
-      </c>
-      <c r="S41">
-        <v>0</v>
-      </c>
-      <c r="T41">
-        <v>100</v>
-      </c>
-      <c r="U41">
+      <c r="P42">
+        <v>90</v>
+      </c>
+      <c r="Q42">
+        <v>100</v>
+      </c>
+      <c r="R42">
+        <v>100</v>
+      </c>
+      <c r="S42">
+        <v>100</v>
+      </c>
+      <c r="T42">
+        <v>100</v>
+      </c>
+      <c r="U42">
         <v>93.8</v>
       </c>
-      <c r="V41">
+      <c r="V42">
         <v>72.7</v>
       </c>
     </row>
@@ -7141,60 +7172,63 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2">
+        <v>19</v>
+      </c>
+      <c r="E2">
+        <v>20</v>
+      </c>
+      <c r="F2" s="2">
+        <v>48.7</v>
+      </c>
+      <c r="G2" s="2">
+        <v>51.3</v>
+      </c>
+      <c r="H2">
+        <v>5.7</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2" s="2">
         <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>38</v>
-      </c>
-      <c r="J2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -7202,22 +7236,22 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3">
         <v>18</v>
       </c>
       <c r="F3" s="2">
-        <v>52.6</v>
+        <v>53.8</v>
       </c>
       <c r="G3" s="2">
-        <v>47.4</v>
+        <v>46.2</v>
       </c>
       <c r="H3">
         <v>6.4</v>
@@ -7231,25 +7265,25 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4">
         <v>23</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" s="2">
-        <v>60.5</v>
+        <v>59</v>
       </c>
       <c r="G4" s="2">
-        <v>39.5</v>
+        <v>41</v>
       </c>
       <c r="H4">
         <v>6.3</v>
@@ -7263,25 +7297,25 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C5">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F5" s="2">
-        <v>68.40000000000001</v>
+        <v>59</v>
       </c>
       <c r="G5" s="2">
-        <v>31.6</v>
+        <v>41</v>
       </c>
       <c r="H5">
         <v>6.3</v>
@@ -7295,28 +7329,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F6" s="2">
-        <v>71.09999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>28.9</v>
+        <v>25.6</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7327,28 +7361,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2">
-        <v>73.7</v>
+        <v>87.2</v>
       </c>
       <c r="G7" s="2">
-        <v>26.3</v>
+        <v>12.8</v>
       </c>
       <c r="H7">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7362,25 +7396,25 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E8">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2">
-        <v>76.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="G8" s="2">
-        <v>23.7</v>
+        <v>5.1</v>
       </c>
       <c r="H8">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7391,7 +7425,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B9" t="s">
         <v>69</v>
@@ -7416,7 +7450,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7425,782 +7459,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>23330051920214</v>
-      </c>
-      <c r="B2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D2" t="s">
-        <v>133</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>23330051920226</v>
-      </c>
-      <c r="B3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>23330051920215</v>
-      </c>
-      <c r="B4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>23330051920227</v>
-      </c>
-      <c r="B5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>23330051920237</v>
-      </c>
-      <c r="B6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>23330051920216</v>
-      </c>
-      <c r="B7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D7" t="s">
-        <v>138</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>23330051920242</v>
-      </c>
-      <c r="B8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" t="s">
-        <v>113</v>
-      </c>
-      <c r="D8" t="s">
-        <v>139</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>23330051920240</v>
-      </c>
-      <c r="B9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" t="s">
-        <v>114</v>
-      </c>
-      <c r="D9" t="s">
-        <v>140</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>23330051920244</v>
-      </c>
-      <c r="B10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D10" t="s">
-        <v>141</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>23330051920248</v>
-      </c>
-      <c r="B11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D11" t="s">
-        <v>142</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>23330051920250</v>
-      </c>
-      <c r="B12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" t="s">
-        <v>116</v>
-      </c>
-      <c r="D12" t="s">
-        <v>143</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>23330051920191</v>
-      </c>
-      <c r="B13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D13" t="s">
-        <v>144</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>23330051920333</v>
-      </c>
-      <c r="B14" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" t="s">
-        <v>90</v>
-      </c>
-      <c r="D14" t="s">
-        <v>145</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>23330051920252</v>
-      </c>
-      <c r="B15" t="s">
-        <v>86</v>
-      </c>
-      <c r="C15" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" t="s">
-        <v>146</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>23330051920254</v>
-      </c>
-      <c r="B16" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" t="s">
-        <v>118</v>
-      </c>
-      <c r="D16" t="s">
-        <v>147</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>23330051920239</v>
-      </c>
-      <c r="B17" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" t="s">
-        <v>119</v>
-      </c>
-      <c r="D17" t="s">
-        <v>148</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>23330051920328</v>
-      </c>
-      <c r="B18" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" t="s">
-        <v>120</v>
-      </c>
-      <c r="D18" t="s">
-        <v>149</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>23330051920256</v>
-      </c>
-      <c r="B19" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" t="s">
-        <v>121</v>
-      </c>
-      <c r="D19" t="s">
-        <v>150</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>23330051920357</v>
-      </c>
-      <c r="B20" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" t="s">
-        <v>85</v>
-      </c>
-      <c r="D20" t="s">
-        <v>151</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>23330051920360</v>
-      </c>
-      <c r="B21" t="s">
-        <v>90</v>
-      </c>
-      <c r="C21" t="s">
-        <v>122</v>
-      </c>
-      <c r="D21" t="s">
-        <v>152</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>23330051920257</v>
-      </c>
-      <c r="B22" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" t="s">
-        <v>75</v>
-      </c>
-      <c r="D22" t="s">
-        <v>153</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>23330051920344</v>
-      </c>
-      <c r="B23" t="s">
-        <v>92</v>
-      </c>
-      <c r="C23" t="s">
-        <v>123</v>
-      </c>
-      <c r="D23" t="s">
-        <v>154</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>23330051920260</v>
-      </c>
-      <c r="B24" t="s">
-        <v>93</v>
-      </c>
-      <c r="C24" t="s">
-        <v>124</v>
-      </c>
-      <c r="D24" t="s">
-        <v>155</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>23330051920262</v>
-      </c>
-      <c r="B25" t="s">
-        <v>94</v>
-      </c>
-      <c r="C25" t="s">
-        <v>125</v>
-      </c>
-      <c r="D25" t="s">
-        <v>156</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>23330051920330</v>
-      </c>
-      <c r="B26" t="s">
-        <v>95</v>
-      </c>
-      <c r="C26" t="s">
-        <v>86</v>
-      </c>
-      <c r="D26" t="s">
-        <v>157</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>23330051920266</v>
-      </c>
-      <c r="B27" t="s">
-        <v>96</v>
-      </c>
-      <c r="C27" t="s">
-        <v>126</v>
-      </c>
-      <c r="D27" t="s">
-        <v>158</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>23330051920269</v>
-      </c>
-      <c r="B28" t="s">
-        <v>95</v>
-      </c>
-      <c r="C28" t="s">
-        <v>127</v>
-      </c>
-      <c r="D28" t="s">
-        <v>159</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>23330051920272</v>
-      </c>
-      <c r="B29" t="s">
-        <v>97</v>
-      </c>
-      <c r="C29" t="s">
-        <v>128</v>
-      </c>
-      <c r="D29" t="s">
-        <v>160</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>23330051920270</v>
-      </c>
-      <c r="B30" t="s">
-        <v>98</v>
-      </c>
-      <c r="C30" t="s">
-        <v>85</v>
-      </c>
-      <c r="D30" t="s">
-        <v>161</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>23330051920207</v>
-      </c>
-      <c r="B31" t="s">
-        <v>99</v>
-      </c>
-      <c r="C31" t="s">
-        <v>84</v>
-      </c>
-      <c r="D31" t="s">
-        <v>162</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>23330051920274</v>
-      </c>
-      <c r="B32" t="s">
-        <v>100</v>
-      </c>
-      <c r="C32" t="s">
-        <v>129</v>
-      </c>
-      <c r="D32" t="s">
-        <v>163</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>23330051920327</v>
-      </c>
-      <c r="B33" t="s">
-        <v>101</v>
-      </c>
-      <c r="C33" t="s">
-        <v>97</v>
-      </c>
-      <c r="D33" t="s">
-        <v>137</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>23330051920276</v>
-      </c>
-      <c r="B34" t="s">
-        <v>102</v>
-      </c>
-      <c r="C34" t="s">
-        <v>86</v>
-      </c>
-      <c r="D34" t="s">
-        <v>164</v>
-      </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>23330051920275</v>
-      </c>
-      <c r="B35" t="s">
-        <v>103</v>
-      </c>
-      <c r="C35" t="s">
-        <v>130</v>
-      </c>
-      <c r="D35" t="s">
-        <v>165</v>
-      </c>
-      <c r="E35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>23330051920278</v>
-      </c>
-      <c r="B36" t="s">
-        <v>104</v>
-      </c>
-      <c r="C36" t="s">
-        <v>131</v>
-      </c>
-      <c r="D36" t="s">
-        <v>166</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>23330051920277</v>
-      </c>
-      <c r="B37" t="s">
-        <v>105</v>
-      </c>
-      <c r="C37" t="s">
-        <v>132</v>
-      </c>
-      <c r="D37" t="s">
-        <v>167</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>23330051920279</v>
-      </c>
-      <c r="B38" t="s">
-        <v>106</v>
-      </c>
-      <c r="C38" t="s">
-        <v>116</v>
-      </c>
-      <c r="D38" t="s">
-        <v>168</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>23330051920280</v>
-      </c>
-      <c r="B39" t="s">
-        <v>107</v>
-      </c>
-      <c r="C39" t="s">
-        <v>89</v>
-      </c>
-      <c r="D39" t="s">
-        <v>169</v>
-      </c>
-      <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -8210,7 +7484,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8219,22 +7493,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -8242,22 +7516,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920237</v>
+        <v>23330051920226</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -8265,65 +7539,65 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920237</v>
+        <v>23330051920226</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920242</v>
+        <v>23330051920254</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920242</v>
+        <v>23330051920254</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>66</v>
@@ -8334,22 +7608,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920244</v>
+        <v>23330051920328</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -8357,68 +7631,68 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920244</v>
+        <v>23330051920328</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920248</v>
+        <v>23330051920357</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920248</v>
+        <v>23330051920357</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -8426,45 +7700,45 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920254</v>
+        <v>23330051920344</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920254</v>
+        <v>23330051920344</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -8472,45 +7746,45 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920328</v>
+        <v>23330051920260</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920328</v>
+        <v>23330051920260</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -8518,45 +7792,45 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920357</v>
+        <v>23330051920327</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920357</v>
+        <v>23330051920327</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -8564,45 +7838,45 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920257</v>
+        <v>23330051920280</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D16" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920257</v>
+        <v>23330051920280</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F17" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -8610,42 +7884,42 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920344</v>
+        <v>23330051920213</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
-        <v>154</v>
+        <v>118</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920344</v>
+        <v>23330051920237</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
         <v>65</v>
@@ -8656,42 +7930,42 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920262</v>
+        <v>23330051920242</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="D20" t="s">
-        <v>156</v>
+        <v>119</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920262</v>
+        <v>23330051920244</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
       <c r="D21" t="s">
-        <v>156</v>
+        <v>120</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F21" t="s">
         <v>65</v>
@@ -8702,19 +7976,19 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920330</v>
+        <v>23330051920257</v>
       </c>
       <c r="B22" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="E22" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
         <v>68</v>
@@ -8728,22 +8002,22 @@
         <v>23330051920330</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -8751,19 +8025,19 @@
         <v>23330051920270</v>
       </c>
       <c r="B24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" t="s">
         <v>98</v>
       </c>
-      <c r="C24" t="s">
-        <v>85</v>
-      </c>
       <c r="D24" t="s">
-        <v>161</v>
+        <v>123</v>
       </c>
       <c r="E24" t="s">
         <v>7</v>
       </c>
       <c r="F24" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G24">
         <v>5</v>
@@ -8771,68 +8045,68 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920270</v>
+        <v>23330051920207</v>
       </c>
       <c r="B25" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s">
-        <v>161</v>
+        <v>124</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920207</v>
+        <v>23330051920276</v>
       </c>
       <c r="B26" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="D26" t="s">
-        <v>162</v>
+        <v>125</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>23330051920207</v>
+        <v>23330051920275</v>
       </c>
       <c r="B27" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="D27" t="s">
-        <v>162</v>
+        <v>126</v>
       </c>
       <c r="E27" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -8840,255 +8114,25 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>23330051920276</v>
+        <v>23330051920277</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="D28" t="s">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="E28" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G28">
         <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>23330051920276</v>
-      </c>
-      <c r="B29" t="s">
-        <v>102</v>
-      </c>
-      <c r="C29" t="s">
-        <v>86</v>
-      </c>
-      <c r="D29" t="s">
-        <v>164</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>64</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>23330051920275</v>
-      </c>
-      <c r="B30" t="s">
-        <v>103</v>
-      </c>
-      <c r="C30" t="s">
-        <v>130</v>
-      </c>
-      <c r="D30" t="s">
-        <v>165</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>64</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>23330051920275</v>
-      </c>
-      <c r="B31" t="s">
-        <v>103</v>
-      </c>
-      <c r="C31" t="s">
-        <v>130</v>
-      </c>
-      <c r="D31" t="s">
-        <v>165</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>66</v>
-      </c>
-      <c r="G31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>23330051920227</v>
-      </c>
-      <c r="B32" t="s">
-        <v>78</v>
-      </c>
-      <c r="C32" t="s">
-        <v>111</v>
-      </c>
-      <c r="D32" t="s">
-        <v>136</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>64</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>23330051920240</v>
-      </c>
-      <c r="B33" t="s">
-        <v>81</v>
-      </c>
-      <c r="C33" t="s">
-        <v>114</v>
-      </c>
-      <c r="D33" t="s">
-        <v>140</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>64</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>23330051920250</v>
-      </c>
-      <c r="B34" t="s">
-        <v>84</v>
-      </c>
-      <c r="C34" t="s">
-        <v>116</v>
-      </c>
-      <c r="D34" t="s">
-        <v>143</v>
-      </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" t="s">
-        <v>64</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>23330051920333</v>
-      </c>
-      <c r="B35" t="s">
-        <v>85</v>
-      </c>
-      <c r="C35" t="s">
-        <v>90</v>
-      </c>
-      <c r="D35" t="s">
-        <v>145</v>
-      </c>
-      <c r="E35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" t="s">
-        <v>64</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>23330051920272</v>
-      </c>
-      <c r="B36" t="s">
-        <v>97</v>
-      </c>
-      <c r="C36" t="s">
-        <v>128</v>
-      </c>
-      <c r="D36" t="s">
-        <v>160</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>64</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>23330051920327</v>
-      </c>
-      <c r="B37" t="s">
-        <v>101</v>
-      </c>
-      <c r="C37" t="s">
-        <v>97</v>
-      </c>
-      <c r="D37" t="s">
-        <v>137</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>64</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>23330051920277</v>
-      </c>
-      <c r="B38" t="s">
-        <v>105</v>
-      </c>
-      <c r="C38" t="s">
-        <v>132</v>
-      </c>
-      <c r="D38" t="s">
-        <v>167</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" t="s">
-        <v>64</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/1BV - Estadisticos 20231.xlsx
+++ b/grupos/1BV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="112">
   <si>
     <t>Materia</t>
   </si>
@@ -218,18 +218,18 @@
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
-    <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
     <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
@@ -251,157 +251,109 @@
     <t>CASTRO</t>
   </si>
   <si>
+    <t>CALVA</t>
+  </si>
+  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MOSCOSO</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
   </si>
   <si>
     <t>ZACARIAS</t>
   </si>
   <si>
-    <t>ALCANTARA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
     <t>BERMUDEZ</t>
   </si>
   <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
     <t>CIRUELO</t>
   </si>
   <si>
+    <t>MONTERROSAS</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>FERRER</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>FERRER</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MONTERROSAS</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
     <t>YAMILETH</t>
   </si>
   <si>
+    <t>LORENA</t>
+  </si>
+  <si>
     <t>MIGUEL ENRIQUE</t>
   </si>
   <si>
     <t>GISELA GUADALUPE</t>
   </si>
   <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>BRISSIA SINAHI</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
+    <t>ANEL</t>
+  </si>
+  <si>
+    <t>INGRID ISABEL</t>
   </si>
   <si>
     <t>VANESA</t>
   </si>
   <si>
+    <t>VALERY MIRANDA</t>
+  </si>
+  <si>
+    <t>LUZ YESENIA</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>VICTORIA VIANNEY</t>
+  </si>
+  <si>
     <t>ANGEL ABRAHAM</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>VALERY MIRANDA</t>
-  </si>
-  <si>
-    <t>LUZ YESENIA</t>
-  </si>
-  <si>
-    <t>BRISEIDA</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>DORIAN</t>
-  </si>
-  <si>
-    <t>VICTORIA VIANNEY</t>
-  </si>
-  <si>
-    <t>ANEL</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
   </si>
 </sst>
 </file>
@@ -937,16 +889,16 @@
         <v>6</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -982,13 +934,13 @@
         <v>9</v>
       </c>
       <c r="AA4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1026,16 +978,16 @@
         <v>5</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1074,7 +1026,7 @@
         <v>5</v>
       </c>
       <c r="AB5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC5">
         <v>5</v>
@@ -1115,16 +1067,16 @@
         <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1157,7 +1109,7 @@
         <v>5</v>
       </c>
       <c r="Z6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA6">
         <v>6</v>
@@ -1204,16 +1156,16 @@
         <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1255,7 +1207,7 @@
         <v>5</v>
       </c>
       <c r="AC7">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1293,16 +1245,16 @@
         <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1338,7 +1290,7 @@
         <v>7</v>
       </c>
       <c r="AA8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB8">
         <v>5</v>
@@ -1382,16 +1334,16 @@
         <v>6</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1424,16 +1376,16 @@
         <v>7</v>
       </c>
       <c r="Z9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC9">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1471,16 +1423,16 @@
         <v>6</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1519,7 +1471,7 @@
         <v>7</v>
       </c>
       <c r="AB10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC10">
         <v>6</v>
@@ -1560,16 +1512,16 @@
         <v>6</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1608,10 +1560,10 @@
         <v>5</v>
       </c>
       <c r="AB11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC11">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1649,16 +1601,16 @@
         <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1691,7 +1643,7 @@
         <v>7</v>
       </c>
       <c r="Z12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA12">
         <v>5</v>
@@ -1738,16 +1690,16 @@
         <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1780,13 +1732,13 @@
         <v>6</v>
       </c>
       <c r="Z13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC13">
         <v>6</v>
@@ -1827,16 +1779,16 @@
         <v>5</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1869,13 +1821,13 @@
         <v>5</v>
       </c>
       <c r="Z14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA14">
         <v>9</v>
       </c>
       <c r="AB14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC14">
         <v>6</v>
@@ -1916,16 +1868,16 @@
         <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1961,7 +1913,7 @@
         <v>5</v>
       </c>
       <c r="AA15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB15">
         <v>5</v>
@@ -2005,16 +1957,16 @@
         <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2053,7 +2005,7 @@
         <v>9</v>
       </c>
       <c r="AB16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC16">
         <v>6</v>
@@ -2094,16 +2046,16 @@
         <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2183,16 +2135,16 @@
         <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2225,10 +2177,10 @@
         <v>6</v>
       </c>
       <c r="Z18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB18">
         <v>6</v>
@@ -2272,16 +2224,16 @@
         <v>6</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2314,13 +2266,13 @@
         <v>5</v>
       </c>
       <c r="Z19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA19">
         <v>5</v>
       </c>
       <c r="AB19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC19">
         <v>6</v>
@@ -2361,16 +2313,16 @@
         <v>5</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2403,10 +2355,10 @@
         <v>5</v>
       </c>
       <c r="Z20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA20">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB20">
         <v>5</v>
@@ -2450,16 +2402,16 @@
         <v>7</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2539,16 +2491,16 @@
         <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2581,10 +2533,10 @@
         <v>5</v>
       </c>
       <c r="Z22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA22">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB22">
         <v>5</v>
@@ -2628,16 +2580,16 @@
         <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2673,10 +2625,10 @@
         <v>5</v>
       </c>
       <c r="AA23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB23">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC23">
         <v>5</v>
@@ -2717,16 +2669,16 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2762,7 +2714,7 @@
         <v>5</v>
       </c>
       <c r="AA24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB24">
         <v>5</v>
@@ -2806,16 +2758,16 @@
         <v>6</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2848,13 +2800,13 @@
         <v>7</v>
       </c>
       <c r="Z25">
+        <v>8</v>
+      </c>
+      <c r="AA25">
+        <v>8</v>
+      </c>
+      <c r="AB25">
         <v>9</v>
-      </c>
-      <c r="AA25">
-        <v>5</v>
-      </c>
-      <c r="AB25">
-        <v>10</v>
       </c>
       <c r="AC25">
         <v>6</v>
@@ -2895,16 +2847,16 @@
         <v>6</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2940,10 +2892,10 @@
         <v>7</v>
       </c>
       <c r="AA26">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC26">
         <v>6</v>
@@ -2984,16 +2936,16 @@
         <v>6</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -3029,7 +2981,7 @@
         <v>5</v>
       </c>
       <c r="AA27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB27">
         <v>5</v>
@@ -3073,16 +3025,16 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3115,16 +3067,16 @@
         <v>5</v>
       </c>
       <c r="Z28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB28">
         <v>5</v>
       </c>
       <c r="AC28">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3162,16 +3114,16 @@
         <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3213,7 +3165,7 @@
         <v>5</v>
       </c>
       <c r="AC29">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3251,16 +3203,16 @@
         <v>6</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3293,10 +3245,10 @@
         <v>5</v>
       </c>
       <c r="Z30">
+        <v>7</v>
+      </c>
+      <c r="AA30">
         <v>9</v>
-      </c>
-      <c r="AA30">
-        <v>8</v>
       </c>
       <c r="AB30">
         <v>7</v>
@@ -3340,16 +3292,16 @@
         <v>5</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3388,7 +3340,7 @@
         <v>5</v>
       </c>
       <c r="AB31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC31">
         <v>5</v>
@@ -3429,16 +3381,16 @@
         <v>6</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3471,7 +3423,7 @@
         <v>5</v>
       </c>
       <c r="Z32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA32">
         <v>8</v>
@@ -3518,16 +3470,16 @@
         <v>8</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3560,16 +3512,16 @@
         <v>8</v>
       </c>
       <c r="Z33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB33">
         <v>10</v>
       </c>
       <c r="AC33">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3607,16 +3559,16 @@
         <v>4</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3658,7 +3610,7 @@
         <v>5</v>
       </c>
       <c r="AC34">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -3696,16 +3648,16 @@
         <v>6</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3738,13 +3690,13 @@
         <v>6</v>
       </c>
       <c r="Z35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC35">
         <v>6</v>
@@ -3785,16 +3737,16 @@
         <v>4</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3830,13 +3782,13 @@
         <v>6</v>
       </c>
       <c r="AA36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC36">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -3874,16 +3826,16 @@
         <v>6</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -3916,13 +3868,13 @@
         <v>5</v>
       </c>
       <c r="Z37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA37">
         <v>10</v>
       </c>
       <c r="AB37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC37">
         <v>6</v>
@@ -3963,16 +3915,16 @@
         <v>6</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P38">
         <v>-1</v>
@@ -4011,7 +3963,7 @@
         <v>5</v>
       </c>
       <c r="AB38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC38">
         <v>6</v>
@@ -4052,16 +4004,16 @@
         <v>5</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P39">
         <v>-1</v>
@@ -4097,13 +4049,13 @@
         <v>5</v>
       </c>
       <c r="AA39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC39">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:29">
@@ -4141,16 +4093,16 @@
         <v>5</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P40">
         <v>-1</v>
@@ -4186,13 +4138,13 @@
         <v>5</v>
       </c>
       <c r="AA40">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC40">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:29">
@@ -4230,16 +4182,16 @@
         <v>4</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P41">
         <v>-1</v>
@@ -4278,7 +4230,7 @@
         <v>5</v>
       </c>
       <c r="AB41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC41">
         <v>5</v>
@@ -4319,16 +4271,16 @@
         <v>6</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P42">
         <v>-1</v>
@@ -4367,7 +4319,7 @@
         <v>6</v>
       </c>
       <c r="AB42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC42">
         <v>5</v>
@@ -4533,13 +4485,13 @@
         <v>100</v>
       </c>
       <c r="M4">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N4">
         <v>100</v>
       </c>
       <c r="O4">
-        <v>68.2</v>
+        <v>85</v>
       </c>
       <c r="P4">
         <v>85</v>
@@ -4554,13 +4506,13 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="U4">
         <v>100</v>
       </c>
       <c r="V4">
-        <v>68.2</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -4604,10 +4556,10 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="O5">
-        <v>59.1</v>
+        <v>75</v>
       </c>
       <c r="P5">
         <v>80</v>
@@ -4625,10 +4577,10 @@
         <v>100</v>
       </c>
       <c r="U5">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="V5">
-        <v>59.1</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -4672,10 +4624,10 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O6">
-        <v>68.2</v>
+        <v>87.5</v>
       </c>
       <c r="P6">
         <v>90</v>
@@ -4693,10 +4645,10 @@
         <v>100</v>
       </c>
       <c r="U6">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V6">
-        <v>68.2</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -4734,16 +4686,16 @@
         <v>88.59999999999999</v>
       </c>
       <c r="L7">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="M7">
+        <v>95</v>
+      </c>
+      <c r="N7">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="O7">
         <v>90</v>
-      </c>
-      <c r="N7">
-        <v>93.8</v>
-      </c>
-      <c r="O7">
-        <v>86.40000000000001</v>
       </c>
       <c r="P7">
         <v>85</v>
@@ -4755,16 +4707,16 @@
         <v>88.59999999999999</v>
       </c>
       <c r="S7">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T7">
+        <v>95</v>
+      </c>
+      <c r="U7">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="V7">
         <v>90</v>
-      </c>
-      <c r="U7">
-        <v>93.8</v>
-      </c>
-      <c r="V7">
-        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -4802,7 +4754,7 @@
         <v>95.5</v>
       </c>
       <c r="L8">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="M8">
         <v>100</v>
@@ -4811,7 +4763,7 @@
         <v>93.8</v>
       </c>
       <c r="O8">
-        <v>68.2</v>
+        <v>87.5</v>
       </c>
       <c r="P8">
         <v>95</v>
@@ -4823,7 +4775,7 @@
         <v>95.5</v>
       </c>
       <c r="S8">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T8">
         <v>100</v>
@@ -4832,7 +4784,7 @@
         <v>93.8</v>
       </c>
       <c r="V8">
-        <v>68.2</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -4879,7 +4831,7 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>81.8</v>
+        <v>95</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -4900,7 +4852,7 @@
         <v>100</v>
       </c>
       <c r="V9">
-        <v>81.8</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -4944,10 +4896,10 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="O10">
-        <v>81.8</v>
+        <v>90</v>
       </c>
       <c r="P10">
         <v>95</v>
@@ -4965,10 +4917,10 @@
         <v>100</v>
       </c>
       <c r="U10">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V10">
-        <v>81.8</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -5006,16 +4958,16 @@
         <v>84.09999999999999</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M11">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N11">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="O11">
-        <v>72.7</v>
+        <v>90</v>
       </c>
       <c r="P11">
         <v>85</v>
@@ -5027,16 +4979,16 @@
         <v>84.09999999999999</v>
       </c>
       <c r="S11">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T11">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="U11">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V11">
-        <v>72.7</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -5080,10 +5032,10 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O12">
-        <v>86.40000000000001</v>
+        <v>95</v>
       </c>
       <c r="P12">
         <v>80</v>
@@ -5101,10 +5053,10 @@
         <v>100</v>
       </c>
       <c r="U12">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V12">
-        <v>86.40000000000001</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -5151,7 +5103,7 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>81.8</v>
+        <v>85</v>
       </c>
       <c r="P13">
         <v>90</v>
@@ -5172,7 +5124,7 @@
         <v>100</v>
       </c>
       <c r="V13">
-        <v>81.8</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -5216,10 +5168,10 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="O14">
-        <v>81.8</v>
+        <v>90</v>
       </c>
       <c r="P14">
         <v>95</v>
@@ -5237,10 +5189,10 @@
         <v>100</v>
       </c>
       <c r="U14">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V14">
-        <v>81.8</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -5278,16 +5230,16 @@
         <v>88.59999999999999</v>
       </c>
       <c r="L15">
-        <v>75</v>
+        <v>81.3</v>
       </c>
       <c r="M15">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N15">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O15">
-        <v>81.8</v>
+        <v>95</v>
       </c>
       <c r="P15">
         <v>85</v>
@@ -5299,16 +5251,16 @@
         <v>88.59999999999999</v>
       </c>
       <c r="S15">
-        <v>75</v>
+        <v>81.3</v>
       </c>
       <c r="T15">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="U15">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V15">
-        <v>81.8</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -5355,7 +5307,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -5376,7 +5328,7 @@
         <v>100</v>
       </c>
       <c r="V16">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -5420,10 +5372,10 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="P17">
         <v>80</v>
@@ -5441,10 +5393,10 @@
         <v>100</v>
       </c>
       <c r="U17">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -5491,7 +5443,7 @@
         <v>100</v>
       </c>
       <c r="O18">
-        <v>77.3</v>
+        <v>92.5</v>
       </c>
       <c r="P18">
         <v>90</v>
@@ -5512,7 +5464,7 @@
         <v>100</v>
       </c>
       <c r="V18">
-        <v>77.3</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -5559,7 +5511,7 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>68.2</v>
+        <v>77.5</v>
       </c>
       <c r="P19">
         <v>90</v>
@@ -5580,7 +5532,7 @@
         <v>100</v>
       </c>
       <c r="V19">
-        <v>68.2</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -5618,16 +5570,16 @@
         <v>86.40000000000001</v>
       </c>
       <c r="L20">
-        <v>93.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="M20">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N20">
-        <v>87.5</v>
+        <v>81.3</v>
       </c>
       <c r="O20">
-        <v>81.8</v>
+        <v>85</v>
       </c>
       <c r="P20">
         <v>80</v>
@@ -5639,16 +5591,16 @@
         <v>86.40000000000001</v>
       </c>
       <c r="S20">
-        <v>93.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="T20">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="U20">
-        <v>87.5</v>
+        <v>81.3</v>
       </c>
       <c r="V20">
-        <v>81.8</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -5686,16 +5638,16 @@
         <v>93.2</v>
       </c>
       <c r="L21">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="M21">
+        <v>90</v>
+      </c>
+      <c r="N21">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="O21">
         <v>80</v>
-      </c>
-      <c r="N21">
-        <v>100</v>
-      </c>
-      <c r="O21">
-        <v>68.2</v>
       </c>
       <c r="P21">
         <v>95</v>
@@ -5707,16 +5659,16 @@
         <v>93.2</v>
       </c>
       <c r="S21">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="T21">
+        <v>90</v>
+      </c>
+      <c r="U21">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="V21">
         <v>80</v>
-      </c>
-      <c r="U21">
-        <v>100</v>
-      </c>
-      <c r="V21">
-        <v>68.2</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -5754,16 +5706,16 @@
         <v>93.2</v>
       </c>
       <c r="L22">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="M22">
         <v>100</v>
       </c>
       <c r="N22">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O22">
-        <v>86.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="P22">
         <v>80</v>
@@ -5775,16 +5727,16 @@
         <v>93.2</v>
       </c>
       <c r="S22">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T22">
         <v>100</v>
       </c>
       <c r="U22">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V22">
-        <v>86.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -5828,10 +5780,10 @@
         <v>100</v>
       </c>
       <c r="N23">
-        <v>100</v>
+        <v>81.3</v>
       </c>
       <c r="O23">
-        <v>81.8</v>
+        <v>92.5</v>
       </c>
       <c r="P23">
         <v>90</v>
@@ -5849,10 +5801,10 @@
         <v>100</v>
       </c>
       <c r="U23">
-        <v>100</v>
+        <v>81.3</v>
       </c>
       <c r="V23">
-        <v>81.8</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -5890,16 +5842,16 @@
         <v>45.5</v>
       </c>
       <c r="L24">
-        <v>62.5</v>
+        <v>31.3</v>
       </c>
       <c r="M24">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="N24">
-        <v>93.8</v>
+        <v>59.4</v>
       </c>
       <c r="O24">
-        <v>36.4</v>
+        <v>20</v>
       </c>
       <c r="P24">
         <v>40</v>
@@ -5911,16 +5863,16 @@
         <v>45.5</v>
       </c>
       <c r="S24">
-        <v>62.5</v>
+        <v>31.3</v>
       </c>
       <c r="T24">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="U24">
-        <v>93.8</v>
+        <v>59.4</v>
       </c>
       <c r="V24">
-        <v>36.4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -5961,13 +5913,13 @@
         <v>100</v>
       </c>
       <c r="M25">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N25">
         <v>100</v>
       </c>
       <c r="O25">
-        <v>81.8</v>
+        <v>95</v>
       </c>
       <c r="P25">
         <v>90</v>
@@ -5982,13 +5934,13 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="U25">
         <v>100</v>
       </c>
       <c r="V25">
-        <v>81.8</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -6032,10 +5984,10 @@
         <v>100</v>
       </c>
       <c r="N26">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O26">
-        <v>86.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="P26">
         <v>90</v>
@@ -6053,10 +6005,10 @@
         <v>100</v>
       </c>
       <c r="U26">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V26">
-        <v>86.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -6100,10 +6052,10 @@
         <v>100</v>
       </c>
       <c r="N27">
-        <v>31.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="O27">
-        <v>72.7</v>
+        <v>85</v>
       </c>
       <c r="P27">
         <v>90</v>
@@ -6121,10 +6073,10 @@
         <v>100</v>
       </c>
       <c r="U27">
-        <v>31.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="V27">
-        <v>72.7</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -6162,16 +6114,16 @@
         <v>52.3</v>
       </c>
       <c r="L28">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M28">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="N28">
-        <v>93.8</v>
+        <v>53.1</v>
       </c>
       <c r="O28">
-        <v>81.8</v>
+        <v>45</v>
       </c>
       <c r="P28">
         <v>45</v>
@@ -6183,16 +6135,16 @@
         <v>52.3</v>
       </c>
       <c r="S28">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T28">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="U28">
-        <v>93.8</v>
+        <v>53.1</v>
       </c>
       <c r="V28">
-        <v>81.8</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -6233,10 +6185,10 @@
         <v>100</v>
       </c>
       <c r="M29">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N29">
-        <v>93.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="O29">
         <v>100</v>
@@ -6254,10 +6206,10 @@
         <v>100</v>
       </c>
       <c r="T29">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="U29">
-        <v>93.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="V29">
         <v>100</v>
@@ -6304,10 +6256,10 @@
         <v>100</v>
       </c>
       <c r="N30">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O30">
-        <v>81.8</v>
+        <v>95</v>
       </c>
       <c r="P30">
         <v>95</v>
@@ -6325,10 +6277,10 @@
         <v>100</v>
       </c>
       <c r="U30">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V30">
-        <v>81.8</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -6372,10 +6324,10 @@
         <v>100</v>
       </c>
       <c r="N31">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O31">
-        <v>81.8</v>
+        <v>82.5</v>
       </c>
       <c r="P31">
         <v>80</v>
@@ -6393,10 +6345,10 @@
         <v>100</v>
       </c>
       <c r="U31">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V31">
-        <v>81.8</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -6434,7 +6386,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="L32">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="M32">
         <v>100</v>
@@ -6443,7 +6395,7 @@
         <v>100</v>
       </c>
       <c r="O32">
-        <v>81.8</v>
+        <v>95</v>
       </c>
       <c r="P32">
         <v>95</v>
@@ -6455,7 +6407,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="S32">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="T32">
         <v>100</v>
@@ -6464,7 +6416,7 @@
         <v>100</v>
       </c>
       <c r="V32">
-        <v>81.8</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -6511,7 +6463,7 @@
         <v>100</v>
       </c>
       <c r="O33">
-        <v>81.8</v>
+        <v>95</v>
       </c>
       <c r="P33">
         <v>100</v>
@@ -6532,7 +6484,7 @@
         <v>100</v>
       </c>
       <c r="V33">
-        <v>81.8</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -6570,16 +6522,16 @@
         <v>72.7</v>
       </c>
       <c r="L34">
-        <v>87.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="M34">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="N34">
-        <v>93.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="O34">
-        <v>81.8</v>
+        <v>95</v>
       </c>
       <c r="P34">
         <v>60</v>
@@ -6591,16 +6543,16 @@
         <v>72.7</v>
       </c>
       <c r="S34">
-        <v>87.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="T34">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="U34">
-        <v>93.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="V34">
-        <v>81.8</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -6644,10 +6596,10 @@
         <v>100</v>
       </c>
       <c r="N35">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O35">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="P35">
         <v>85</v>
@@ -6665,10 +6617,10 @@
         <v>100</v>
       </c>
       <c r="U35">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V35">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -6712,10 +6664,10 @@
         <v>100</v>
       </c>
       <c r="N36">
-        <v>100</v>
+        <v>81.3</v>
       </c>
       <c r="O36">
-        <v>81.8</v>
+        <v>85</v>
       </c>
       <c r="P36">
         <v>55</v>
@@ -6733,10 +6685,10 @@
         <v>100</v>
       </c>
       <c r="U36">
-        <v>100</v>
+        <v>81.3</v>
       </c>
       <c r="V36">
-        <v>81.8</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -6774,7 +6726,7 @@
         <v>95.5</v>
       </c>
       <c r="L37">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M37">
         <v>100</v>
@@ -6783,7 +6735,7 @@
         <v>100</v>
       </c>
       <c r="O37">
-        <v>81.8</v>
+        <v>95</v>
       </c>
       <c r="P37">
         <v>95</v>
@@ -6795,7 +6747,7 @@
         <v>95.5</v>
       </c>
       <c r="S37">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T37">
         <v>100</v>
@@ -6804,7 +6756,7 @@
         <v>100</v>
       </c>
       <c r="V37">
-        <v>81.8</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -6845,13 +6797,13 @@
         <v>100</v>
       </c>
       <c r="M38">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N38">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="O38">
-        <v>81.8</v>
+        <v>95</v>
       </c>
       <c r="P38">
         <v>90</v>
@@ -6866,13 +6818,13 @@
         <v>100</v>
       </c>
       <c r="T38">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="U38">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="V38">
-        <v>81.8</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -6916,10 +6868,10 @@
         <v>100</v>
       </c>
       <c r="N39">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="O39">
-        <v>81.8</v>
+        <v>92.5</v>
       </c>
       <c r="P39">
         <v>95</v>
@@ -6937,10 +6889,10 @@
         <v>100</v>
       </c>
       <c r="U39">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="V39">
-        <v>81.8</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -6984,10 +6936,10 @@
         <v>100</v>
       </c>
       <c r="N40">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O40">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="P40">
         <v>90</v>
@@ -7005,10 +6957,10 @@
         <v>100</v>
       </c>
       <c r="U40">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V40">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -7046,16 +6998,16 @@
         <v>79.5</v>
       </c>
       <c r="L41">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="M41">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N41">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="O41">
-        <v>77.3</v>
+        <v>77.5</v>
       </c>
       <c r="P41">
         <v>75</v>
@@ -7067,16 +7019,16 @@
         <v>79.5</v>
       </c>
       <c r="S41">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="T41">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="U41">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="V41">
-        <v>77.3</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="42" spans="1:22">
@@ -7120,10 +7072,10 @@
         <v>100</v>
       </c>
       <c r="N42">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O42">
-        <v>72.7</v>
+        <v>87.5</v>
       </c>
       <c r="P42">
         <v>90</v>
@@ -7141,10 +7093,10 @@
         <v>100</v>
       </c>
       <c r="U42">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V42">
-        <v>72.7</v>
+        <v>87.5</v>
       </c>
     </row>
   </sheetData>
@@ -7233,7 +7185,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
@@ -7242,19 +7194,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="2">
-        <v>53.8</v>
+        <v>51.3</v>
       </c>
       <c r="G3" s="2">
-        <v>46.2</v>
+        <v>48.7</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7274,19 +7226,19 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" s="2">
-        <v>59</v>
+        <v>56.4</v>
       </c>
       <c r="G4" s="2">
-        <v>41</v>
+        <v>43.6</v>
       </c>
       <c r="H4">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7306,19 +7258,19 @@
         <v>39</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" s="2">
-        <v>59</v>
+        <v>56.4</v>
       </c>
       <c r="G5" s="2">
-        <v>41</v>
+        <v>43.6</v>
       </c>
       <c r="H5">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7329,7 +7281,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
@@ -7338,19 +7290,19 @@
         <v>39</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F6" s="2">
-        <v>74.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="G6" s="2">
-        <v>25.6</v>
+        <v>43.6</v>
       </c>
       <c r="H6">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7428,7 +7380,7 @@
         <v>64</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -7484,7 +7436,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7522,16 +7474,16 @@
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7545,16 +7497,16 @@
         <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7562,16 +7514,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920254</v>
+        <v>23330051920215</v>
       </c>
       <c r="B4" t="s">
         <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -7585,22 +7537,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920254</v>
+        <v>23330051920215</v>
       </c>
       <c r="B5" t="s">
         <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7608,22 +7560,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920328</v>
+        <v>23330051920254</v>
       </c>
       <c r="B6" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7631,19 +7583,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920328</v>
+        <v>23330051920254</v>
       </c>
       <c r="B7" t="s">
         <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>69</v>
@@ -7654,16 +7606,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920357</v>
+        <v>23330051920328</v>
       </c>
       <c r="B8" t="s">
         <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -7677,22 +7629,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920357</v>
+        <v>23330051920328</v>
       </c>
       <c r="B9" t="s">
         <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7700,22 +7652,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920344</v>
+        <v>23330051920275</v>
       </c>
       <c r="B10" t="s">
         <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7723,22 +7675,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920344</v>
+        <v>23330051920275</v>
       </c>
       <c r="B11" t="s">
         <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7746,22 +7698,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920260</v>
+        <v>23330051920227</v>
       </c>
       <c r="B12" t="s">
         <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7769,22 +7721,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920260</v>
+        <v>23330051920237</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7792,22 +7744,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920327</v>
+        <v>23330051920242</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -7815,16 +7767,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920327</v>
+        <v>23330051920244</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -7838,22 +7790,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920280</v>
+        <v>23330051920330</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="D16" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -7861,22 +7813,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920280</v>
+        <v>23330051920270</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E17" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -7884,22 +7836,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920213</v>
+        <v>23330051920276</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D18" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F18" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -7907,231 +7859,24 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920237</v>
+        <v>23330051920280</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>23330051920242</v>
-      </c>
-      <c r="B20" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" t="s">
-        <v>104</v>
-      </c>
-      <c r="D20" t="s">
-        <v>119</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>68</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>23330051920244</v>
-      </c>
-      <c r="B21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C21" t="s">
-        <v>92</v>
-      </c>
-      <c r="D21" t="s">
-        <v>120</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>65</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>23330051920257</v>
-      </c>
-      <c r="B22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" t="s">
-        <v>105</v>
-      </c>
-      <c r="D22" t="s">
-        <v>121</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>68</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>23330051920330</v>
-      </c>
-      <c r="B23" t="s">
-        <v>89</v>
-      </c>
-      <c r="C23" t="s">
-        <v>106</v>
-      </c>
-      <c r="D23" t="s">
-        <v>122</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>65</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>23330051920270</v>
-      </c>
-      <c r="B24" t="s">
-        <v>90</v>
-      </c>
-      <c r="C24" t="s">
-        <v>98</v>
-      </c>
-      <c r="D24" t="s">
-        <v>123</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>65</v>
-      </c>
-      <c r="G24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>23330051920207</v>
-      </c>
-      <c r="B25" t="s">
-        <v>91</v>
-      </c>
-      <c r="C25" t="s">
-        <v>107</v>
-      </c>
-      <c r="D25" t="s">
-        <v>124</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>66</v>
-      </c>
-      <c r="G25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>23330051920276</v>
-      </c>
-      <c r="B26" t="s">
-        <v>92</v>
-      </c>
-      <c r="C26" t="s">
-        <v>106</v>
-      </c>
-      <c r="D26" t="s">
-        <v>125</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>65</v>
-      </c>
-      <c r="G26">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>23330051920275</v>
-      </c>
-      <c r="B27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" t="s">
-        <v>108</v>
-      </c>
-      <c r="D27" t="s">
-        <v>126</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>68</v>
-      </c>
-      <c r="G27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>23330051920277</v>
-      </c>
-      <c r="B28" t="s">
-        <v>94</v>
-      </c>
-      <c r="C28" t="s">
-        <v>109</v>
-      </c>
-      <c r="D28" t="s">
-        <v>127</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>67</v>
-      </c>
-      <c r="G28">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1BV - Estadisticos 20231.xlsx
+++ b/grupos/1BV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="106">
   <si>
     <t>Materia</t>
   </si>
@@ -215,24 +215,24 @@
     <t>Recursos socioemocionales I</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
-    <t>Villanueva Morales Luis Arturo</t>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -248,73 +248,73 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>FUENTES</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
     <t>CALVA</t>
   </si>
   <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>DAMIAN</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CANDELARIO</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>BERMUDEZ</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>MONTERROSAS</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>FERRER</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>ANGEL JESUS</t>
+  </si>
+  <si>
+    <t>VIVIANA JOSELIN</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
   </si>
   <si>
     <t>YAMILETH</t>
@@ -323,34 +323,16 @@
     <t>LORENA</t>
   </si>
   <si>
+    <t>INGRID ISABEL</t>
+  </si>
+  <si>
+    <t>XIMENA ISABEL</t>
+  </si>
+  <si>
     <t>MIGUEL ENRIQUE</t>
   </si>
   <si>
-    <t>GISELA GUADALUPE</t>
-  </si>
-  <si>
-    <t>ANEL</t>
-  </si>
-  <si>
-    <t>INGRID ISABEL</t>
-  </si>
-  <si>
-    <t>VANESA</t>
-  </si>
-  <si>
-    <t>VALERY MIRANDA</t>
-  </si>
-  <si>
-    <t>LUZ YESENIA</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>VICTORIA VIANNEY</t>
+    <t>DANNA PAOLA</t>
   </si>
   <si>
     <t>ANGEL ABRAHAM</t>
@@ -901,22 +883,22 @@
         <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <v>-1</v>
@@ -990,43 +972,43 @@
         <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V5">
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>6</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z5">
         <v>5</v>
       </c>
       <c r="AA5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC5">
         <v>5</v>
@@ -1079,22 +1061,22 @@
         <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
         <v>-1</v>
@@ -1115,7 +1097,7 @@
         <v>6</v>
       </c>
       <c r="AB6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC6">
         <v>6</v>
@@ -1168,28 +1150,28 @@
         <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S7">
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>6</v>
@@ -1201,10 +1183,10 @@
         <v>5</v>
       </c>
       <c r="AA7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC7">
         <v>5</v>
@@ -1257,28 +1239,28 @@
         <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S8">
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>7</v>
@@ -1293,7 +1275,7 @@
         <v>7</v>
       </c>
       <c r="AB8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC8">
         <v>5</v>
@@ -1346,22 +1328,22 @@
         <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>-1</v>
@@ -1435,34 +1417,34 @@
         <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z10">
         <v>7</v>
@@ -1471,7 +1453,7 @@
         <v>7</v>
       </c>
       <c r="AB10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC10">
         <v>6</v>
@@ -1524,22 +1506,22 @@
         <v>5</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S11">
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>-1</v>
@@ -1557,10 +1539,10 @@
         <v>5</v>
       </c>
       <c r="AA11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC11">
         <v>5</v>
@@ -1613,43 +1595,43 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S12">
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X12">
+        <v>8</v>
+      </c>
+      <c r="Y12">
+        <v>6</v>
+      </c>
+      <c r="Z12">
+        <v>7</v>
+      </c>
+      <c r="AA12">
+        <v>6</v>
+      </c>
+      <c r="AB12">
         <v>9</v>
-      </c>
-      <c r="Y12">
-        <v>7</v>
-      </c>
-      <c r="Z12">
-        <v>7</v>
-      </c>
-      <c r="AA12">
-        <v>5</v>
-      </c>
-      <c r="AB12">
-        <v>10</v>
       </c>
       <c r="AC12">
         <v>6</v>
@@ -1702,31 +1684,31 @@
         <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>6</v>
@@ -1791,22 +1773,22 @@
         <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V14">
         <v>-1</v>
@@ -1818,7 +1800,7 @@
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z14">
         <v>6</v>
@@ -1827,7 +1809,7 @@
         <v>9</v>
       </c>
       <c r="AB14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC14">
         <v>6</v>
@@ -1880,28 +1862,28 @@
         <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S15">
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>7</v>
@@ -1913,10 +1895,10 @@
         <v>5</v>
       </c>
       <c r="AA15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC15">
         <v>6</v>
@@ -1969,22 +1951,22 @@
         <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>-1</v>
@@ -2005,7 +1987,7 @@
         <v>9</v>
       </c>
       <c r="AB16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC16">
         <v>6</v>
@@ -2058,28 +2040,28 @@
         <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S17">
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>7</v>
@@ -2091,10 +2073,10 @@
         <v>5</v>
       </c>
       <c r="AA17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC17">
         <v>5</v>
@@ -2147,28 +2129,28 @@
         <v>6</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S18">
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>7</v>
@@ -2180,10 +2162,10 @@
         <v>7</v>
       </c>
       <c r="AA18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC18">
         <v>6</v>
@@ -2236,22 +2218,22 @@
         <v>6</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V19">
         <v>-1</v>
@@ -2263,13 +2245,13 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z19">
         <v>5</v>
       </c>
       <c r="AA19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB19">
         <v>7</v>
@@ -2325,22 +2307,22 @@
         <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S20">
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>-1</v>
@@ -2361,7 +2343,7 @@
         <v>7</v>
       </c>
       <c r="AB20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC20">
         <v>6</v>
@@ -2414,43 +2396,43 @@
         <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S21">
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z21">
         <v>5</v>
       </c>
       <c r="AA21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC21">
         <v>5</v>
@@ -2503,22 +2485,22 @@
         <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
         <v>-1</v>
@@ -2527,10 +2509,10 @@
         <v>7</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z22">
         <v>7</v>
@@ -2539,7 +2521,7 @@
         <v>8</v>
       </c>
       <c r="AB22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC22">
         <v>5</v>
@@ -2592,22 +2574,22 @@
         <v>5</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>-1</v>
@@ -2619,13 +2601,13 @@
         <v>6</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z23">
         <v>5</v>
       </c>
       <c r="AA23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB23">
         <v>7</v>
@@ -2681,22 +2663,22 @@
         <v>5</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S24">
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V24">
         <v>-1</v>
@@ -2770,22 +2752,22 @@
         <v>6</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S25">
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="V25">
         <v>-1</v>
@@ -2803,10 +2785,10 @@
         <v>8</v>
       </c>
       <c r="AA25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB25">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC25">
         <v>6</v>
@@ -2859,28 +2841,28 @@
         <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X26">
         <v>8</v>
@@ -2895,7 +2877,7 @@
         <v>8</v>
       </c>
       <c r="AB26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC26">
         <v>6</v>
@@ -2948,34 +2930,34 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S27">
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V27">
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z27">
         <v>5</v>
@@ -3037,22 +3019,22 @@
         <v>5</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S28">
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V28">
         <v>-1</v>
@@ -3061,7 +3043,7 @@
         <v>5</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y28">
         <v>5</v>
@@ -3070,7 +3052,7 @@
         <v>5</v>
       </c>
       <c r="AA28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB28">
         <v>5</v>
@@ -3126,34 +3108,34 @@
         <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S29">
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V29">
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X29">
         <v>6</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z29">
         <v>5</v>
@@ -3215,40 +3197,40 @@
         <v>6</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S30">
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V30">
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X30">
         <v>7</v>
       </c>
       <c r="Y30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z30">
         <v>7</v>
       </c>
       <c r="AA30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB30">
         <v>7</v>
@@ -3304,28 +3286,28 @@
         <v>5</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S31">
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X31">
         <v>7</v>
@@ -3340,7 +3322,7 @@
         <v>5</v>
       </c>
       <c r="AB31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC31">
         <v>5</v>
@@ -3393,43 +3375,43 @@
         <v>6</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S32">
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V32">
         <v>-1</v>
       </c>
       <c r="W32">
+        <v>8</v>
+      </c>
+      <c r="X32">
+        <v>8</v>
+      </c>
+      <c r="Y32">
+        <v>6</v>
+      </c>
+      <c r="Z32">
+        <v>6</v>
+      </c>
+      <c r="AA32">
         <v>9</v>
       </c>
-      <c r="X32">
-        <v>8</v>
-      </c>
-      <c r="Y32">
-        <v>5</v>
-      </c>
-      <c r="Z32">
-        <v>6</v>
-      </c>
-      <c r="AA32">
-        <v>8</v>
-      </c>
       <c r="AB32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC32">
         <v>6</v>
@@ -3482,22 +3464,22 @@
         <v>8</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
         <v>-1</v>
@@ -3571,22 +3553,22 @@
         <v>5</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="S34">
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V34">
         <v>-1</v>
@@ -3595,7 +3577,7 @@
         <v>5</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y34">
         <v>5</v>
@@ -3660,28 +3642,28 @@
         <v>6</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S35">
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V35">
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X35">
         <v>9</v>
@@ -3749,22 +3731,22 @@
         <v>5</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S36">
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V36">
         <v>-1</v>
@@ -3782,10 +3764,10 @@
         <v>6</v>
       </c>
       <c r="AA36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC36">
         <v>5</v>
@@ -3838,34 +3820,34 @@
         <v>6</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S37">
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V37">
         <v>-1</v>
       </c>
       <c r="W37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X37">
         <v>8</v>
       </c>
       <c r="Y37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z37">
         <v>6</v>
@@ -3927,28 +3909,28 @@
         <v>6</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S38">
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V38">
         <v>-1</v>
       </c>
       <c r="W38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X38">
         <v>7</v>
@@ -3960,10 +3942,10 @@
         <v>8</v>
       </c>
       <c r="AA38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC38">
         <v>6</v>
@@ -4016,22 +3998,22 @@
         <v>5</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S39">
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V39">
         <v>-1</v>
@@ -4049,10 +4031,10 @@
         <v>5</v>
       </c>
       <c r="AA39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC39">
         <v>5</v>
@@ -4105,31 +4087,31 @@
         <v>5</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S40">
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V40">
         <v>-1</v>
       </c>
       <c r="W40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y40">
         <v>5</v>
@@ -4138,7 +4120,7 @@
         <v>5</v>
       </c>
       <c r="AA40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB40">
         <v>6</v>
@@ -4194,22 +4176,22 @@
         <v>5</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S41">
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V41">
         <v>-1</v>
@@ -4227,7 +4209,7 @@
         <v>5</v>
       </c>
       <c r="AA41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB41">
         <v>5</v>
@@ -4283,22 +4265,22 @@
         <v>5</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S42">
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V42">
         <v>-1</v>
@@ -4494,19 +4476,19 @@
         <v>85</v>
       </c>
       <c r="P4">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="Q4">
         <v>100</v>
       </c>
       <c r="R4">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S4">
         <v>100</v>
       </c>
       <c r="T4">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U4">
         <v>100</v>
@@ -4562,13 +4544,13 @@
         <v>75</v>
       </c>
       <c r="P5">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="Q5">
-        <v>83.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="R5">
-        <v>86.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -4577,7 +4559,7 @@
         <v>100</v>
       </c>
       <c r="U5">
-        <v>84.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="V5">
         <v>75</v>
@@ -4636,7 +4618,7 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>86.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -4645,7 +4627,7 @@
         <v>100</v>
       </c>
       <c r="U6">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V6">
         <v>87.5</v>
@@ -4698,22 +4680,22 @@
         <v>90</v>
       </c>
       <c r="P7">
-        <v>85</v>
+        <v>86.7</v>
       </c>
       <c r="Q7">
         <v>100</v>
       </c>
       <c r="R7">
-        <v>88.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S7">
         <v>90.59999999999999</v>
       </c>
       <c r="T7">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U7">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="V7">
         <v>90</v>
@@ -4766,13 +4748,13 @@
         <v>87.5</v>
       </c>
       <c r="P8">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="Q8">
         <v>100</v>
       </c>
       <c r="R8">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="S8">
         <v>96.90000000000001</v>
@@ -4781,7 +4763,7 @@
         <v>100</v>
       </c>
       <c r="U8">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="V8">
         <v>87.5</v>
@@ -4834,13 +4816,13 @@
         <v>95</v>
       </c>
       <c r="P9">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="Q9">
         <v>100</v>
       </c>
       <c r="R9">
-        <v>90.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -4902,13 +4884,13 @@
         <v>90</v>
       </c>
       <c r="P10">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="Q10">
         <v>100</v>
       </c>
       <c r="R10">
-        <v>86.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -4917,7 +4899,7 @@
         <v>100</v>
       </c>
       <c r="U10">
-        <v>93.8</v>
+        <v>91.7</v>
       </c>
       <c r="V10">
         <v>90</v>
@@ -4970,22 +4952,22 @@
         <v>90</v>
       </c>
       <c r="P11">
-        <v>85</v>
+        <v>86.7</v>
       </c>
       <c r="Q11">
         <v>100</v>
       </c>
       <c r="R11">
-        <v>84.09999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S11">
         <v>93.8</v>
       </c>
       <c r="T11">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="U11">
-        <v>93.8</v>
+        <v>91.7</v>
       </c>
       <c r="V11">
         <v>90</v>
@@ -5038,13 +5020,13 @@
         <v>95</v>
       </c>
       <c r="P12">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="Q12">
         <v>100</v>
       </c>
       <c r="R12">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -5053,7 +5035,7 @@
         <v>100</v>
       </c>
       <c r="U12">
-        <v>96.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="V12">
         <v>95</v>
@@ -5112,7 +5094,7 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -5174,13 +5156,13 @@
         <v>90</v>
       </c>
       <c r="P14">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="Q14">
         <v>100</v>
       </c>
       <c r="R14">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -5189,7 +5171,7 @@
         <v>100</v>
       </c>
       <c r="U14">
-        <v>93.8</v>
+        <v>91.7</v>
       </c>
       <c r="V14">
         <v>90</v>
@@ -5242,22 +5224,22 @@
         <v>95</v>
       </c>
       <c r="P15">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="Q15">
         <v>100</v>
       </c>
       <c r="R15">
-        <v>88.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S15">
         <v>81.3</v>
       </c>
       <c r="T15">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="U15">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V15">
         <v>95</v>
@@ -5310,13 +5292,13 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="Q16">
         <v>100</v>
       </c>
       <c r="R16">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -5325,7 +5307,7 @@
         <v>100</v>
       </c>
       <c r="U16">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V16">
         <v>100</v>
@@ -5378,13 +5360,13 @@
         <v>42.5</v>
       </c>
       <c r="P17">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="Q17">
         <v>100</v>
       </c>
       <c r="R17">
-        <v>79.5</v>
+        <v>79.7</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -5393,7 +5375,7 @@
         <v>100</v>
       </c>
       <c r="U17">
-        <v>84.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="V17">
         <v>42.5</v>
@@ -5446,13 +5428,13 @@
         <v>92.5</v>
       </c>
       <c r="P18">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="Q18">
         <v>100</v>
       </c>
       <c r="R18">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -5514,13 +5496,13 @@
         <v>77.5</v>
       </c>
       <c r="P19">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="Q19">
         <v>100</v>
       </c>
       <c r="R19">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -5588,16 +5570,16 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>86.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="S20">
         <v>78.09999999999999</v>
       </c>
       <c r="T20">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U20">
-        <v>81.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="V20">
         <v>85</v>
@@ -5650,22 +5632,22 @@
         <v>80</v>
       </c>
       <c r="P21">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="Q21">
         <v>100</v>
       </c>
       <c r="R21">
-        <v>93.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S21">
         <v>93.8</v>
       </c>
       <c r="T21">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="U21">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="V21">
         <v>80</v>
@@ -5718,13 +5700,13 @@
         <v>97.5</v>
       </c>
       <c r="P22">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="Q22">
         <v>100</v>
       </c>
       <c r="R22">
-        <v>93.2</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S22">
         <v>96.90000000000001</v>
@@ -5733,7 +5715,7 @@
         <v>100</v>
       </c>
       <c r="U22">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="V22">
         <v>97.5</v>
@@ -5792,7 +5774,7 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>93.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -5801,7 +5783,7 @@
         <v>100</v>
       </c>
       <c r="U23">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="V23">
         <v>92.5</v>
@@ -5854,22 +5836,22 @@
         <v>20</v>
       </c>
       <c r="P24">
-        <v>40</v>
+        <v>26.7</v>
       </c>
       <c r="Q24">
         <v>100</v>
       </c>
       <c r="R24">
-        <v>45.5</v>
+        <v>31.3</v>
       </c>
       <c r="S24">
         <v>31.3</v>
       </c>
       <c r="T24">
-        <v>87.5</v>
+        <v>90</v>
       </c>
       <c r="U24">
-        <v>59.4</v>
+        <v>39.6</v>
       </c>
       <c r="V24">
         <v>20</v>
@@ -5928,16 +5910,16 @@
         <v>100</v>
       </c>
       <c r="R25">
-        <v>88.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S25">
         <v>100</v>
       </c>
       <c r="T25">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U25">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V25">
         <v>95</v>
@@ -5996,7 +5978,7 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -6005,7 +5987,7 @@
         <v>100</v>
       </c>
       <c r="U26">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V26">
         <v>97.5</v>
@@ -6058,22 +6040,22 @@
         <v>85</v>
       </c>
       <c r="P27">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="Q27">
         <v>100</v>
       </c>
       <c r="R27">
-        <v>88.59999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="S27">
         <v>100</v>
       </c>
       <c r="T27">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U27">
-        <v>65.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="V27">
         <v>85</v>
@@ -6126,22 +6108,22 @@
         <v>45</v>
       </c>
       <c r="P28">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="Q28">
         <v>100</v>
       </c>
       <c r="R28">
-        <v>52.3</v>
+        <v>35.9</v>
       </c>
       <c r="S28">
         <v>50</v>
       </c>
       <c r="T28">
-        <v>87.5</v>
+        <v>90</v>
       </c>
       <c r="U28">
-        <v>53.1</v>
+        <v>35.4</v>
       </c>
       <c r="V28">
         <v>45</v>
@@ -6194,22 +6176,22 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>90</v>
+        <v>86.7</v>
       </c>
       <c r="Q29">
         <v>100</v>
       </c>
       <c r="R29">
-        <v>86.40000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="S29">
         <v>100</v>
       </c>
       <c r="T29">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U29">
-        <v>78.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="V29">
         <v>100</v>
@@ -6262,13 +6244,13 @@
         <v>95</v>
       </c>
       <c r="P30">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="Q30">
         <v>100</v>
       </c>
       <c r="R30">
-        <v>86.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S30">
         <v>100</v>
@@ -6277,7 +6259,7 @@
         <v>100</v>
       </c>
       <c r="U30">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V30">
         <v>95</v>
@@ -6330,22 +6312,22 @@
         <v>82.5</v>
       </c>
       <c r="P31">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="Q31">
         <v>100</v>
       </c>
       <c r="R31">
-        <v>88.59999999999999</v>
+        <v>60.9</v>
       </c>
       <c r="S31">
         <v>100</v>
       </c>
       <c r="T31">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="U31">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="V31">
         <v>82.5</v>
@@ -6398,13 +6380,13 @@
         <v>95</v>
       </c>
       <c r="P32">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="Q32">
         <v>100</v>
       </c>
       <c r="R32">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="S32">
         <v>87.5</v>
@@ -6413,7 +6395,7 @@
         <v>100</v>
       </c>
       <c r="U32">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="V32">
         <v>95</v>
@@ -6534,22 +6516,22 @@
         <v>95</v>
       </c>
       <c r="P34">
-        <v>60</v>
+        <v>73.3</v>
       </c>
       <c r="Q34">
         <v>100</v>
       </c>
       <c r="R34">
-        <v>72.7</v>
+        <v>62.5</v>
       </c>
       <c r="S34">
         <v>78.09999999999999</v>
       </c>
       <c r="T34">
-        <v>85</v>
+        <v>88.3</v>
       </c>
       <c r="U34">
-        <v>71.90000000000001</v>
+        <v>52.1</v>
       </c>
       <c r="V34">
         <v>95</v>
@@ -6602,13 +6584,13 @@
         <v>100</v>
       </c>
       <c r="P35">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="Q35">
         <v>100</v>
       </c>
       <c r="R35">
-        <v>97.7</v>
+        <v>95.3</v>
       </c>
       <c r="S35">
         <v>100</v>
@@ -6617,7 +6599,7 @@
         <v>100</v>
       </c>
       <c r="U35">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V35">
         <v>100</v>
@@ -6670,13 +6652,13 @@
         <v>85</v>
       </c>
       <c r="P36">
-        <v>55</v>
+        <v>63.3</v>
       </c>
       <c r="Q36">
         <v>100</v>
       </c>
       <c r="R36">
-        <v>88.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="S36">
         <v>100</v>
@@ -6685,7 +6667,7 @@
         <v>100</v>
       </c>
       <c r="U36">
-        <v>81.3</v>
+        <v>83.3</v>
       </c>
       <c r="V36">
         <v>85</v>
@@ -6738,13 +6720,13 @@
         <v>95</v>
       </c>
       <c r="P37">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="Q37">
         <v>100</v>
       </c>
       <c r="R37">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="S37">
         <v>93.8</v>
@@ -6753,7 +6735,7 @@
         <v>100</v>
       </c>
       <c r="U37">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V37">
         <v>95</v>
@@ -6812,16 +6794,16 @@
         <v>100</v>
       </c>
       <c r="R38">
-        <v>88.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S38">
         <v>100</v>
       </c>
       <c r="T38">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U38">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="V38">
         <v>95</v>
@@ -6874,13 +6856,13 @@
         <v>92.5</v>
       </c>
       <c r="P39">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="Q39">
         <v>100</v>
       </c>
       <c r="R39">
-        <v>84.09999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="S39">
         <v>100</v>
@@ -6889,7 +6871,7 @@
         <v>100</v>
       </c>
       <c r="U39">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="V39">
         <v>92.5</v>
@@ -6942,13 +6924,13 @@
         <v>100</v>
       </c>
       <c r="P40">
-        <v>90</v>
+        <v>86.7</v>
       </c>
       <c r="Q40">
         <v>100</v>
       </c>
       <c r="R40">
-        <v>97.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S40">
         <v>100</v>
@@ -6957,7 +6939,7 @@
         <v>100</v>
       </c>
       <c r="U40">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="V40">
         <v>100</v>
@@ -7010,22 +6992,22 @@
         <v>77.5</v>
       </c>
       <c r="P41">
-        <v>75</v>
+        <v>76.7</v>
       </c>
       <c r="Q41">
         <v>100</v>
       </c>
       <c r="R41">
-        <v>79.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="S41">
         <v>84.40000000000001</v>
       </c>
       <c r="T41">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U41">
-        <v>87.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="V41">
         <v>77.5</v>
@@ -7078,13 +7060,13 @@
         <v>87.5</v>
       </c>
       <c r="P42">
-        <v>90</v>
+        <v>86.7</v>
       </c>
       <c r="Q42">
         <v>100</v>
       </c>
       <c r="R42">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S42">
         <v>100</v>
@@ -7093,7 +7075,7 @@
         <v>100</v>
       </c>
       <c r="U42">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="V42">
         <v>87.5</v>
@@ -7153,7 +7135,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
@@ -7162,19 +7144,19 @@
         <v>39</v>
       </c>
       <c r="D2">
+        <v>20</v>
+      </c>
+      <c r="E2">
         <v>19</v>
       </c>
-      <c r="E2">
-        <v>20</v>
-      </c>
       <c r="F2" s="2">
+        <v>51.3</v>
+      </c>
+      <c r="G2" s="2">
         <v>48.7</v>
       </c>
-      <c r="G2" s="2">
-        <v>51.3</v>
-      </c>
       <c r="H2">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7185,7 +7167,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
@@ -7194,19 +7176,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F3" s="2">
-        <v>51.3</v>
+        <v>56.4</v>
       </c>
       <c r="G3" s="2">
-        <v>48.7</v>
+        <v>43.6</v>
       </c>
       <c r="H3">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7217,7 +7199,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
@@ -7226,19 +7208,19 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F4" s="2">
-        <v>56.4</v>
+        <v>61.5</v>
       </c>
       <c r="G4" s="2">
-        <v>43.6</v>
+        <v>38.5</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7249,7 +7231,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
@@ -7258,19 +7240,19 @@
         <v>39</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2">
-        <v>56.4</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>43.6</v>
+        <v>17.9</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7281,7 +7263,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
@@ -7290,19 +7272,19 @@
         <v>39</v>
       </c>
       <c r="D6">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F6" s="2">
-        <v>56.4</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>43.6</v>
+        <v>15.4</v>
       </c>
       <c r="H6">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7313,7 +7295,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>70</v>
@@ -7322,19 +7304,19 @@
         <v>39</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" s="2">
-        <v>87.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G7" s="2">
-        <v>12.8</v>
+        <v>15.4</v>
       </c>
       <c r="H7">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7366,7 +7348,7 @@
         <v>5.1</v>
       </c>
       <c r="H8">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7380,7 +7362,7 @@
         <v>64</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -7436,7 +7418,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7468,22 +7450,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920226</v>
+        <v>23330051920216</v>
       </c>
       <c r="B2" t="s">
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7491,22 +7473,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920226</v>
+        <v>23330051920216</v>
       </c>
       <c r="B3" t="s">
         <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7514,22 +7496,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920215</v>
+        <v>23330051920248</v>
       </c>
       <c r="B4" t="s">
         <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7537,22 +7519,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920215</v>
+        <v>23330051920248</v>
       </c>
       <c r="B5" t="s">
         <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7560,22 +7542,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920254</v>
+        <v>23330051920357</v>
       </c>
       <c r="B6" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7583,22 +7565,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920254</v>
+        <v>23330051920357</v>
       </c>
       <c r="B7" t="s">
         <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7606,22 +7588,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920328</v>
+        <v>23330051920277</v>
       </c>
       <c r="B8" t="s">
         <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7629,22 +7611,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920328</v>
+        <v>23330051920277</v>
       </c>
       <c r="B9" t="s">
         <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7652,22 +7634,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920275</v>
+        <v>23330051920226</v>
       </c>
       <c r="B10" t="s">
         <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7675,22 +7657,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920275</v>
+        <v>23330051920215</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7701,19 +7683,19 @@
         <v>23330051920227</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7721,22 +7703,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920237</v>
+        <v>23330051920252</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="D13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7744,22 +7726,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920242</v>
+        <v>23330051920254</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -7767,19 +7749,19 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920244</v>
+        <v>23330051920256</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D15" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F15" t="s">
         <v>65</v>
@@ -7790,93 +7772,24 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920330</v>
+        <v>23330051920280</v>
       </c>
       <c r="B16" t="s">
         <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D16" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F16" t="s">
         <v>65</v>
       </c>
       <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>23330051920270</v>
-      </c>
-      <c r="B17" t="s">
-        <v>86</v>
-      </c>
-      <c r="C17" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" t="s">
-        <v>109</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>65</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>23330051920276</v>
-      </c>
-      <c r="B18" t="s">
-        <v>87</v>
-      </c>
-      <c r="C18" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18" t="s">
-        <v>110</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>65</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>23330051920280</v>
-      </c>
-      <c r="B19" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19" t="s">
-        <v>79</v>
-      </c>
-      <c r="D19" t="s">
-        <v>111</v>
-      </c>
-      <c r="E19" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" t="s">
-        <v>66</v>
-      </c>
-      <c r="G19">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1BV - Estadisticos 20231.xlsx
+++ b/grupos/1BV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="107">
   <si>
     <t>Materia</t>
   </si>
@@ -218,21 +218,21 @@
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -248,91 +248,94 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CALVA</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
     <t>FUENTES</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CALVA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
     <t>ZACARIAS</t>
   </si>
   <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
     <t>DAMIAN</t>
   </si>
   <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>BERMUDEZ</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CANDELARIO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
+    <t>CLAUDIA RUBI</t>
+  </si>
+  <si>
+    <t>MIGUEL ENRIQUE</t>
+  </si>
+  <si>
+    <t>NURIA BELEN</t>
+  </si>
+  <si>
+    <t>YAMILETH</t>
+  </si>
+  <si>
+    <t>LORENA</t>
   </si>
   <si>
     <t>ANGEL JESUS</t>
   </si>
   <si>
+    <t>VALERY MIRANDA</t>
+  </si>
+  <si>
     <t>VIVIANA JOSELIN</t>
   </si>
   <si>
+    <t>GISELA GUADALUPE</t>
+  </si>
+  <si>
     <t>VANESSA</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>YAMILETH</t>
-  </si>
-  <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>INGRID ISABEL</t>
-  </si>
-  <si>
-    <t>XIMENA ISABEL</t>
-  </si>
-  <si>
-    <t>MIGUEL ENRIQUE</t>
-  </si>
-  <si>
-    <t>DANNA PAOLA</t>
   </si>
   <si>
     <t>ANGEL ABRAHAM</t>
@@ -892,7 +895,7 @@
         <v>7</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>8</v>
@@ -901,7 +904,7 @@
         <v>7</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W4">
         <v>8</v>
@@ -981,7 +984,7 @@
         <v>7</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
         <v>8</v>
@@ -990,7 +993,7 @@
         <v>5</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W5">
         <v>7</v>
@@ -1002,7 +1005,7 @@
         <v>6</v>
       </c>
       <c r="Z5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA5">
         <v>6</v>
@@ -1070,7 +1073,7 @@
         <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>6</v>
@@ -1079,7 +1082,7 @@
         <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>8</v>
@@ -1091,7 +1094,7 @@
         <v>5</v>
       </c>
       <c r="Z6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA6">
         <v>6</v>
@@ -1159,7 +1162,7 @@
         <v>6</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>8</v>
@@ -1168,7 +1171,7 @@
         <v>8</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>6</v>
@@ -1180,7 +1183,7 @@
         <v>6</v>
       </c>
       <c r="Z7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA7">
         <v>6</v>
@@ -1248,7 +1251,7 @@
         <v>6</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>7</v>
@@ -1257,7 +1260,7 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W8">
         <v>7</v>
@@ -1337,7 +1340,7 @@
         <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1346,7 +1349,7 @@
         <v>9</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>9</v>
@@ -1358,7 +1361,7 @@
         <v>7</v>
       </c>
       <c r="Z9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA9">
         <v>8</v>
@@ -1367,7 +1370,7 @@
         <v>8</v>
       </c>
       <c r="AC9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1426,7 +1429,7 @@
         <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -1435,7 +1438,7 @@
         <v>7</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W10">
         <v>8</v>
@@ -1447,7 +1450,7 @@
         <v>6</v>
       </c>
       <c r="Z10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA10">
         <v>7</v>
@@ -1515,7 +1518,7 @@
         <v>5</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1524,7 +1527,7 @@
         <v>9</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W11">
         <v>7</v>
@@ -1536,7 +1539,7 @@
         <v>5</v>
       </c>
       <c r="Z11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA11">
         <v>7</v>
@@ -1604,7 +1607,7 @@
         <v>6</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>9</v>
@@ -1613,7 +1616,7 @@
         <v>7</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>7</v>
@@ -1625,7 +1628,7 @@
         <v>6</v>
       </c>
       <c r="Z12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA12">
         <v>6</v>
@@ -1634,7 +1637,7 @@
         <v>9</v>
       </c>
       <c r="AC12">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1693,7 +1696,7 @@
         <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>7</v>
@@ -1702,7 +1705,7 @@
         <v>8</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>7</v>
@@ -1714,7 +1717,7 @@
         <v>6</v>
       </c>
       <c r="Z13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA13">
         <v>8</v>
@@ -1782,7 +1785,7 @@
         <v>7</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1791,7 +1794,7 @@
         <v>6</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W14">
         <v>9</v>
@@ -1871,7 +1874,7 @@
         <v>5</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>7</v>
@@ -1880,7 +1883,7 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>8</v>
@@ -1892,7 +1895,7 @@
         <v>5</v>
       </c>
       <c r="Z15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA15">
         <v>6</v>
@@ -1960,7 +1963,7 @@
         <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -1969,7 +1972,7 @@
         <v>9</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>9</v>
@@ -1981,7 +1984,7 @@
         <v>7</v>
       </c>
       <c r="Z16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA16">
         <v>9</v>
@@ -2049,7 +2052,7 @@
         <v>5</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T17">
         <v>8</v>
@@ -2058,7 +2061,7 @@
         <v>8</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W17">
         <v>7</v>
@@ -2138,7 +2141,7 @@
         <v>6</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>10</v>
@@ -2147,7 +2150,7 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W18">
         <v>9</v>
@@ -2159,7 +2162,7 @@
         <v>6</v>
       </c>
       <c r="Z18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA18">
         <v>9</v>
@@ -2227,7 +2230,7 @@
         <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>8</v>
@@ -2236,7 +2239,7 @@
         <v>9</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -2248,7 +2251,7 @@
         <v>6</v>
       </c>
       <c r="Z19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA19">
         <v>6</v>
@@ -2316,7 +2319,7 @@
         <v>5</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>8</v>
@@ -2325,7 +2328,7 @@
         <v>8</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>6</v>
@@ -2337,7 +2340,7 @@
         <v>5</v>
       </c>
       <c r="Z20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA20">
         <v>7</v>
@@ -2346,7 +2349,7 @@
         <v>6</v>
       </c>
       <c r="AC20">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2405,7 +2408,7 @@
         <v>4</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>9</v>
@@ -2414,7 +2417,7 @@
         <v>7</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2426,7 +2429,7 @@
         <v>5</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA21">
         <v>7</v>
@@ -2435,7 +2438,7 @@
         <v>7</v>
       </c>
       <c r="AC21">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2494,7 +2497,7 @@
         <v>7</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>9</v>
@@ -2503,7 +2506,7 @@
         <v>10</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>7</v>
@@ -2524,7 +2527,7 @@
         <v>7</v>
       </c>
       <c r="AC22">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2583,7 +2586,7 @@
         <v>6</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>7</v>
@@ -2592,7 +2595,7 @@
         <v>7</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W23">
         <v>8</v>
@@ -2604,7 +2607,7 @@
         <v>6</v>
       </c>
       <c r="Z23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA23">
         <v>6</v>
@@ -2672,7 +2675,7 @@
         <v>0</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
         <v>5</v>
@@ -2681,7 +2684,7 @@
         <v>5</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W24">
         <v>5</v>
@@ -2761,7 +2764,7 @@
         <v>7</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>7</v>
@@ -2770,7 +2773,7 @@
         <v>4</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W25">
         <v>8</v>
@@ -2782,7 +2785,7 @@
         <v>7</v>
       </c>
       <c r="Z25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA25">
         <v>7</v>
@@ -2850,7 +2853,7 @@
         <v>6</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
         <v>9</v>
@@ -2859,7 +2862,7 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W26">
         <v>9</v>
@@ -2871,7 +2874,7 @@
         <v>6</v>
       </c>
       <c r="Z26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA26">
         <v>8</v>
@@ -2939,7 +2942,7 @@
         <v>4</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T27">
         <v>5</v>
@@ -2948,7 +2951,7 @@
         <v>5</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W27">
         <v>7</v>
@@ -2960,7 +2963,7 @@
         <v>5</v>
       </c>
       <c r="Z27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA27">
         <v>5</v>
@@ -2969,7 +2972,7 @@
         <v>5</v>
       </c>
       <c r="AC27">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3028,7 +3031,7 @@
         <v>4</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T28">
         <v>5</v>
@@ -3037,7 +3040,7 @@
         <v>5</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W28">
         <v>5</v>
@@ -3117,7 +3120,7 @@
         <v>7</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
         <v>5</v>
@@ -3126,7 +3129,7 @@
         <v>5</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W29">
         <v>5</v>
@@ -3138,7 +3141,7 @@
         <v>5</v>
       </c>
       <c r="Z29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA29">
         <v>5</v>
@@ -3206,7 +3209,7 @@
         <v>9</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
         <v>8</v>
@@ -3215,7 +3218,7 @@
         <v>9</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W30">
         <v>8</v>
@@ -3227,7 +3230,7 @@
         <v>7</v>
       </c>
       <c r="Z30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA30">
         <v>8</v>
@@ -3295,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
         <v>5</v>
@@ -3304,7 +3307,7 @@
         <v>7</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W31">
         <v>6</v>
@@ -3384,7 +3387,7 @@
         <v>7</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>10</v>
@@ -3393,7 +3396,7 @@
         <v>6</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W32">
         <v>8</v>
@@ -3405,7 +3408,7 @@
         <v>6</v>
       </c>
       <c r="Z32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA32">
         <v>9</v>
@@ -3473,7 +3476,7 @@
         <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3482,7 +3485,7 @@
         <v>10</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W33">
         <v>10</v>
@@ -3562,7 +3565,7 @@
         <v>3</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T34">
         <v>5</v>
@@ -3571,7 +3574,7 @@
         <v>5</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W34">
         <v>5</v>
@@ -3583,7 +3586,7 @@
         <v>5</v>
       </c>
       <c r="Z34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA34">
         <v>5</v>
@@ -3651,7 +3654,7 @@
         <v>7</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -3660,7 +3663,7 @@
         <v>8</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W35">
         <v>8</v>
@@ -3740,7 +3743,7 @@
         <v>5</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T36">
         <v>8</v>
@@ -3749,7 +3752,7 @@
         <v>7</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W36">
         <v>5</v>
@@ -3761,7 +3764,7 @@
         <v>5</v>
       </c>
       <c r="Z36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA36">
         <v>6</v>
@@ -3829,7 +3832,7 @@
         <v>8</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T37">
         <v>10</v>
@@ -3838,7 +3841,7 @@
         <v>10</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W37">
         <v>9</v>
@@ -3850,7 +3853,7 @@
         <v>6</v>
       </c>
       <c r="Z37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA37">
         <v>10</v>
@@ -3918,7 +3921,7 @@
         <v>8</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
         <v>8</v>
@@ -3927,7 +3930,7 @@
         <v>9</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W38">
         <v>6</v>
@@ -4007,7 +4010,7 @@
         <v>6</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T39">
         <v>7</v>
@@ -4016,7 +4019,7 @@
         <v>9</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W39">
         <v>7</v>
@@ -4028,7 +4031,7 @@
         <v>6</v>
       </c>
       <c r="Z39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA39">
         <v>6</v>
@@ -4037,7 +4040,7 @@
         <v>7</v>
       </c>
       <c r="AC39">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:29">
@@ -4096,7 +4099,7 @@
         <v>5</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T40">
         <v>5</v>
@@ -4105,7 +4108,7 @@
         <v>6</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W40">
         <v>7</v>
@@ -4185,7 +4188,7 @@
         <v>8</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T41">
         <v>8</v>
@@ -4194,7 +4197,7 @@
         <v>5</v>
       </c>
       <c r="V41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W41">
         <v>5</v>
@@ -4206,7 +4209,7 @@
         <v>5</v>
       </c>
       <c r="Z41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA41">
         <v>6</v>
@@ -4274,7 +4277,7 @@
         <v>6</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T42">
         <v>7</v>
@@ -4283,7 +4286,7 @@
         <v>7</v>
       </c>
       <c r="V42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W42">
         <v>8</v>
@@ -4295,7 +4298,7 @@
         <v>6</v>
       </c>
       <c r="Z42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA42">
         <v>6</v>
@@ -4494,7 +4497,7 @@
         <v>100</v>
       </c>
       <c r="V4">
-        <v>85</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -4562,7 +4565,7 @@
         <v>87.5</v>
       </c>
       <c r="V5">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -4630,7 +4633,7 @@
         <v>97.90000000000001</v>
       </c>
       <c r="V6">
-        <v>87.5</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -4689,7 +4692,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="S7">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="T7">
         <v>96.7</v>
@@ -4698,7 +4701,7 @@
         <v>95.8</v>
       </c>
       <c r="V7">
-        <v>90</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -4757,7 +4760,7 @@
         <v>93.8</v>
       </c>
       <c r="S8">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="T8">
         <v>100</v>
@@ -4766,7 +4769,7 @@
         <v>95.8</v>
       </c>
       <c r="V8">
-        <v>87.5</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -4834,7 +4837,7 @@
         <v>100</v>
       </c>
       <c r="V9">
-        <v>95</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -4902,7 +4905,7 @@
         <v>91.7</v>
       </c>
       <c r="V10">
-        <v>90</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -4961,7 +4964,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="S11">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="T11">
         <v>93.3</v>
@@ -4970,7 +4973,7 @@
         <v>91.7</v>
       </c>
       <c r="V11">
-        <v>90</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -5038,7 +5041,7 @@
         <v>91.7</v>
       </c>
       <c r="V12">
-        <v>95</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -5097,7 +5100,7 @@
         <v>93.8</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T13">
         <v>100</v>
@@ -5106,7 +5109,7 @@
         <v>100</v>
       </c>
       <c r="V13">
-        <v>85</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -5174,7 +5177,7 @@
         <v>91.7</v>
       </c>
       <c r="V14">
-        <v>90</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -5233,7 +5236,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="S15">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="T15">
         <v>93.3</v>
@@ -5242,7 +5245,7 @@
         <v>97.90000000000001</v>
       </c>
       <c r="V15">
-        <v>95</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -5310,7 +5313,7 @@
         <v>97.90000000000001</v>
       </c>
       <c r="V16">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -5378,7 +5381,7 @@
         <v>85.40000000000001</v>
       </c>
       <c r="V17">
-        <v>42.5</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -5446,7 +5449,7 @@
         <v>100</v>
       </c>
       <c r="V18">
-        <v>92.5</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -5514,7 +5517,7 @@
         <v>100</v>
       </c>
       <c r="V19">
-        <v>77.5</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -5573,7 +5576,7 @@
         <v>82.8</v>
       </c>
       <c r="S20">
-        <v>78.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="T20">
         <v>96.7</v>
@@ -5582,7 +5585,7 @@
         <v>85.40000000000001</v>
       </c>
       <c r="V20">
-        <v>85</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -5641,7 +5644,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="S21">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="T21">
         <v>93.3</v>
@@ -5650,7 +5653,7 @@
         <v>95.8</v>
       </c>
       <c r="V21">
-        <v>80</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -5709,7 +5712,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="S22">
-        <v>96.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="T22">
         <v>100</v>
@@ -5718,7 +5721,7 @@
         <v>93.8</v>
       </c>
       <c r="V22">
-        <v>97.5</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -5786,7 +5789,7 @@
         <v>87.5</v>
       </c>
       <c r="V23">
-        <v>92.5</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -5845,7 +5848,7 @@
         <v>31.3</v>
       </c>
       <c r="S24">
-        <v>31.3</v>
+        <v>20.8</v>
       </c>
       <c r="T24">
         <v>90</v>
@@ -5854,7 +5857,7 @@
         <v>39.6</v>
       </c>
       <c r="V24">
-        <v>20</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -5913,7 +5916,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="T25">
         <v>96.7</v>
@@ -5922,7 +5925,7 @@
         <v>93.8</v>
       </c>
       <c r="V25">
-        <v>95</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -5990,7 +5993,7 @@
         <v>97.90000000000001</v>
       </c>
       <c r="V26">
-        <v>97.5</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -6058,7 +6061,7 @@
         <v>66.7</v>
       </c>
       <c r="V27">
-        <v>85</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -6117,7 +6120,7 @@
         <v>35.9</v>
       </c>
       <c r="S28">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="T28">
         <v>90</v>
@@ -6126,7 +6129,7 @@
         <v>35.4</v>
       </c>
       <c r="V28">
-        <v>45</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -6194,7 +6197,7 @@
         <v>75</v>
       </c>
       <c r="V29">
-        <v>100</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -6262,7 +6265,7 @@
         <v>97.90000000000001</v>
       </c>
       <c r="V30">
-        <v>95</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -6321,7 +6324,7 @@
         <v>60.9</v>
       </c>
       <c r="S31">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="T31">
         <v>96.7</v>
@@ -6330,7 +6333,7 @@
         <v>91.7</v>
       </c>
       <c r="V31">
-        <v>82.5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -6389,7 +6392,7 @@
         <v>93.8</v>
       </c>
       <c r="S32">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="T32">
         <v>100</v>
@@ -6398,7 +6401,7 @@
         <v>95.8</v>
       </c>
       <c r="V32">
-        <v>95</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -6466,7 +6469,7 @@
         <v>100</v>
       </c>
       <c r="V33">
-        <v>95</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -6525,7 +6528,7 @@
         <v>62.5</v>
       </c>
       <c r="S34">
-        <v>78.09999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="T34">
         <v>88.3</v>
@@ -6534,7 +6537,7 @@
         <v>52.1</v>
       </c>
       <c r="V34">
-        <v>95</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -6670,7 +6673,7 @@
         <v>83.3</v>
       </c>
       <c r="V36">
-        <v>85</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -6729,7 +6732,7 @@
         <v>95.3</v>
       </c>
       <c r="S37">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="T37">
         <v>100</v>
@@ -6738,7 +6741,7 @@
         <v>97.90000000000001</v>
       </c>
       <c r="V37">
-        <v>95</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -6806,7 +6809,7 @@
         <v>91.7</v>
       </c>
       <c r="V38">
-        <v>95</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -6874,7 +6877,7 @@
         <v>91.7</v>
       </c>
       <c r="V39">
-        <v>92.5</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -6942,7 +6945,7 @@
         <v>95.8</v>
       </c>
       <c r="V40">
-        <v>100</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -7001,7 +7004,7 @@
         <v>78.09999999999999</v>
       </c>
       <c r="S41">
-        <v>84.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="T41">
         <v>96.7</v>
@@ -7010,7 +7013,7 @@
         <v>85.40000000000001</v>
       </c>
       <c r="V41">
-        <v>77.5</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:22">
@@ -7078,7 +7081,7 @@
         <v>91.7</v>
       </c>
       <c r="V42">
-        <v>87.5</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -7144,16 +7147,16 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F2" s="2">
-        <v>51.3</v>
+        <v>53.8</v>
       </c>
       <c r="G2" s="2">
-        <v>48.7</v>
+        <v>46.2</v>
       </c>
       <c r="H2">
         <v>5.6</v>
@@ -7167,7 +7170,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
@@ -7176,19 +7179,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F3" s="2">
-        <v>56.4</v>
+        <v>61.5</v>
       </c>
       <c r="G3" s="2">
-        <v>43.6</v>
+        <v>38.5</v>
       </c>
       <c r="H3">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7199,7 +7202,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
@@ -7208,19 +7211,19 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>61.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>38.5</v>
+        <v>17.9</v>
       </c>
       <c r="H4">
-        <v>5.8</v>
+        <v>6.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7231,7 +7234,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
@@ -7240,19 +7243,19 @@
         <v>39</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2">
-        <v>82.09999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>17.9</v>
+        <v>15.4</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7263,7 +7266,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
@@ -7284,7 +7287,7 @@
         <v>15.4</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7295,7 +7298,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>70</v>
@@ -7304,16 +7307,16 @@
         <v>39</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2">
-        <v>84.59999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="G7" s="2">
-        <v>15.4</v>
+        <v>12.8</v>
       </c>
       <c r="H7">
         <v>6.9</v>
@@ -7418,7 +7421,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7450,22 +7453,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920216</v>
+        <v>23330051920214</v>
       </c>
       <c r="B2" t="s">
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7473,16 +7476,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920216</v>
+        <v>23330051920214</v>
       </c>
       <c r="B3" t="s">
         <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -7496,22 +7499,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920248</v>
+        <v>23330051920254</v>
       </c>
       <c r="B4" t="s">
         <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7519,22 +7522,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920248</v>
+        <v>23330051920254</v>
       </c>
       <c r="B5" t="s">
         <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7542,19 +7545,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920357</v>
+        <v>23330051920239</v>
       </c>
       <c r="B6" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
         <v>66</v>
@@ -7565,16 +7568,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920357</v>
+        <v>23330051920239</v>
       </c>
       <c r="B7" t="s">
         <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -7588,22 +7591,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920277</v>
+        <v>23330051920226</v>
       </c>
       <c r="B8" t="s">
         <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7611,22 +7614,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920277</v>
+        <v>23330051920215</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7634,16 +7637,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920226</v>
+        <v>23330051920216</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
@@ -7657,22 +7660,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920215</v>
+        <v>23330051920242</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7680,22 +7683,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920227</v>
+        <v>23330051920248</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7703,19 +7706,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920252</v>
+        <v>23330051920328</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
         <v>66</v>
@@ -7726,22 +7729,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920254</v>
+        <v>23330051920357</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -7749,16 +7752,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920256</v>
+        <v>23330051920280</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
@@ -7767,29 +7770,6 @@
         <v>65</v>
       </c>
       <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920280</v>
-      </c>
-      <c r="B16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D16" t="s">
-        <v>105</v>
-      </c>
-      <c r="E16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1BV - Estadisticos 20231.xlsx
+++ b/grupos/1BV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="142">
   <si>
     <t>Materia</t>
   </si>
@@ -56,6 +56,9 @@
     <t>Pensamiento matemático I</t>
   </si>
   <si>
+    <t>Recursos socioemocionales I</t>
+  </si>
+  <si>
     <t>Nombre</t>
   </si>
   <si>
@@ -212,9 +215,6 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>Recursos socioemocionales I</t>
-  </si>
-  <si>
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
@@ -248,73 +248,124 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CALVA</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>FUENTES</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>ALCANTARA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>DAMIAN</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>FERRER</t>
+  </si>
+  <si>
+    <t>SOSA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>CANDELARIO</t>
+  </si>
+  <si>
     <t>ALVAREZ</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CALVA</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>FUENTES</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>BERMUDEZ</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>DAMIAN</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>CLAUDIA RUBI</t>
-  </si>
-  <si>
-    <t>MIGUEL ENRIQUE</t>
-  </si>
-  <si>
-    <t>NURIA BELEN</t>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>MONTERROSAS</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
   </si>
   <si>
     <t>YAMILETH</t>
@@ -323,22 +374,76 @@
     <t>LORENA</t>
   </si>
   <si>
+    <t>VALERY MIRANDA</t>
+  </si>
+  <si>
+    <t>VIVIANA JOSELIN</t>
+  </si>
+  <si>
+    <t>GISELA GUADALUPE</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>ANGEL ABRAHAM</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>INGRID ISABEL</t>
+  </si>
+  <si>
+    <t>VANESA</t>
+  </si>
+  <si>
     <t>ANGEL JESUS</t>
   </si>
   <si>
-    <t>VALERY MIRANDA</t>
-  </si>
-  <si>
-    <t>VIVIANA JOSELIN</t>
-  </si>
-  <si>
-    <t>GISELA GUADALUPE</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>ANGEL ABRAHAM</t>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>LUZ YESENIA</t>
+  </si>
+  <si>
+    <t>ANDREA</t>
+  </si>
+  <si>
+    <t>SILVANA</t>
+  </si>
+  <si>
+    <t>XIMENA ISABEL</t>
+  </si>
+  <si>
+    <t>DANNA PAOLA</t>
+  </si>
+  <si>
+    <t>BRISEIDA</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>SAMANTHA BETHANY</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>DORIAN</t>
+  </si>
+  <si>
+    <t>VICTORIA VIANNEY</t>
+  </si>
+  <si>
+    <t>ANEL</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
   </si>
 </sst>
 </file>
@@ -700,13 +805,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AG42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:33">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -717,35 +822,39 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-      <c r="W1" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
+      <c r="Z1" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
-    </row>
-    <row r="2" spans="1:29">
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+    </row>
+    <row r="2" spans="1:33">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -771,77 +880,89 @@
         <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="W2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="Y2" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:29">
+      <c r="AG2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33">
       <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>6</v>
@@ -865,72 +986,84 @@
         <v>6</v>
       </c>
       <c r="I4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC4">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD4">
+        <v>7</v>
+      </c>
+      <c r="AE4">
+        <v>8</v>
+      </c>
+      <c r="AF4">
+        <v>7</v>
+      </c>
+      <c r="AG4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>5</v>
@@ -954,72 +1087,84 @@
         <v>5</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J5">
         <v>7</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>5</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O5">
         <v>5</v>
       </c>
       <c r="P5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA5">
         <v>6</v>
       </c>
       <c r="AB5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD5">
+        <v>6</v>
+      </c>
+      <c r="AE5">
+        <v>5</v>
+      </c>
+      <c r="AF5">
+        <v>5</v>
+      </c>
+      <c r="AG5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -1046,31 +1191,31 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S6">
         <v>8</v>
@@ -1079,36 +1224,48 @@
         <v>6</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>6</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD6">
+        <v>6</v>
+      </c>
+      <c r="AE6">
+        <v>7</v>
+      </c>
+      <c r="AF6">
+        <v>6</v>
+      </c>
+      <c r="AG6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -1132,58 +1289,58 @@
         <v>6</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>6</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>6</v>
       </c>
       <c r="S7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA7">
         <v>6</v>
@@ -1192,12 +1349,24 @@
         <v>6</v>
       </c>
       <c r="AC7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD7">
+        <v>6</v>
+      </c>
+      <c r="AE7">
+        <v>6</v>
+      </c>
+      <c r="AF7">
+        <v>5</v>
+      </c>
+      <c r="AG7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -1221,31 +1390,31 @@
         <v>5</v>
       </c>
       <c r="I8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>6</v>
       </c>
       <c r="L8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>6</v>
@@ -1254,22 +1423,22 @@
         <v>8</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z8">
         <v>7</v>
@@ -1278,15 +1447,27 @@
         <v>7</v>
       </c>
       <c r="AB8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD8">
+        <v>7</v>
+      </c>
+      <c r="AE8">
+        <v>7</v>
+      </c>
+      <c r="AF8">
+        <v>5</v>
+      </c>
+      <c r="AG8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -1313,10 +1494,10 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L9">
         <v>6</v>
@@ -1325,31 +1506,31 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P9">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>9</v>
@@ -1358,24 +1539,36 @@
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD9">
+        <v>8</v>
+      </c>
+      <c r="AE9">
+        <v>8</v>
+      </c>
+      <c r="AF9">
+        <v>6</v>
+      </c>
+      <c r="AG9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>7</v>
@@ -1402,69 +1595,81 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>7</v>
       </c>
       <c r="N10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
       <c r="P10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S10">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z10">
         <v>8</v>
       </c>
       <c r="AA10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD10">
+        <v>7</v>
+      </c>
+      <c r="AE10">
+        <v>7</v>
+      </c>
+      <c r="AF10">
+        <v>6</v>
+      </c>
+      <c r="AG10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>5</v>
@@ -1488,52 +1693,52 @@
         <v>6</v>
       </c>
       <c r="I11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y11">
         <v>5</v>
@@ -1545,15 +1750,27 @@
         <v>7</v>
       </c>
       <c r="AB11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD11">
+        <v>7</v>
+      </c>
+      <c r="AE11">
+        <v>7</v>
+      </c>
+      <c r="AF11">
+        <v>5</v>
+      </c>
+      <c r="AG11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>7</v>
@@ -1577,72 +1794,84 @@
         <v>6</v>
       </c>
       <c r="I12">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N12">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O12">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>7</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB12">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AC12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD12">
+        <v>6</v>
+      </c>
+      <c r="AE12">
+        <v>9</v>
+      </c>
+      <c r="AF12">
+        <v>5</v>
+      </c>
+      <c r="AG12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>7</v>
@@ -1666,72 +1895,84 @@
         <v>6</v>
       </c>
       <c r="I13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K13">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>7</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA13">
         <v>8</v>
       </c>
       <c r="AB13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC13">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD13">
+        <v>8</v>
+      </c>
+      <c r="AE13">
+        <v>7</v>
+      </c>
+      <c r="AF13">
+        <v>6</v>
+      </c>
+      <c r="AG13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>7</v>
@@ -1758,58 +1999,58 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L14">
         <v>5</v>
       </c>
       <c r="M14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AA14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB14">
         <v>6</v>
@@ -1817,10 +2058,22 @@
       <c r="AC14">
         <v>6</v>
       </c>
-    </row>
-    <row r="15" spans="1:29">
+      <c r="AD14">
+        <v>9</v>
+      </c>
+      <c r="AE14">
+        <v>6</v>
+      </c>
+      <c r="AF14">
+        <v>6</v>
+      </c>
+      <c r="AG14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>6</v>
@@ -1844,72 +2097,84 @@
         <v>6</v>
       </c>
       <c r="I15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L15">
+        <v>5</v>
+      </c>
+      <c r="M15">
         <v>4</v>
       </c>
-      <c r="M15">
-        <v>5</v>
-      </c>
       <c r="N15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>8</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC15">
         <v>6</v>
       </c>
-    </row>
-    <row r="16" spans="1:29">
+      <c r="AD15">
+        <v>6</v>
+      </c>
+      <c r="AE15">
+        <v>6</v>
+      </c>
+      <c r="AF15">
+        <v>6</v>
+      </c>
+      <c r="AG15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>8</v>
@@ -1936,69 +2201,81 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N16">
         <v>8</v>
       </c>
       <c r="O16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S16">
         <v>9</v>
       </c>
       <c r="T16">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U16">
         <v>9</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>9</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA16">
         <v>9</v>
       </c>
       <c r="AB16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD16">
+        <v>9</v>
+      </c>
+      <c r="AE16">
+        <v>8</v>
+      </c>
+      <c r="AF16">
+        <v>6</v>
+      </c>
+      <c r="AG16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>5</v>
@@ -2022,20 +2299,20 @@
         <v>5</v>
       </c>
       <c r="I17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L17">
+        <v>5</v>
+      </c>
+      <c r="M17">
         <v>4</v>
       </c>
-      <c r="M17">
-        <v>5</v>
-      </c>
       <c r="N17">
         <v>5</v>
       </c>
@@ -2043,51 +2320,63 @@
         <v>5</v>
       </c>
       <c r="P17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC17">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:29">
+      <c r="AD17">
+        <v>6</v>
+      </c>
+      <c r="AE17">
+        <v>6</v>
+      </c>
+      <c r="AF17">
+        <v>5</v>
+      </c>
+      <c r="AG17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>6</v>
@@ -2114,69 +2403,81 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>6</v>
       </c>
       <c r="M18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O18">
         <v>6</v>
       </c>
       <c r="P18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA18">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC18">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD18">
+        <v>9</v>
+      </c>
+      <c r="AE18">
+        <v>7</v>
+      </c>
+      <c r="AF18">
+        <v>6</v>
+      </c>
+      <c r="AG18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>5</v>
@@ -2203,34 +2504,34 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M19">
         <v>5</v>
       </c>
       <c r="N19">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <v>8</v>
@@ -2239,33 +2540,45 @@
         <v>9</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC19">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD19">
+        <v>6</v>
+      </c>
+      <c r="AE19">
+        <v>7</v>
+      </c>
+      <c r="AF19">
+        <v>6</v>
+      </c>
+      <c r="AG19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>7</v>
@@ -2289,13 +2602,13 @@
         <v>6</v>
       </c>
       <c r="I20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L20">
         <v>5</v>
@@ -2304,7 +2617,7 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O20">
         <v>6</v>
@@ -2313,48 +2626,60 @@
         <v>6</v>
       </c>
       <c r="Q20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S20">
         <v>8</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U20">
         <v>8</v>
       </c>
       <c r="V20">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y20">
         <v>5</v>
       </c>
       <c r="Z20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA20">
         <v>7</v>
       </c>
       <c r="AB20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD20">
+        <v>7</v>
+      </c>
+      <c r="AE20">
+        <v>6</v>
+      </c>
+      <c r="AF20">
+        <v>5</v>
+      </c>
+      <c r="AG20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>7</v>
@@ -2381,69 +2706,81 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K21">
         <v>7</v>
       </c>
       <c r="L21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M21">
         <v>6</v>
       </c>
       <c r="N21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R21">
+        <v>7</v>
+      </c>
+      <c r="S21">
+        <v>8</v>
+      </c>
+      <c r="T21">
         <v>4</v>
       </c>
-      <c r="S21">
-        <v>8</v>
-      </c>
-      <c r="T21">
-        <v>9</v>
-      </c>
       <c r="U21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC21">
         <v>6</v>
       </c>
-    </row>
-    <row r="22" spans="1:29">
+      <c r="AD21">
+        <v>7</v>
+      </c>
+      <c r="AE21">
+        <v>7</v>
+      </c>
+      <c r="AF21">
+        <v>6</v>
+      </c>
+      <c r="AG21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>5</v>
@@ -2467,72 +2804,84 @@
         <v>5</v>
       </c>
       <c r="I22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N22">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O22">
         <v>5</v>
       </c>
       <c r="P22">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S22">
         <v>8</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z22">
         <v>7</v>
       </c>
       <c r="AA22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC22">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD22">
+        <v>8</v>
+      </c>
+      <c r="AE22">
+        <v>7</v>
+      </c>
+      <c r="AF22">
+        <v>6</v>
+      </c>
+      <c r="AG22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23">
         <v>6</v>
@@ -2559,13 +2908,13 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K23">
         <v>6</v>
       </c>
       <c r="L23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M23">
         <v>5</v>
@@ -2577,51 +2926,63 @@
         <v>5</v>
       </c>
       <c r="P23">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA23">
         <v>6</v>
       </c>
       <c r="AB23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD23">
+        <v>6</v>
+      </c>
+      <c r="AE23">
+        <v>7</v>
+      </c>
+      <c r="AF23">
+        <v>5</v>
+      </c>
+      <c r="AG23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24">
         <v>5</v>
@@ -2645,17 +3006,17 @@
         <v>5</v>
       </c>
       <c r="I24">
+        <v>10</v>
+      </c>
+      <c r="J24">
         <v>4</v>
       </c>
-      <c r="J24">
-        <v>5</v>
-      </c>
       <c r="K24">
+        <v>5</v>
+      </c>
+      <c r="L24">
         <v>0</v>
       </c>
-      <c r="L24">
-        <v>5</v>
-      </c>
       <c r="M24">
         <v>5</v>
       </c>
@@ -2666,20 +3027,20 @@
         <v>5</v>
       </c>
       <c r="P24">
+        <v>5</v>
+      </c>
+      <c r="Q24">
+        <v>5</v>
+      </c>
+      <c r="R24">
         <v>3</v>
       </c>
-      <c r="Q24">
-        <v>5</v>
-      </c>
-      <c r="R24">
+      <c r="S24">
+        <v>5</v>
+      </c>
+      <c r="T24">
         <v>0</v>
       </c>
-      <c r="S24">
-        <v>5</v>
-      </c>
-      <c r="T24">
-        <v>5</v>
-      </c>
       <c r="U24">
         <v>5</v>
       </c>
@@ -2707,10 +3068,22 @@
       <c r="AC24">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:29">
+      <c r="AD24">
+        <v>5</v>
+      </c>
+      <c r="AE24">
+        <v>5</v>
+      </c>
+      <c r="AF24">
+        <v>5</v>
+      </c>
+      <c r="AG24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>6</v>
@@ -2737,55 +3110,55 @@
         <v>10</v>
       </c>
       <c r="J25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>7</v>
       </c>
       <c r="S25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25">
         <v>7</v>
       </c>
       <c r="U25">
+        <v>10</v>
+      </c>
+      <c r="V25">
+        <v>7</v>
+      </c>
+      <c r="W25">
         <v>4</v>
       </c>
-      <c r="V25">
-        <v>6</v>
-      </c>
-      <c r="W25">
-        <v>8</v>
-      </c>
       <c r="X25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA25">
         <v>7</v>
@@ -2794,12 +3167,24 @@
         <v>7</v>
       </c>
       <c r="AC25">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD25">
+        <v>7</v>
+      </c>
+      <c r="AE25">
+        <v>7</v>
+      </c>
+      <c r="AF25">
+        <v>6</v>
+      </c>
+      <c r="AG25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26">
         <v>6</v>
@@ -2826,69 +3211,81 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K26">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T26">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA26">
         <v>8</v>
       </c>
       <c r="AB26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC26">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD26">
+        <v>8</v>
+      </c>
+      <c r="AE26">
+        <v>7</v>
+      </c>
+      <c r="AF26">
+        <v>6</v>
+      </c>
+      <c r="AG26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>7</v>
@@ -2912,72 +3309,84 @@
         <v>6</v>
       </c>
       <c r="I27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L27">
         <v>6</v>
       </c>
       <c r="M27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P27">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q27">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>4</v>
       </c>
       <c r="S27">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>5</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y27">
         <v>5</v>
       </c>
       <c r="Z27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB27">
         <v>5</v>
       </c>
       <c r="AC27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD27">
+        <v>5</v>
+      </c>
+      <c r="AE27">
+        <v>5</v>
+      </c>
+      <c r="AF27">
+        <v>5</v>
+      </c>
+      <c r="AG27">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:33">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>7</v>
@@ -3001,17 +3410,17 @@
         <v>6</v>
       </c>
       <c r="I28">
+        <v>10</v>
+      </c>
+      <c r="J28">
         <v>4</v>
       </c>
-      <c r="J28">
-        <v>5</v>
-      </c>
       <c r="K28">
+        <v>5</v>
+      </c>
+      <c r="L28">
         <v>0</v>
       </c>
-      <c r="L28">
-        <v>5</v>
-      </c>
       <c r="M28">
         <v>5</v>
       </c>
@@ -3022,20 +3431,20 @@
         <v>5</v>
       </c>
       <c r="P28">
+        <v>5</v>
+      </c>
+      <c r="Q28">
+        <v>5</v>
+      </c>
+      <c r="R28">
         <v>3</v>
       </c>
-      <c r="Q28">
-        <v>5</v>
-      </c>
-      <c r="R28">
+      <c r="S28">
+        <v>5</v>
+      </c>
+      <c r="T28">
         <v>4</v>
       </c>
-      <c r="S28">
-        <v>5</v>
-      </c>
-      <c r="T28">
-        <v>5</v>
-      </c>
       <c r="U28">
         <v>5</v>
       </c>
@@ -3046,7 +3455,7 @@
         <v>5</v>
       </c>
       <c r="X28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y28">
         <v>5</v>
@@ -3055,7 +3464,7 @@
         <v>5</v>
       </c>
       <c r="AA28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB28">
         <v>5</v>
@@ -3063,10 +3472,22 @@
       <c r="AC28">
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="1:29">
+      <c r="AD28">
+        <v>5</v>
+      </c>
+      <c r="AE28">
+        <v>5</v>
+      </c>
+      <c r="AF28">
+        <v>5</v>
+      </c>
+      <c r="AG28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29">
         <v>5</v>
@@ -3090,16 +3511,16 @@
         <v>6</v>
       </c>
       <c r="I29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M29">
         <v>5</v>
@@ -3111,22 +3532,22 @@
         <v>5</v>
       </c>
       <c r="P29">
+        <v>5</v>
+      </c>
+      <c r="Q29">
+        <v>10</v>
+      </c>
+      <c r="R29">
         <v>4</v>
       </c>
-      <c r="Q29">
-        <v>6</v>
-      </c>
-      <c r="R29">
-        <v>7</v>
-      </c>
       <c r="S29">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U29">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V29">
         <v>5</v>
@@ -3135,27 +3556,39 @@
         <v>5</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y29">
         <v>5</v>
       </c>
       <c r="Z29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB29">
         <v>5</v>
       </c>
       <c r="AC29">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD29">
+        <v>5</v>
+      </c>
+      <c r="AE29">
+        <v>5</v>
+      </c>
+      <c r="AF29">
+        <v>5</v>
+      </c>
+      <c r="AG29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30">
         <v>7</v>
@@ -3182,69 +3615,81 @@
         <v>10</v>
       </c>
       <c r="J30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K30">
         <v>6</v>
       </c>
       <c r="L30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M30">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N30">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O30">
         <v>6</v>
       </c>
       <c r="P30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U30">
         <v>9</v>
       </c>
       <c r="V30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z30">
         <v>8</v>
       </c>
       <c r="AA30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB30">
         <v>7</v>
       </c>
       <c r="AC30">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD30">
+        <v>8</v>
+      </c>
+      <c r="AE30">
+        <v>7</v>
+      </c>
+      <c r="AF30">
+        <v>6</v>
+      </c>
+      <c r="AG30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31">
         <v>6</v>
@@ -3268,20 +3713,20 @@
         <v>5</v>
       </c>
       <c r="I31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K31">
         <v>5</v>
       </c>
       <c r="L31">
+        <v>5</v>
+      </c>
+      <c r="M31">
         <v>4</v>
       </c>
-      <c r="M31">
-        <v>5</v>
-      </c>
       <c r="N31">
         <v>5</v>
       </c>
@@ -3292,17 +3737,17 @@
         <v>5</v>
       </c>
       <c r="Q31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R31">
+        <v>5</v>
+      </c>
+      <c r="S31">
+        <v>7</v>
+      </c>
+      <c r="T31">
         <v>0</v>
       </c>
-      <c r="S31">
-        <v>7</v>
-      </c>
-      <c r="T31">
-        <v>5</v>
-      </c>
       <c r="U31">
         <v>7</v>
       </c>
@@ -3310,30 +3755,42 @@
         <v>5</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y31">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC31">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="1:29">
+      <c r="AD31">
+        <v>5</v>
+      </c>
+      <c r="AE31">
+        <v>6</v>
+      </c>
+      <c r="AF31">
+        <v>5</v>
+      </c>
+      <c r="AG31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32">
         <v>7</v>
@@ -3360,69 +3817,81 @@
         <v>10</v>
       </c>
       <c r="J32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K32">
         <v>6</v>
       </c>
       <c r="L32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M32">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O32">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P32">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB32">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC32">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD32">
+        <v>9</v>
+      </c>
+      <c r="AE32">
+        <v>8</v>
+      </c>
+      <c r="AF32">
+        <v>6</v>
+      </c>
+      <c r="AG32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33">
       <c r="A33" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B33">
         <v>9</v>
@@ -3449,25 +3918,25 @@
         <v>10</v>
       </c>
       <c r="J33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L33">
         <v>8</v>
       </c>
       <c r="M33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N33">
         <v>10</v>
       </c>
       <c r="O33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q33">
         <v>10</v>
@@ -3485,33 +3954,45 @@
         <v>10</v>
       </c>
       <c r="V33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W33">
         <v>10</v>
       </c>
       <c r="X33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA33">
         <v>10</v>
       </c>
       <c r="AB33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC33">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD33">
+        <v>10</v>
+      </c>
+      <c r="AE33">
+        <v>10</v>
+      </c>
+      <c r="AF33">
+        <v>7</v>
+      </c>
+      <c r="AG33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33">
       <c r="A34" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B34">
         <v>5</v>
@@ -3535,19 +4016,19 @@
         <v>6</v>
       </c>
       <c r="I34">
+        <v>10</v>
+      </c>
+      <c r="J34">
         <v>4</v>
       </c>
-      <c r="J34">
-        <v>8</v>
-      </c>
       <c r="K34">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L34">
         <v>4</v>
       </c>
       <c r="M34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N34">
         <v>5</v>
@@ -3556,22 +4037,22 @@
         <v>5</v>
       </c>
       <c r="P34">
+        <v>5</v>
+      </c>
+      <c r="Q34">
+        <v>5</v>
+      </c>
+      <c r="R34">
         <v>4</v>
       </c>
-      <c r="Q34">
-        <v>7</v>
-      </c>
-      <c r="R34">
+      <c r="S34">
+        <v>7</v>
+      </c>
+      <c r="T34">
         <v>3</v>
       </c>
-      <c r="S34">
-        <v>9</v>
-      </c>
-      <c r="T34">
-        <v>5</v>
-      </c>
       <c r="U34">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V34">
         <v>5</v>
@@ -3580,27 +4061,39 @@
         <v>5</v>
       </c>
       <c r="X34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y34">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB34">
         <v>5</v>
       </c>
       <c r="AC34">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD34">
+        <v>5</v>
+      </c>
+      <c r="AE34">
+        <v>5</v>
+      </c>
+      <c r="AF34">
+        <v>5</v>
+      </c>
+      <c r="AG34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:33">
       <c r="A35" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B35">
         <v>7</v>
@@ -3624,72 +4117,84 @@
         <v>6</v>
       </c>
       <c r="I35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J35">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K35">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O35">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q35">
         <v>10</v>
       </c>
       <c r="R35">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W35">
         <v>8</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC35">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD35">
+        <v>8</v>
+      </c>
+      <c r="AE35">
+        <v>7</v>
+      </c>
+      <c r="AF35">
+        <v>6</v>
+      </c>
+      <c r="AG35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33">
       <c r="A36" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B36">
         <v>7</v>
@@ -3713,19 +4218,19 @@
         <v>6</v>
       </c>
       <c r="I36">
+        <v>10</v>
+      </c>
+      <c r="J36">
         <v>4</v>
       </c>
-      <c r="J36">
-        <v>6</v>
-      </c>
       <c r="K36">
+        <v>6</v>
+      </c>
+      <c r="L36">
         <v>4</v>
       </c>
-      <c r="L36">
-        <v>6</v>
-      </c>
       <c r="M36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N36">
         <v>5</v>
@@ -3734,51 +4239,63 @@
         <v>5</v>
       </c>
       <c r="P36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q36">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T36">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U36">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V36">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y36">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC36">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD36">
+        <v>6</v>
+      </c>
+      <c r="AE36">
+        <v>6</v>
+      </c>
+      <c r="AF36">
+        <v>5</v>
+      </c>
+      <c r="AG36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:33">
       <c r="A37" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <v>8</v>
@@ -3802,72 +4319,84 @@
         <v>6</v>
       </c>
       <c r="I37">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J37">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K37">
         <v>6</v>
       </c>
       <c r="L37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M37">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N37">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O37">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R37">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S37">
         <v>9</v>
       </c>
       <c r="T37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V37">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X37">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y37">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z37">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB37">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AC37">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD37">
+        <v>10</v>
+      </c>
+      <c r="AE37">
+        <v>9</v>
+      </c>
+      <c r="AF37">
+        <v>6</v>
+      </c>
+      <c r="AG37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:33">
       <c r="A38" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B38">
         <v>6</v>
@@ -3891,72 +4420,84 @@
         <v>6</v>
       </c>
       <c r="I38">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K38">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N38">
         <v>5</v>
       </c>
       <c r="O38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q38">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R38">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="S38">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T38">
         <v>8</v>
       </c>
       <c r="U38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V38">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W38">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y38">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z38">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB38">
         <v>7</v>
       </c>
       <c r="AC38">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD38">
+        <v>6</v>
+      </c>
+      <c r="AE38">
+        <v>7</v>
+      </c>
+      <c r="AF38">
+        <v>6</v>
+      </c>
+      <c r="AG38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:33">
       <c r="A39" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B39">
         <v>7</v>
@@ -3980,13 +4521,13 @@
         <v>6</v>
       </c>
       <c r="I39">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K39">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L39">
         <v>5</v>
@@ -4001,10 +4542,10 @@
         <v>5</v>
       </c>
       <c r="P39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R39">
         <v>6</v>
@@ -4013,7 +4554,7 @@
         <v>9</v>
       </c>
       <c r="T39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U39">
         <v>9</v>
@@ -4022,30 +4563,42 @@
         <v>7</v>
       </c>
       <c r="W39">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA39">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC39">
         <v>6</v>
       </c>
-    </row>
-    <row r="40" spans="1:29">
+      <c r="AD39">
+        <v>6</v>
+      </c>
+      <c r="AE39">
+        <v>7</v>
+      </c>
+      <c r="AF39">
+        <v>6</v>
+      </c>
+      <c r="AG39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:33">
       <c r="A40" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B40">
         <v>5</v>
@@ -4072,69 +4625,81 @@
         <v>10</v>
       </c>
       <c r="J40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K40">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L40">
         <v>5</v>
       </c>
       <c r="M40">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N40">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S40">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T40">
         <v>5</v>
       </c>
       <c r="U40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V40">
         <v>5</v>
       </c>
       <c r="W40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X40">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y40">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC40">
         <v>5</v>
       </c>
-    </row>
-    <row r="41" spans="1:29">
+      <c r="AD40">
+        <v>7</v>
+      </c>
+      <c r="AE40">
+        <v>6</v>
+      </c>
+      <c r="AF40">
+        <v>5</v>
+      </c>
+      <c r="AG40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:33">
       <c r="A41" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B41">
         <v>5</v>
@@ -4158,19 +4723,19 @@
         <v>5</v>
       </c>
       <c r="I41">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L41">
         <v>4</v>
       </c>
       <c r="M41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N41">
         <v>5</v>
@@ -4179,25 +4744,25 @@
         <v>5</v>
       </c>
       <c r="P41">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q41">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R41">
         <v>8</v>
       </c>
       <c r="S41">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T41">
         <v>8</v>
       </c>
       <c r="U41">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V41">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W41">
         <v>5</v>
@@ -4209,21 +4774,33 @@
         <v>5</v>
       </c>
       <c r="Z41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB41">
         <v>5</v>
       </c>
       <c r="AC41">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD41">
+        <v>6</v>
+      </c>
+      <c r="AE41">
+        <v>5</v>
+      </c>
+      <c r="AF41">
+        <v>5</v>
+      </c>
+      <c r="AG41">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:33">
       <c r="A42" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B42">
         <v>6</v>
@@ -4250,10 +4827,10 @@
         <v>10</v>
       </c>
       <c r="J42">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L42">
         <v>6</v>
@@ -4262,60 +4839,72 @@
         <v>6</v>
       </c>
       <c r="N42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O42">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P42">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q42">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R42">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S42">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U42">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V42">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB42">
         <v>6</v>
       </c>
       <c r="AC42">
+        <v>7</v>
+      </c>
+      <c r="AD42">
+        <v>6</v>
+      </c>
+      <c r="AE42">
+        <v>6</v>
+      </c>
+      <c r="AF42">
+        <v>5</v>
+      </c>
+      <c r="AG42">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="P1:V1"/>
-    <mergeCell ref="W1:AC1"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="R1:Y1"/>
+    <mergeCell ref="Z1:AG1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4323,16 +4912,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V42"/>
+  <dimension ref="A1:Y42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:25">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -4340,26 +4929,29 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
+      <c r="R1" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:22">
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+    </row>
+    <row r="2" spans="1:25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -4385,56 +4977,65 @@
         <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:22">
+      <c r="Y2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
       <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>80</v>
@@ -4458,51 +5059,60 @@
         <v>68.2</v>
       </c>
       <c r="I4">
+        <v>100</v>
+      </c>
+      <c r="J4">
         <v>85</v>
       </c>
-      <c r="J4">
-        <v>100</v>
-      </c>
       <c r="K4">
+        <v>100</v>
+      </c>
+      <c r="L4">
         <v>90.90000000000001</v>
       </c>
-      <c r="L4">
-        <v>100</v>
-      </c>
       <c r="M4">
+        <v>100</v>
+      </c>
+      <c r="N4">
         <v>95</v>
       </c>
-      <c r="N4">
-        <v>100</v>
-      </c>
       <c r="O4">
+        <v>100</v>
+      </c>
+      <c r="P4">
         <v>85</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
+        <v>100</v>
+      </c>
+      <c r="R4">
         <v>90</v>
       </c>
-      <c r="Q4">
-        <v>100</v>
-      </c>
-      <c r="R4">
+      <c r="S4">
+        <v>100</v>
+      </c>
+      <c r="T4">
         <v>90.59999999999999</v>
       </c>
-      <c r="S4">
-        <v>100</v>
-      </c>
-      <c r="T4">
+      <c r="U4">
+        <v>100</v>
+      </c>
+      <c r="V4">
         <v>96.7</v>
       </c>
-      <c r="U4">
-        <v>100</v>
-      </c>
-      <c r="V4">
+      <c r="W4">
+        <v>100</v>
+      </c>
+      <c r="X4">
         <v>88.90000000000001</v>
       </c>
-    </row>
-    <row r="5" spans="1:22">
+      <c r="Y4">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>80</v>
@@ -4529,48 +5139,57 @@
         <v>80</v>
       </c>
       <c r="J5">
+        <v>80</v>
+      </c>
+      <c r="K5">
         <v>83.3</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>86.40000000000001</v>
       </c>
-      <c r="L5">
-        <v>100</v>
-      </c>
       <c r="M5">
         <v>100</v>
       </c>
       <c r="N5">
+        <v>100</v>
+      </c>
+      <c r="O5">
         <v>84.40000000000001</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>75</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
+        <v>60</v>
+      </c>
+      <c r="R5">
         <v>83.3</v>
       </c>
-      <c r="Q5">
+      <c r="S5">
         <v>88.90000000000001</v>
       </c>
-      <c r="R5">
+      <c r="T5">
         <v>84.40000000000001</v>
       </c>
-      <c r="S5">
-        <v>100</v>
-      </c>
-      <c r="T5">
-        <v>100</v>
-      </c>
       <c r="U5">
+        <v>100</v>
+      </c>
+      <c r="V5">
+        <v>100</v>
+      </c>
+      <c r="W5">
         <v>87.5</v>
       </c>
-      <c r="V5">
+      <c r="X5">
         <v>81</v>
       </c>
-    </row>
-    <row r="6" spans="1:22">
+      <c r="Y5">
+        <v>42.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>80</v>
@@ -4594,51 +5213,60 @@
         <v>68.2</v>
       </c>
       <c r="I6">
+        <v>100</v>
+      </c>
+      <c r="J6">
         <v>90</v>
       </c>
-      <c r="J6">
-        <v>100</v>
-      </c>
       <c r="K6">
+        <v>100</v>
+      </c>
+      <c r="L6">
         <v>86.40000000000001</v>
       </c>
-      <c r="L6">
-        <v>100</v>
-      </c>
       <c r="M6">
         <v>100</v>
       </c>
       <c r="N6">
+        <v>100</v>
+      </c>
+      <c r="O6">
         <v>96.90000000000001</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>87.5</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
+        <v>100</v>
+      </c>
+      <c r="R6">
         <v>90</v>
       </c>
-      <c r="Q6">
-        <v>100</v>
-      </c>
-      <c r="R6">
+      <c r="S6">
+        <v>100</v>
+      </c>
+      <c r="T6">
         <v>90.59999999999999</v>
       </c>
-      <c r="S6">
-        <v>100</v>
-      </c>
-      <c r="T6">
-        <v>100</v>
-      </c>
       <c r="U6">
+        <v>100</v>
+      </c>
+      <c r="V6">
+        <v>100</v>
+      </c>
+      <c r="W6">
         <v>97.90000000000001</v>
       </c>
-      <c r="V6">
+      <c r="X6">
         <v>92.09999999999999</v>
       </c>
-    </row>
-    <row r="7" spans="1:22">
+      <c r="Y6">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>80</v>
@@ -4662,51 +5290,60 @@
         <v>86.40000000000001</v>
       </c>
       <c r="I7">
+        <v>100</v>
+      </c>
+      <c r="J7">
         <v>85</v>
       </c>
-      <c r="J7">
-        <v>100</v>
-      </c>
       <c r="K7">
+        <v>100</v>
+      </c>
+      <c r="L7">
         <v>88.59999999999999</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>90.59999999999999</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>95</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>96.90000000000001</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>90</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
+        <v>100</v>
+      </c>
+      <c r="R7">
         <v>86.7</v>
       </c>
-      <c r="Q7">
-        <v>100</v>
-      </c>
-      <c r="R7">
+      <c r="S7">
+        <v>100</v>
+      </c>
+      <c r="T7">
         <v>89.09999999999999</v>
       </c>
-      <c r="S7">
+      <c r="U7">
         <v>93.8</v>
       </c>
-      <c r="T7">
+      <c r="V7">
         <v>96.7</v>
       </c>
-      <c r="U7">
+      <c r="W7">
         <v>95.8</v>
       </c>
-      <c r="V7">
+      <c r="X7">
         <v>90.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:22">
+      <c r="Y7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>90</v>
@@ -4730,51 +5367,60 @@
         <v>68.2</v>
       </c>
       <c r="I8">
+        <v>100</v>
+      </c>
+      <c r="J8">
         <v>95</v>
       </c>
-      <c r="J8">
-        <v>100</v>
-      </c>
       <c r="K8">
+        <v>100</v>
+      </c>
+      <c r="L8">
         <v>95.5</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>96.90000000000001</v>
       </c>
-      <c r="M8">
-        <v>100</v>
-      </c>
       <c r="N8">
+        <v>100</v>
+      </c>
+      <c r="O8">
         <v>93.8</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>87.5</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
+        <v>100</v>
+      </c>
+      <c r="R8">
         <v>93.3</v>
       </c>
-      <c r="Q8">
-        <v>100</v>
-      </c>
-      <c r="R8">
+      <c r="S8">
+        <v>100</v>
+      </c>
+      <c r="T8">
         <v>93.8</v>
-      </c>
-      <c r="S8">
-        <v>95.8</v>
-      </c>
-      <c r="T8">
-        <v>100</v>
       </c>
       <c r="U8">
         <v>95.8</v>
       </c>
       <c r="V8">
+        <v>100</v>
+      </c>
+      <c r="W8">
+        <v>95.8</v>
+      </c>
+      <c r="X8">
         <v>93.7</v>
       </c>
-    </row>
-    <row r="9" spans="1:22">
+      <c r="Y8">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>100</v>
@@ -4804,11 +5450,11 @@
         <v>100</v>
       </c>
       <c r="K9">
+        <v>100</v>
+      </c>
+      <c r="L9">
         <v>90.90000000000001</v>
       </c>
-      <c r="L9">
-        <v>100</v>
-      </c>
       <c r="M9">
         <v>100</v>
       </c>
@@ -4816,33 +5462,42 @@
         <v>100</v>
       </c>
       <c r="O9">
+        <v>100</v>
+      </c>
+      <c r="P9">
         <v>95</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
+        <v>100</v>
+      </c>
+      <c r="R9">
         <v>96.7</v>
       </c>
-      <c r="Q9">
-        <v>100</v>
-      </c>
-      <c r="R9">
+      <c r="S9">
+        <v>100</v>
+      </c>
+      <c r="T9">
         <v>92.2</v>
       </c>
-      <c r="S9">
-        <v>100</v>
-      </c>
-      <c r="T9">
-        <v>100</v>
-      </c>
       <c r="U9">
         <v>100</v>
       </c>
       <c r="V9">
+        <v>100</v>
+      </c>
+      <c r="W9">
+        <v>100</v>
+      </c>
+      <c r="X9">
         <v>95.2</v>
       </c>
-    </row>
-    <row r="10" spans="1:22">
+      <c r="Y9">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>90</v>
@@ -4866,51 +5521,60 @@
         <v>81.8</v>
       </c>
       <c r="I10">
+        <v>100</v>
+      </c>
+      <c r="J10">
         <v>95</v>
       </c>
-      <c r="J10">
-        <v>100</v>
-      </c>
       <c r="K10">
+        <v>100</v>
+      </c>
+      <c r="L10">
         <v>86.40000000000001</v>
       </c>
-      <c r="L10">
-        <v>100</v>
-      </c>
       <c r="M10">
         <v>100</v>
       </c>
       <c r="N10">
+        <v>100</v>
+      </c>
+      <c r="O10">
         <v>93.8</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>90</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
+        <v>100</v>
+      </c>
+      <c r="R10">
         <v>93.3</v>
       </c>
-      <c r="Q10">
-        <v>100</v>
-      </c>
-      <c r="R10">
+      <c r="S10">
+        <v>100</v>
+      </c>
+      <c r="T10">
         <v>89.09999999999999</v>
       </c>
-      <c r="S10">
-        <v>100</v>
-      </c>
-      <c r="T10">
-        <v>100</v>
-      </c>
       <c r="U10">
+        <v>100</v>
+      </c>
+      <c r="V10">
+        <v>100</v>
+      </c>
+      <c r="W10">
         <v>91.7</v>
       </c>
-      <c r="V10">
+      <c r="X10">
         <v>93.7</v>
       </c>
-    </row>
-    <row r="11" spans="1:22">
+      <c r="Y10">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>80</v>
@@ -4934,51 +5598,60 @@
         <v>72.7</v>
       </c>
       <c r="I11">
+        <v>80</v>
+      </c>
+      <c r="J11">
         <v>85</v>
       </c>
-      <c r="J11">
-        <v>100</v>
-      </c>
       <c r="K11">
+        <v>100</v>
+      </c>
+      <c r="L11">
         <v>84.09999999999999</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>93.8</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>90</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>93.8</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>90</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
+        <v>90</v>
+      </c>
+      <c r="R11">
         <v>86.7</v>
       </c>
-      <c r="Q11">
-        <v>100</v>
-      </c>
-      <c r="R11">
+      <c r="S11">
+        <v>100</v>
+      </c>
+      <c r="T11">
         <v>89.09999999999999</v>
       </c>
-      <c r="S11">
+      <c r="U11">
         <v>95.8</v>
       </c>
-      <c r="T11">
+      <c r="V11">
         <v>93.3</v>
       </c>
-      <c r="U11">
+      <c r="W11">
         <v>91.7</v>
       </c>
-      <c r="V11">
+      <c r="X11">
         <v>88.90000000000001</v>
       </c>
-    </row>
-    <row r="12" spans="1:22">
+      <c r="Y11">
+        <v>53.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>90</v>
@@ -5002,11 +5675,11 @@
         <v>86.40000000000001</v>
       </c>
       <c r="I12">
+        <v>100</v>
+      </c>
+      <c r="J12">
         <v>80</v>
       </c>
-      <c r="J12">
-        <v>100</v>
-      </c>
       <c r="K12">
         <v>100</v>
       </c>
@@ -5017,36 +5690,45 @@
         <v>100</v>
       </c>
       <c r="N12">
+        <v>100</v>
+      </c>
+      <c r="O12">
         <v>96.90000000000001</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>95</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
+        <v>100</v>
+      </c>
+      <c r="R12">
         <v>86.7</v>
       </c>
-      <c r="Q12">
-        <v>100</v>
-      </c>
-      <c r="R12">
+      <c r="S12">
+        <v>100</v>
+      </c>
+      <c r="T12">
         <v>95.3</v>
       </c>
-      <c r="S12">
-        <v>100</v>
-      </c>
-      <c r="T12">
-        <v>100</v>
-      </c>
       <c r="U12">
+        <v>100</v>
+      </c>
+      <c r="V12">
+        <v>100</v>
+      </c>
+      <c r="W12">
         <v>91.7</v>
       </c>
-      <c r="V12">
+      <c r="X12">
         <v>95.2</v>
       </c>
-    </row>
-    <row r="13" spans="1:22">
+      <c r="Y12">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>90</v>
@@ -5070,17 +5752,17 @@
         <v>81.8</v>
       </c>
       <c r="I13">
+        <v>100</v>
+      </c>
+      <c r="J13">
         <v>90</v>
       </c>
-      <c r="J13">
-        <v>100</v>
-      </c>
       <c r="K13">
+        <v>100</v>
+      </c>
+      <c r="L13">
         <v>95.5</v>
       </c>
-      <c r="L13">
-        <v>100</v>
-      </c>
       <c r="M13">
         <v>100</v>
       </c>
@@ -5088,33 +5770,42 @@
         <v>100</v>
       </c>
       <c r="O13">
+        <v>100</v>
+      </c>
+      <c r="P13">
         <v>85</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
+        <v>100</v>
+      </c>
+      <c r="R13">
         <v>90</v>
       </c>
-      <c r="Q13">
-        <v>100</v>
-      </c>
-      <c r="R13">
+      <c r="S13">
+        <v>100</v>
+      </c>
+      <c r="T13">
         <v>93.8</v>
       </c>
-      <c r="S13">
+      <c r="U13">
         <v>93.8</v>
       </c>
-      <c r="T13">
-        <v>100</v>
-      </c>
-      <c r="U13">
-        <v>100</v>
-      </c>
       <c r="V13">
+        <v>100</v>
+      </c>
+      <c r="W13">
+        <v>100</v>
+      </c>
+      <c r="X13">
         <v>90.5</v>
       </c>
-    </row>
-    <row r="14" spans="1:22">
+      <c r="Y13">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>90</v>
@@ -5138,51 +5829,60 @@
         <v>81.8</v>
       </c>
       <c r="I14">
+        <v>100</v>
+      </c>
+      <c r="J14">
         <v>95</v>
       </c>
-      <c r="J14">
-        <v>100</v>
-      </c>
       <c r="K14">
+        <v>100</v>
+      </c>
+      <c r="L14">
         <v>93.2</v>
       </c>
-      <c r="L14">
-        <v>100</v>
-      </c>
       <c r="M14">
         <v>100</v>
       </c>
       <c r="N14">
+        <v>100</v>
+      </c>
+      <c r="O14">
         <v>93.8</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>90</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
+        <v>100</v>
+      </c>
+      <c r="R14">
         <v>96.7</v>
       </c>
-      <c r="Q14">
-        <v>100</v>
-      </c>
-      <c r="R14">
+      <c r="S14">
+        <v>100</v>
+      </c>
+      <c r="T14">
         <v>92.2</v>
       </c>
-      <c r="S14">
-        <v>100</v>
-      </c>
-      <c r="T14">
-        <v>100</v>
-      </c>
       <c r="U14">
+        <v>100</v>
+      </c>
+      <c r="V14">
+        <v>100</v>
+      </c>
+      <c r="W14">
         <v>91.7</v>
       </c>
-      <c r="V14">
+      <c r="X14">
         <v>93.7</v>
       </c>
-    </row>
-    <row r="15" spans="1:22">
+      <c r="Y14">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>80</v>
@@ -5206,51 +5906,60 @@
         <v>81.8</v>
       </c>
       <c r="I15">
+        <v>100</v>
+      </c>
+      <c r="J15">
         <v>85</v>
       </c>
-      <c r="J15">
-        <v>100</v>
-      </c>
       <c r="K15">
+        <v>100</v>
+      </c>
+      <c r="L15">
         <v>88.59999999999999</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>81.3</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>90</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>96.90000000000001</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>95</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
+        <v>100</v>
+      </c>
+      <c r="R15">
         <v>90</v>
       </c>
-      <c r="Q15">
-        <v>100</v>
-      </c>
-      <c r="R15">
+      <c r="S15">
+        <v>100</v>
+      </c>
+      <c r="T15">
         <v>89.09999999999999</v>
       </c>
-      <c r="S15">
+      <c r="U15">
         <v>87.5</v>
       </c>
-      <c r="T15">
+      <c r="V15">
         <v>93.3</v>
       </c>
-      <c r="U15">
+      <c r="W15">
         <v>97.90000000000001</v>
       </c>
-      <c r="V15">
+      <c r="X15">
         <v>95.2</v>
       </c>
-    </row>
-    <row r="16" spans="1:22">
+      <c r="Y15">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>100</v>
@@ -5280,11 +5989,11 @@
         <v>100</v>
       </c>
       <c r="K16">
+        <v>100</v>
+      </c>
+      <c r="L16">
         <v>90.90000000000001</v>
       </c>
-      <c r="L16">
-        <v>100</v>
-      </c>
       <c r="M16">
         <v>100</v>
       </c>
@@ -5295,30 +6004,39 @@
         <v>100</v>
       </c>
       <c r="P16">
+        <v>100</v>
+      </c>
+      <c r="Q16">
+        <v>100</v>
+      </c>
+      <c r="R16">
         <v>96.7</v>
       </c>
-      <c r="Q16">
-        <v>100</v>
-      </c>
-      <c r="R16">
+      <c r="S16">
+        <v>100</v>
+      </c>
+      <c r="T16">
         <v>90.59999999999999</v>
       </c>
-      <c r="S16">
-        <v>100</v>
-      </c>
-      <c r="T16">
-        <v>100</v>
-      </c>
       <c r="U16">
+        <v>100</v>
+      </c>
+      <c r="V16">
+        <v>100</v>
+      </c>
+      <c r="W16">
         <v>97.90000000000001</v>
       </c>
-      <c r="V16">
+      <c r="X16">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="17" spans="1:22">
+      <c r="Y16">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>80</v>
@@ -5345,48 +6063,57 @@
         <v>80</v>
       </c>
       <c r="J17">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="K17">
+        <v>100</v>
+      </c>
+      <c r="L17">
         <v>79.5</v>
       </c>
-      <c r="L17">
-        <v>100</v>
-      </c>
       <c r="M17">
         <v>100</v>
       </c>
       <c r="N17">
+        <v>100</v>
+      </c>
+      <c r="O17">
         <v>84.40000000000001</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>42.5</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
+        <v>90</v>
+      </c>
+      <c r="R17">
         <v>83.3</v>
       </c>
-      <c r="Q17">
-        <v>100</v>
-      </c>
-      <c r="R17">
+      <c r="S17">
+        <v>100</v>
+      </c>
+      <c r="T17">
         <v>79.7</v>
       </c>
-      <c r="S17">
-        <v>100</v>
-      </c>
-      <c r="T17">
-        <v>100</v>
-      </c>
       <c r="U17">
+        <v>100</v>
+      </c>
+      <c r="V17">
+        <v>100</v>
+      </c>
+      <c r="W17">
         <v>85.40000000000001</v>
       </c>
-      <c r="V17">
+      <c r="X17">
         <v>60.3</v>
       </c>
-    </row>
-    <row r="18" spans="1:22">
+      <c r="Y17">
+        <v>53.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>80</v>
@@ -5410,17 +6137,17 @@
         <v>77.3</v>
       </c>
       <c r="I18">
+        <v>100</v>
+      </c>
+      <c r="J18">
         <v>90</v>
       </c>
-      <c r="J18">
-        <v>100</v>
-      </c>
       <c r="K18">
+        <v>100</v>
+      </c>
+      <c r="L18">
         <v>93.2</v>
       </c>
-      <c r="L18">
-        <v>100</v>
-      </c>
       <c r="M18">
         <v>100</v>
       </c>
@@ -5428,33 +6155,42 @@
         <v>100</v>
       </c>
       <c r="O18">
+        <v>100</v>
+      </c>
+      <c r="P18">
         <v>92.5</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
+        <v>100</v>
+      </c>
+      <c r="R18">
         <v>93.3</v>
       </c>
-      <c r="Q18">
-        <v>100</v>
-      </c>
-      <c r="R18">
+      <c r="S18">
+        <v>100</v>
+      </c>
+      <c r="T18">
         <v>93.8</v>
       </c>
-      <c r="S18">
-        <v>100</v>
-      </c>
-      <c r="T18">
-        <v>100</v>
-      </c>
       <c r="U18">
         <v>100</v>
       </c>
       <c r="V18">
+        <v>100</v>
+      </c>
+      <c r="W18">
+        <v>100</v>
+      </c>
+      <c r="X18">
         <v>93.7</v>
       </c>
-    </row>
-    <row r="19" spans="1:22">
+      <c r="Y18">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>80</v>
@@ -5478,17 +6214,17 @@
         <v>68.2</v>
       </c>
       <c r="I19">
+        <v>100</v>
+      </c>
+      <c r="J19">
         <v>90</v>
       </c>
-      <c r="J19">
-        <v>100</v>
-      </c>
       <c r="K19">
+        <v>100</v>
+      </c>
+      <c r="L19">
         <v>95.5</v>
       </c>
-      <c r="L19">
-        <v>100</v>
-      </c>
       <c r="M19">
         <v>100</v>
       </c>
@@ -5496,33 +6232,42 @@
         <v>100</v>
       </c>
       <c r="O19">
+        <v>100</v>
+      </c>
+      <c r="P19">
         <v>77.5</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
+        <v>100</v>
+      </c>
+      <c r="R19">
         <v>93.3</v>
       </c>
-      <c r="Q19">
-        <v>100</v>
-      </c>
-      <c r="R19">
+      <c r="S19">
+        <v>100</v>
+      </c>
+      <c r="T19">
         <v>96.90000000000001</v>
       </c>
-      <c r="S19">
-        <v>100</v>
-      </c>
-      <c r="T19">
-        <v>100</v>
-      </c>
       <c r="U19">
         <v>100</v>
       </c>
       <c r="V19">
+        <v>100</v>
+      </c>
+      <c r="W19">
+        <v>100</v>
+      </c>
+      <c r="X19">
         <v>84.09999999999999</v>
       </c>
-    </row>
-    <row r="20" spans="1:22">
+      <c r="Y19">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>90</v>
@@ -5546,51 +6291,60 @@
         <v>81.8</v>
       </c>
       <c r="I20">
+        <v>100</v>
+      </c>
+      <c r="J20">
         <v>80</v>
       </c>
-      <c r="J20">
-        <v>100</v>
-      </c>
       <c r="K20">
+        <v>100</v>
+      </c>
+      <c r="L20">
         <v>86.40000000000001</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>78.09999999999999</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>95</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>81.3</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>85</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
+        <v>70</v>
+      </c>
+      <c r="R20">
         <v>80</v>
       </c>
-      <c r="Q20">
-        <v>100</v>
-      </c>
-      <c r="R20">
+      <c r="S20">
+        <v>100</v>
+      </c>
+      <c r="T20">
         <v>82.8</v>
       </c>
-      <c r="S20">
+      <c r="U20">
         <v>83.3</v>
       </c>
-      <c r="T20">
+      <c r="V20">
         <v>96.7</v>
       </c>
-      <c r="U20">
+      <c r="W20">
         <v>85.40000000000001</v>
       </c>
-      <c r="V20">
+      <c r="X20">
         <v>82.5</v>
       </c>
-    </row>
-    <row r="21" spans="1:22">
+      <c r="Y20">
+        <v>46.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>90</v>
@@ -5614,51 +6368,60 @@
         <v>68.2</v>
       </c>
       <c r="I21">
+        <v>100</v>
+      </c>
+      <c r="J21">
         <v>95</v>
       </c>
-      <c r="J21">
-        <v>100</v>
-      </c>
       <c r="K21">
+        <v>100</v>
+      </c>
+      <c r="L21">
         <v>93.2</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>93.8</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>90</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>96.90000000000001</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>80</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
+        <v>100</v>
+      </c>
+      <c r="R21">
         <v>96.7</v>
       </c>
-      <c r="Q21">
-        <v>100</v>
-      </c>
-      <c r="R21">
+      <c r="S21">
+        <v>100</v>
+      </c>
+      <c r="T21">
         <v>90.59999999999999</v>
-      </c>
-      <c r="S21">
-        <v>95.8</v>
-      </c>
-      <c r="T21">
-        <v>93.3</v>
       </c>
       <c r="U21">
         <v>95.8</v>
       </c>
       <c r="V21">
+        <v>93.3</v>
+      </c>
+      <c r="W21">
+        <v>95.8</v>
+      </c>
+      <c r="X21">
         <v>85.7</v>
       </c>
-    </row>
-    <row r="22" spans="1:22">
+      <c r="Y21">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>80</v>
@@ -5682,51 +6445,60 @@
         <v>86.40000000000001</v>
       </c>
       <c r="I22">
+        <v>100</v>
+      </c>
+      <c r="J22">
         <v>80</v>
       </c>
-      <c r="J22">
-        <v>100</v>
-      </c>
       <c r="K22">
+        <v>100</v>
+      </c>
+      <c r="L22">
         <v>93.2</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>96.90000000000001</v>
       </c>
-      <c r="M22">
-        <v>100</v>
-      </c>
       <c r="N22">
+        <v>100</v>
+      </c>
+      <c r="O22">
         <v>90.59999999999999</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>97.5</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
+        <v>100</v>
+      </c>
+      <c r="R22">
         <v>83.3</v>
       </c>
-      <c r="Q22">
-        <v>100</v>
-      </c>
-      <c r="R22">
+      <c r="S22">
+        <v>100</v>
+      </c>
+      <c r="T22">
         <v>89.09999999999999</v>
-      </c>
-      <c r="S22">
-        <v>93.8</v>
-      </c>
-      <c r="T22">
-        <v>100</v>
       </c>
       <c r="U22">
         <v>93.8</v>
       </c>
       <c r="V22">
+        <v>100</v>
+      </c>
+      <c r="W22">
+        <v>93.8</v>
+      </c>
+      <c r="X22">
         <v>96.8</v>
       </c>
-    </row>
-    <row r="23" spans="1:22">
+      <c r="Y22">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23">
         <v>80</v>
@@ -5750,51 +6522,60 @@
         <v>81.8</v>
       </c>
       <c r="I23">
+        <v>100</v>
+      </c>
+      <c r="J23">
         <v>90</v>
       </c>
-      <c r="J23">
-        <v>100</v>
-      </c>
       <c r="K23">
+        <v>100</v>
+      </c>
+      <c r="L23">
         <v>93.2</v>
       </c>
-      <c r="L23">
-        <v>100</v>
-      </c>
       <c r="M23">
         <v>100</v>
       </c>
       <c r="N23">
+        <v>100</v>
+      </c>
+      <c r="O23">
         <v>81.3</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>92.5</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
+        <v>100</v>
+      </c>
+      <c r="R23">
         <v>90</v>
       </c>
-      <c r="Q23">
-        <v>100</v>
-      </c>
-      <c r="R23">
+      <c r="S23">
+        <v>100</v>
+      </c>
+      <c r="T23">
         <v>90.59999999999999</v>
       </c>
-      <c r="S23">
-        <v>100</v>
-      </c>
-      <c r="T23">
-        <v>100</v>
-      </c>
       <c r="U23">
+        <v>100</v>
+      </c>
+      <c r="V23">
+        <v>100</v>
+      </c>
+      <c r="W23">
         <v>87.5</v>
       </c>
-      <c r="V23">
+      <c r="X23">
         <v>92.09999999999999</v>
       </c>
-    </row>
-    <row r="24" spans="1:22">
+      <c r="Y23">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24">
         <v>80</v>
@@ -5818,51 +6599,60 @@
         <v>36.4</v>
       </c>
       <c r="I24">
+        <v>20</v>
+      </c>
+      <c r="J24">
         <v>40</v>
       </c>
-      <c r="J24">
-        <v>100</v>
-      </c>
       <c r="K24">
+        <v>100</v>
+      </c>
+      <c r="L24">
         <v>45.5</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>31.3</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>87.5</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>59.4</v>
       </c>
-      <c r="O24">
+      <c r="P24">
         <v>20</v>
       </c>
-      <c r="P24">
+      <c r="Q24">
+        <v>10</v>
+      </c>
+      <c r="R24">
         <v>26.7</v>
       </c>
-      <c r="Q24">
-        <v>100</v>
-      </c>
-      <c r="R24">
+      <c r="S24">
+        <v>100</v>
+      </c>
+      <c r="T24">
         <v>31.3</v>
       </c>
-      <c r="S24">
+      <c r="U24">
         <v>20.8</v>
       </c>
-      <c r="T24">
+      <c r="V24">
         <v>90</v>
       </c>
-      <c r="U24">
+      <c r="W24">
         <v>39.6</v>
       </c>
-      <c r="V24">
+      <c r="X24">
         <v>12.7</v>
       </c>
-    </row>
-    <row r="25" spans="1:22">
+      <c r="Y24">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>80</v>
@@ -5886,51 +6676,60 @@
         <v>81.8</v>
       </c>
       <c r="I25">
+        <v>100</v>
+      </c>
+      <c r="J25">
         <v>90</v>
       </c>
-      <c r="J25">
-        <v>100</v>
-      </c>
       <c r="K25">
+        <v>100</v>
+      </c>
+      <c r="L25">
         <v>88.59999999999999</v>
       </c>
-      <c r="L25">
-        <v>100</v>
-      </c>
       <c r="M25">
+        <v>100</v>
+      </c>
+      <c r="N25">
         <v>95</v>
       </c>
-      <c r="N25">
-        <v>100</v>
-      </c>
       <c r="O25">
+        <v>100</v>
+      </c>
+      <c r="P25">
         <v>95</v>
       </c>
-      <c r="P25">
+      <c r="Q25">
+        <v>100</v>
+      </c>
+      <c r="R25">
         <v>90</v>
       </c>
-      <c r="Q25">
-        <v>100</v>
-      </c>
-      <c r="R25">
+      <c r="S25">
+        <v>100</v>
+      </c>
+      <c r="T25">
         <v>89.09999999999999</v>
       </c>
-      <c r="S25">
+      <c r="U25">
         <v>95.8</v>
       </c>
-      <c r="T25">
+      <c r="V25">
         <v>96.7</v>
       </c>
-      <c r="U25">
+      <c r="W25">
         <v>93.8</v>
       </c>
-      <c r="V25">
+      <c r="X25">
         <v>93.7</v>
       </c>
-    </row>
-    <row r="26" spans="1:22">
+      <c r="Y25">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26">
         <v>80</v>
@@ -5954,51 +6753,60 @@
         <v>86.40000000000001</v>
       </c>
       <c r="I26">
+        <v>100</v>
+      </c>
+      <c r="J26">
         <v>90</v>
       </c>
-      <c r="J26">
-        <v>100</v>
-      </c>
       <c r="K26">
+        <v>100</v>
+      </c>
+      <c r="L26">
         <v>93.2</v>
       </c>
-      <c r="L26">
-        <v>100</v>
-      </c>
       <c r="M26">
         <v>100</v>
       </c>
       <c r="N26">
+        <v>100</v>
+      </c>
+      <c r="O26">
         <v>96.90000000000001</v>
       </c>
-      <c r="O26">
+      <c r="P26">
         <v>97.5</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
+        <v>100</v>
+      </c>
+      <c r="R26">
         <v>90</v>
       </c>
-      <c r="Q26">
-        <v>100</v>
-      </c>
-      <c r="R26">
+      <c r="S26">
+        <v>100</v>
+      </c>
+      <c r="T26">
         <v>95.3</v>
       </c>
-      <c r="S26">
-        <v>100</v>
-      </c>
-      <c r="T26">
-        <v>100</v>
-      </c>
       <c r="U26">
+        <v>100</v>
+      </c>
+      <c r="V26">
+        <v>100</v>
+      </c>
+      <c r="W26">
         <v>97.90000000000001</v>
       </c>
-      <c r="V26">
+      <c r="X26">
         <v>96.8</v>
       </c>
-    </row>
-    <row r="27" spans="1:22">
+      <c r="Y26">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>90</v>
@@ -6022,51 +6830,60 @@
         <v>72.7</v>
       </c>
       <c r="I27">
+        <v>100</v>
+      </c>
+      <c r="J27">
         <v>90</v>
       </c>
-      <c r="J27">
-        <v>100</v>
-      </c>
       <c r="K27">
+        <v>100</v>
+      </c>
+      <c r="L27">
         <v>88.59999999999999</v>
       </c>
-      <c r="L27">
-        <v>100</v>
-      </c>
       <c r="M27">
         <v>100</v>
       </c>
       <c r="N27">
+        <v>100</v>
+      </c>
+      <c r="O27">
         <v>65.59999999999999</v>
       </c>
-      <c r="O27">
+      <c r="P27">
         <v>85</v>
       </c>
-      <c r="P27">
+      <c r="Q27">
+        <v>100</v>
+      </c>
+      <c r="R27">
         <v>80</v>
       </c>
-      <c r="Q27">
-        <v>100</v>
-      </c>
-      <c r="R27">
+      <c r="S27">
+        <v>100</v>
+      </c>
+      <c r="T27">
         <v>67.2</v>
       </c>
-      <c r="S27">
-        <v>100</v>
-      </c>
-      <c r="T27">
+      <c r="U27">
+        <v>100</v>
+      </c>
+      <c r="V27">
         <v>98.3</v>
       </c>
-      <c r="U27">
+      <c r="W27">
         <v>66.7</v>
       </c>
-      <c r="V27">
+      <c r="X27">
         <v>60.3</v>
       </c>
-    </row>
-    <row r="28" spans="1:22">
+      <c r="Y27">
+        <v>46.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>90</v>
@@ -6090,51 +6907,60 @@
         <v>81.8</v>
       </c>
       <c r="I28">
+        <v>100</v>
+      </c>
+      <c r="J28">
         <v>45</v>
       </c>
-      <c r="J28">
-        <v>100</v>
-      </c>
       <c r="K28">
+        <v>100</v>
+      </c>
+      <c r="L28">
         <v>52.3</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>50</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>87.5</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>53.1</v>
       </c>
-      <c r="O28">
+      <c r="P28">
         <v>45</v>
       </c>
-      <c r="P28">
+      <c r="Q28">
+        <v>50</v>
+      </c>
+      <c r="R28">
         <v>30</v>
       </c>
-      <c r="Q28">
-        <v>100</v>
-      </c>
-      <c r="R28">
+      <c r="S28">
+        <v>100</v>
+      </c>
+      <c r="T28">
         <v>35.9</v>
       </c>
-      <c r="S28">
+      <c r="U28">
         <v>33.3</v>
       </c>
-      <c r="T28">
+      <c r="V28">
         <v>90</v>
       </c>
-      <c r="U28">
+      <c r="W28">
         <v>35.4</v>
       </c>
-      <c r="V28">
+      <c r="X28">
         <v>28.6</v>
       </c>
-    </row>
-    <row r="29" spans="1:22">
+      <c r="Y28">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29">
         <v>80</v>
@@ -6158,51 +6984,60 @@
         <v>100</v>
       </c>
       <c r="I29">
+        <v>100</v>
+      </c>
+      <c r="J29">
         <v>90</v>
       </c>
-      <c r="J29">
-        <v>100</v>
-      </c>
       <c r="K29">
+        <v>100</v>
+      </c>
+      <c r="L29">
         <v>86.40000000000001</v>
       </c>
-      <c r="L29">
-        <v>100</v>
-      </c>
       <c r="M29">
+        <v>100</v>
+      </c>
+      <c r="N29">
         <v>95</v>
       </c>
-      <c r="N29">
+      <c r="O29">
         <v>78.09999999999999</v>
       </c>
-      <c r="O29">
-        <v>100</v>
-      </c>
       <c r="P29">
+        <v>100</v>
+      </c>
+      <c r="Q29">
+        <v>100</v>
+      </c>
+      <c r="R29">
         <v>86.7</v>
       </c>
-      <c r="Q29">
-        <v>100</v>
-      </c>
-      <c r="R29">
+      <c r="S29">
+        <v>100</v>
+      </c>
+      <c r="T29">
         <v>79.7</v>
       </c>
-      <c r="S29">
-        <v>100</v>
-      </c>
-      <c r="T29">
+      <c r="U29">
+        <v>100</v>
+      </c>
+      <c r="V29">
         <v>96.7</v>
       </c>
-      <c r="U29">
+      <c r="W29">
         <v>75</v>
       </c>
-      <c r="V29">
+      <c r="X29">
         <v>96.8</v>
       </c>
-    </row>
-    <row r="30" spans="1:22">
+      <c r="Y29">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30">
         <v>90</v>
@@ -6226,51 +7061,60 @@
         <v>81.8</v>
       </c>
       <c r="I30">
+        <v>100</v>
+      </c>
+      <c r="J30">
         <v>95</v>
       </c>
-      <c r="J30">
-        <v>100</v>
-      </c>
       <c r="K30">
+        <v>100</v>
+      </c>
+      <c r="L30">
         <v>86.40000000000001</v>
       </c>
-      <c r="L30">
-        <v>100</v>
-      </c>
       <c r="M30">
         <v>100</v>
       </c>
       <c r="N30">
+        <v>100</v>
+      </c>
+      <c r="O30">
         <v>96.90000000000001</v>
       </c>
-      <c r="O30">
+      <c r="P30">
         <v>95</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
+        <v>100</v>
+      </c>
+      <c r="R30">
         <v>96.7</v>
       </c>
-      <c r="Q30">
-        <v>100</v>
-      </c>
-      <c r="R30">
+      <c r="S30">
+        <v>100</v>
+      </c>
+      <c r="T30">
         <v>89.09999999999999</v>
       </c>
-      <c r="S30">
-        <v>100</v>
-      </c>
-      <c r="T30">
-        <v>100</v>
-      </c>
       <c r="U30">
+        <v>100</v>
+      </c>
+      <c r="V30">
+        <v>100</v>
+      </c>
+      <c r="W30">
         <v>97.90000000000001</v>
       </c>
-      <c r="V30">
+      <c r="X30">
         <v>95.2</v>
       </c>
-    </row>
-    <row r="31" spans="1:22">
+      <c r="Y30">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31">
         <v>80</v>
@@ -6294,51 +7138,60 @@
         <v>81.8</v>
       </c>
       <c r="I31">
+        <v>100</v>
+      </c>
+      <c r="J31">
         <v>80</v>
       </c>
-      <c r="J31">
-        <v>100</v>
-      </c>
       <c r="K31">
+        <v>100</v>
+      </c>
+      <c r="L31">
         <v>88.59999999999999</v>
       </c>
-      <c r="L31">
-        <v>100</v>
-      </c>
       <c r="M31">
         <v>100</v>
       </c>
       <c r="N31">
+        <v>100</v>
+      </c>
+      <c r="O31">
         <v>90.59999999999999</v>
       </c>
-      <c r="O31">
+      <c r="P31">
         <v>82.5</v>
       </c>
-      <c r="P31">
+      <c r="Q31">
+        <v>100</v>
+      </c>
+      <c r="R31">
         <v>86.7</v>
       </c>
-      <c r="Q31">
-        <v>100</v>
-      </c>
-      <c r="R31">
+      <c r="S31">
+        <v>100</v>
+      </c>
+      <c r="T31">
         <v>60.9</v>
       </c>
-      <c r="S31">
+      <c r="U31">
         <v>95.8</v>
       </c>
-      <c r="T31">
+      <c r="V31">
         <v>96.7</v>
       </c>
-      <c r="U31">
+      <c r="W31">
         <v>91.7</v>
       </c>
-      <c r="V31">
+      <c r="X31">
         <v>81</v>
       </c>
-    </row>
-    <row r="32" spans="1:22">
+      <c r="Y31">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32">
         <v>90</v>
@@ -6362,51 +7215,60 @@
         <v>81.8</v>
       </c>
       <c r="I32">
+        <v>80</v>
+      </c>
+      <c r="J32">
         <v>95</v>
       </c>
-      <c r="J32">
-        <v>100</v>
-      </c>
       <c r="K32">
+        <v>100</v>
+      </c>
+      <c r="L32">
         <v>90.90000000000001</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>87.5</v>
       </c>
-      <c r="M32">
-        <v>100</v>
-      </c>
       <c r="N32">
         <v>100</v>
       </c>
       <c r="O32">
+        <v>100</v>
+      </c>
+      <c r="P32">
         <v>95</v>
       </c>
-      <c r="P32">
+      <c r="Q32">
+        <v>90</v>
+      </c>
+      <c r="R32">
         <v>96.7</v>
       </c>
-      <c r="Q32">
-        <v>100</v>
-      </c>
-      <c r="R32">
+      <c r="S32">
+        <v>100</v>
+      </c>
+      <c r="T32">
         <v>93.8</v>
       </c>
-      <c r="S32">
+      <c r="U32">
         <v>91.7</v>
       </c>
-      <c r="T32">
-        <v>100</v>
-      </c>
-      <c r="U32">
+      <c r="V32">
+        <v>100</v>
+      </c>
+      <c r="W32">
         <v>95.8</v>
       </c>
-      <c r="V32">
+      <c r="X32">
         <v>92.09999999999999</v>
       </c>
-    </row>
-    <row r="33" spans="1:22">
+      <c r="Y32">
+        <v>55.1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25">
       <c r="A33" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B33">
         <v>100</v>
@@ -6448,11 +7310,11 @@
         <v>100</v>
       </c>
       <c r="O33">
+        <v>100</v>
+      </c>
+      <c r="P33">
         <v>95</v>
       </c>
-      <c r="P33">
-        <v>100</v>
-      </c>
       <c r="Q33">
         <v>100</v>
       </c>
@@ -6469,12 +7331,21 @@
         <v>100</v>
       </c>
       <c r="V33">
+        <v>100</v>
+      </c>
+      <c r="W33">
+        <v>100</v>
+      </c>
+      <c r="X33">
         <v>96.8</v>
       </c>
-    </row>
-    <row r="34" spans="1:22">
+      <c r="Y33">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25">
       <c r="A34" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B34">
         <v>80</v>
@@ -6498,51 +7369,60 @@
         <v>81.8</v>
       </c>
       <c r="I34">
+        <v>80</v>
+      </c>
+      <c r="J34">
         <v>60</v>
       </c>
-      <c r="J34">
-        <v>100</v>
-      </c>
       <c r="K34">
+        <v>100</v>
+      </c>
+      <c r="L34">
         <v>72.7</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>78.09999999999999</v>
       </c>
-      <c r="M34">
+      <c r="N34">
         <v>85</v>
       </c>
-      <c r="N34">
+      <c r="O34">
         <v>71.90000000000001</v>
       </c>
-      <c r="O34">
+      <c r="P34">
         <v>95</v>
       </c>
-      <c r="P34">
+      <c r="Q34">
+        <v>50</v>
+      </c>
+      <c r="R34">
         <v>73.3</v>
       </c>
-      <c r="Q34">
-        <v>100</v>
-      </c>
-      <c r="R34">
+      <c r="S34">
+        <v>100</v>
+      </c>
+      <c r="T34">
         <v>62.5</v>
       </c>
-      <c r="S34">
+      <c r="U34">
         <v>85.40000000000001</v>
       </c>
-      <c r="T34">
+      <c r="V34">
         <v>88.3</v>
       </c>
-      <c r="U34">
+      <c r="W34">
         <v>52.1</v>
       </c>
-      <c r="V34">
+      <c r="X34">
         <v>84.09999999999999</v>
       </c>
-    </row>
-    <row r="35" spans="1:22">
+      <c r="Y34">
+        <v>32.1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25">
       <c r="A35" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B35">
         <v>90</v>
@@ -6566,51 +7446,60 @@
         <v>90.90000000000001</v>
       </c>
       <c r="I35">
+        <v>100</v>
+      </c>
+      <c r="J35">
         <v>85</v>
       </c>
-      <c r="J35">
-        <v>100</v>
-      </c>
       <c r="K35">
+        <v>100</v>
+      </c>
+      <c r="L35">
         <v>97.7</v>
       </c>
-      <c r="L35">
-        <v>100</v>
-      </c>
       <c r="M35">
         <v>100</v>
       </c>
       <c r="N35">
+        <v>100</v>
+      </c>
+      <c r="O35">
         <v>96.90000000000001</v>
       </c>
-      <c r="O35">
-        <v>100</v>
-      </c>
       <c r="P35">
+        <v>100</v>
+      </c>
+      <c r="Q35">
+        <v>100</v>
+      </c>
+      <c r="R35">
         <v>90</v>
       </c>
-      <c r="Q35">
-        <v>100</v>
-      </c>
-      <c r="R35">
+      <c r="S35">
+        <v>100</v>
+      </c>
+      <c r="T35">
         <v>95.3</v>
       </c>
-      <c r="S35">
-        <v>100</v>
-      </c>
-      <c r="T35">
-        <v>100</v>
-      </c>
       <c r="U35">
+        <v>100</v>
+      </c>
+      <c r="V35">
+        <v>100</v>
+      </c>
+      <c r="W35">
         <v>97.90000000000001</v>
       </c>
-      <c r="V35">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="36" spans="1:22">
+      <c r="X35">
+        <v>100</v>
+      </c>
+      <c r="Y35">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25">
       <c r="A36" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B36">
         <v>90</v>
@@ -6634,51 +7523,60 @@
         <v>81.8</v>
       </c>
       <c r="I36">
+        <v>100</v>
+      </c>
+      <c r="J36">
         <v>55</v>
       </c>
-      <c r="J36">
-        <v>100</v>
-      </c>
       <c r="K36">
+        <v>100</v>
+      </c>
+      <c r="L36">
         <v>88.59999999999999</v>
       </c>
-      <c r="L36">
-        <v>100</v>
-      </c>
       <c r="M36">
         <v>100</v>
       </c>
       <c r="N36">
+        <v>100</v>
+      </c>
+      <c r="O36">
         <v>81.3</v>
       </c>
-      <c r="O36">
+      <c r="P36">
         <v>85</v>
       </c>
-      <c r="P36">
+      <c r="Q36">
+        <v>100</v>
+      </c>
+      <c r="R36">
         <v>63.3</v>
       </c>
-      <c r="Q36">
-        <v>100</v>
-      </c>
-      <c r="R36">
+      <c r="S36">
+        <v>100</v>
+      </c>
+      <c r="T36">
         <v>87.5</v>
       </c>
-      <c r="S36">
-        <v>100</v>
-      </c>
-      <c r="T36">
-        <v>100</v>
-      </c>
       <c r="U36">
+        <v>100</v>
+      </c>
+      <c r="V36">
+        <v>100</v>
+      </c>
+      <c r="W36">
         <v>83.3</v>
       </c>
-      <c r="V36">
+      <c r="X36">
         <v>87.3</v>
       </c>
-    </row>
-    <row r="37" spans="1:22">
+      <c r="Y36">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25">
       <c r="A37" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <v>100</v>
@@ -6702,51 +7600,60 @@
         <v>81.8</v>
       </c>
       <c r="I37">
+        <v>80</v>
+      </c>
+      <c r="J37">
         <v>95</v>
       </c>
-      <c r="J37">
-        <v>100</v>
-      </c>
       <c r="K37">
+        <v>100</v>
+      </c>
+      <c r="L37">
         <v>95.5</v>
       </c>
-      <c r="L37">
+      <c r="M37">
         <v>93.8</v>
       </c>
-      <c r="M37">
-        <v>100</v>
-      </c>
       <c r="N37">
         <v>100</v>
       </c>
       <c r="O37">
+        <v>100</v>
+      </c>
+      <c r="P37">
         <v>95</v>
       </c>
-      <c r="P37">
+      <c r="Q37">
+        <v>90</v>
+      </c>
+      <c r="R37">
         <v>96.7</v>
       </c>
-      <c r="Q37">
-        <v>100</v>
-      </c>
-      <c r="R37">
+      <c r="S37">
+        <v>100</v>
+      </c>
+      <c r="T37">
         <v>95.3</v>
       </c>
-      <c r="S37">
+      <c r="U37">
         <v>95.8</v>
       </c>
-      <c r="T37">
-        <v>100</v>
-      </c>
-      <c r="U37">
+      <c r="V37">
+        <v>100</v>
+      </c>
+      <c r="W37">
         <v>97.90000000000001</v>
       </c>
-      <c r="V37">
+      <c r="X37">
         <v>96.8</v>
       </c>
-    </row>
-    <row r="38" spans="1:22">
+      <c r="Y37">
+        <v>57.7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25">
       <c r="A38" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B38">
         <v>80</v>
@@ -6770,51 +7677,60 @@
         <v>81.8</v>
       </c>
       <c r="I38">
+        <v>100</v>
+      </c>
+      <c r="J38">
         <v>90</v>
       </c>
-      <c r="J38">
-        <v>100</v>
-      </c>
       <c r="K38">
+        <v>100</v>
+      </c>
+      <c r="L38">
         <v>88.59999999999999</v>
       </c>
-      <c r="L38">
-        <v>100</v>
-      </c>
       <c r="M38">
+        <v>100</v>
+      </c>
+      <c r="N38">
         <v>95</v>
       </c>
-      <c r="N38">
+      <c r="O38">
         <v>87.5</v>
       </c>
-      <c r="O38">
+      <c r="P38">
         <v>95</v>
       </c>
-      <c r="P38">
+      <c r="Q38">
+        <v>100</v>
+      </c>
+      <c r="R38">
         <v>90</v>
       </c>
-      <c r="Q38">
-        <v>100</v>
-      </c>
-      <c r="R38">
+      <c r="S38">
+        <v>100</v>
+      </c>
+      <c r="T38">
         <v>89.09999999999999</v>
       </c>
-      <c r="S38">
-        <v>100</v>
-      </c>
-      <c r="T38">
+      <c r="U38">
+        <v>100</v>
+      </c>
+      <c r="V38">
         <v>96.7</v>
       </c>
-      <c r="U38">
+      <c r="W38">
         <v>91.7</v>
       </c>
-      <c r="V38">
+      <c r="X38">
         <v>96.8</v>
       </c>
-    </row>
-    <row r="39" spans="1:22">
+      <c r="Y38">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25">
       <c r="A39" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B39">
         <v>90</v>
@@ -6838,51 +7754,60 @@
         <v>81.8</v>
       </c>
       <c r="I39">
+        <v>100</v>
+      </c>
+      <c r="J39">
         <v>95</v>
       </c>
-      <c r="J39">
-        <v>100</v>
-      </c>
       <c r="K39">
+        <v>100</v>
+      </c>
+      <c r="L39">
         <v>84.09999999999999</v>
       </c>
-      <c r="L39">
-        <v>100</v>
-      </c>
       <c r="M39">
         <v>100</v>
       </c>
       <c r="N39">
+        <v>100</v>
+      </c>
+      <c r="O39">
         <v>87.5</v>
       </c>
-      <c r="O39">
+      <c r="P39">
         <v>92.5</v>
       </c>
-      <c r="P39">
+      <c r="Q39">
+        <v>100</v>
+      </c>
+      <c r="R39">
         <v>90</v>
       </c>
-      <c r="Q39">
-        <v>100</v>
-      </c>
-      <c r="R39">
+      <c r="S39">
+        <v>100</v>
+      </c>
+      <c r="T39">
         <v>84.40000000000001</v>
       </c>
-      <c r="S39">
-        <v>100</v>
-      </c>
-      <c r="T39">
-        <v>100</v>
-      </c>
       <c r="U39">
+        <v>100</v>
+      </c>
+      <c r="V39">
+        <v>100</v>
+      </c>
+      <c r="W39">
         <v>91.7</v>
       </c>
-      <c r="V39">
+      <c r="X39">
         <v>95.2</v>
       </c>
-    </row>
-    <row r="40" spans="1:22">
+      <c r="Y39">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25">
       <c r="A40" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B40">
         <v>80</v>
@@ -6906,51 +7831,60 @@
         <v>90.90000000000001</v>
       </c>
       <c r="I40">
+        <v>100</v>
+      </c>
+      <c r="J40">
         <v>90</v>
       </c>
-      <c r="J40">
-        <v>100</v>
-      </c>
       <c r="K40">
+        <v>100</v>
+      </c>
+      <c r="L40">
         <v>97.7</v>
       </c>
-      <c r="L40">
-        <v>100</v>
-      </c>
       <c r="M40">
         <v>100</v>
       </c>
       <c r="N40">
+        <v>100</v>
+      </c>
+      <c r="O40">
         <v>96.90000000000001</v>
       </c>
-      <c r="O40">
-        <v>100</v>
-      </c>
       <c r="P40">
+        <v>100</v>
+      </c>
+      <c r="Q40">
+        <v>100</v>
+      </c>
+      <c r="R40">
         <v>86.7</v>
       </c>
-      <c r="Q40">
-        <v>100</v>
-      </c>
-      <c r="R40">
+      <c r="S40">
+        <v>100</v>
+      </c>
+      <c r="T40">
         <v>90.59999999999999</v>
       </c>
-      <c r="S40">
-        <v>100</v>
-      </c>
-      <c r="T40">
-        <v>100</v>
-      </c>
       <c r="U40">
+        <v>100</v>
+      </c>
+      <c r="V40">
+        <v>100</v>
+      </c>
+      <c r="W40">
         <v>95.8</v>
       </c>
-      <c r="V40">
+      <c r="X40">
         <v>96.8</v>
       </c>
-    </row>
-    <row r="41" spans="1:22">
+      <c r="Y40">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25">
       <c r="A41" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B41">
         <v>80</v>
@@ -6974,51 +7908,60 @@
         <v>77.3</v>
       </c>
       <c r="I41">
+        <v>80</v>
+      </c>
+      <c r="J41">
         <v>75</v>
       </c>
-      <c r="J41">
-        <v>100</v>
-      </c>
       <c r="K41">
+        <v>100</v>
+      </c>
+      <c r="L41">
         <v>79.5</v>
       </c>
-      <c r="L41">
+      <c r="M41">
         <v>84.40000000000001</v>
       </c>
-      <c r="M41">
+      <c r="N41">
         <v>95</v>
       </c>
-      <c r="N41">
+      <c r="O41">
         <v>87.5</v>
       </c>
-      <c r="O41">
+      <c r="P41">
         <v>77.5</v>
       </c>
-      <c r="P41">
+      <c r="Q41">
+        <v>90</v>
+      </c>
+      <c r="R41">
         <v>76.7</v>
       </c>
-      <c r="Q41">
-        <v>100</v>
-      </c>
-      <c r="R41">
+      <c r="S41">
+        <v>100</v>
+      </c>
+      <c r="T41">
         <v>78.09999999999999</v>
       </c>
-      <c r="S41">
+      <c r="U41">
         <v>83.3</v>
       </c>
-      <c r="T41">
+      <c r="V41">
         <v>96.7</v>
       </c>
-      <c r="U41">
+      <c r="W41">
         <v>85.40000000000001</v>
       </c>
-      <c r="V41">
+      <c r="X41">
         <v>84.09999999999999</v>
       </c>
-    </row>
-    <row r="42" spans="1:22">
+      <c r="Y41">
+        <v>57.7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25">
       <c r="A42" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B42">
         <v>80</v>
@@ -7042,11 +7985,11 @@
         <v>72.7</v>
       </c>
       <c r="I42">
+        <v>80</v>
+      </c>
+      <c r="J42">
         <v>90</v>
       </c>
-      <c r="J42">
-        <v>100</v>
-      </c>
       <c r="K42">
         <v>100</v>
       </c>
@@ -7057,38 +8000,47 @@
         <v>100</v>
       </c>
       <c r="N42">
+        <v>100</v>
+      </c>
+      <c r="O42">
         <v>90.59999999999999</v>
       </c>
-      <c r="O42">
+      <c r="P42">
         <v>87.5</v>
       </c>
-      <c r="P42">
+      <c r="Q42">
+        <v>90</v>
+      </c>
+      <c r="R42">
         <v>86.7</v>
       </c>
-      <c r="Q42">
-        <v>100</v>
-      </c>
-      <c r="R42">
+      <c r="S42">
+        <v>100</v>
+      </c>
+      <c r="T42">
         <v>98.40000000000001</v>
       </c>
-      <c r="S42">
-        <v>100</v>
-      </c>
-      <c r="T42">
-        <v>100</v>
-      </c>
       <c r="U42">
+        <v>100</v>
+      </c>
+      <c r="V42">
+        <v>100</v>
+      </c>
+      <c r="W42">
         <v>91.7</v>
       </c>
-      <c r="V42">
+      <c r="X42">
         <v>88.90000000000001</v>
+      </c>
+      <c r="Y42">
+        <v>57.7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="P1:V1"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="R1:Y1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7109,36 +8061,36 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
@@ -7147,19 +8099,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F2" s="2">
-        <v>53.8</v>
+        <v>5.1</v>
       </c>
       <c r="G2" s="2">
-        <v>46.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H2">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7170,28 +8122,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C3">
         <v>39</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F3" s="2">
-        <v>61.5</v>
+        <v>53.8</v>
       </c>
       <c r="G3" s="2">
-        <v>38.5</v>
+        <v>46.2</v>
       </c>
       <c r="H3">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7202,28 +8154,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C4">
         <v>39</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F4" s="2">
-        <v>82.09999999999999</v>
+        <v>61.5</v>
       </c>
       <c r="G4" s="2">
-        <v>17.9</v>
+        <v>38.5</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7234,28 +8186,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C5">
         <v>39</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2">
-        <v>84.59999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>15.4</v>
+        <v>17.9</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7266,10 +8218,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C6">
         <v>39</v>
@@ -7287,7 +8239,7 @@
         <v>15.4</v>
       </c>
       <c r="H6">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7298,25 +8250,25 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C7">
         <v>39</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" s="2">
-        <v>87.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G7" s="2">
-        <v>12.8</v>
+        <v>15.4</v>
       </c>
       <c r="H7">
         <v>6.9</v>
@@ -7330,28 +8282,28 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C8">
         <v>39</v>
       </c>
       <c r="D8">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F8" s="2">
-        <v>94.90000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="G8" s="2">
-        <v>5.1</v>
+        <v>12.8</v>
       </c>
       <c r="H8">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7362,21 +8314,33 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C9">
+        <v>39</v>
+      </c>
+      <c r="D9">
+        <v>37</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9" s="2">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="G9" s="2">
+        <v>5.1</v>
+      </c>
+      <c r="H9">
+        <v>7.2</v>
+      </c>
+      <c r="I9">
         <v>0</v>
       </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="I9">
+      <c r="J9" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7411,7 +8375,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -7421,7 +8385,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7445,7 +8409,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -7453,22 +8417,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920214</v>
+        <v>23330051920226</v>
       </c>
       <c r="B2" t="s">
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7476,19 +8440,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920214</v>
+        <v>23330051920226</v>
       </c>
       <c r="B3" t="s">
         <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
         <v>65</v>
@@ -7499,16 +8463,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920254</v>
+        <v>23330051920215</v>
       </c>
       <c r="B4" t="s">
         <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -7522,19 +8486,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920254</v>
+        <v>23330051920215</v>
       </c>
       <c r="B5" t="s">
         <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
         <v>65</v>
@@ -7545,22 +8509,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920239</v>
+        <v>23330051920242</v>
       </c>
       <c r="B6" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7568,19 +8532,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920239</v>
+        <v>23330051920242</v>
       </c>
       <c r="B7" t="s">
         <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
         <v>65</v>
@@ -7591,22 +8555,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920226</v>
+        <v>23330051920248</v>
       </c>
       <c r="B8" t="s">
         <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7614,22 +8578,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920215</v>
+        <v>23330051920248</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7637,22 +8601,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920216</v>
+        <v>23330051920328</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7660,19 +8624,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920242</v>
+        <v>23330051920328</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
         <v>65</v>
@@ -7683,22 +8647,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920248</v>
+        <v>23330051920357</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7706,22 +8670,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920328</v>
+        <v>23330051920357</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7729,16 +8693,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920357</v>
+        <v>23330051920280</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="E14" t="s">
         <v>11</v>
@@ -7755,21 +8719,458 @@
         <v>23330051920280</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D15" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F15" t="s">
         <v>65</v>
       </c>
       <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>23330051920213</v>
+      </c>
+      <c r="B16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" t="s">
+        <v>123</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
+        <v>65</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>23330051920227</v>
+      </c>
+      <c r="B17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" t="s">
+        <v>124</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" t="s">
+        <v>65</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>23330051920237</v>
+      </c>
+      <c r="B18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18" t="s">
+        <v>125</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" t="s">
+        <v>65</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>23330051920216</v>
+      </c>
+      <c r="B19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" t="s">
+        <v>86</v>
+      </c>
+      <c r="D19" t="s">
+        <v>126</v>
+      </c>
+      <c r="E19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" t="s">
+        <v>65</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>23330051920240</v>
+      </c>
+      <c r="B20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" t="s">
+        <v>127</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" t="s">
+        <v>65</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>23330051920244</v>
+      </c>
+      <c r="B21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" t="s">
+        <v>128</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" t="s">
+        <v>65</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>23330051920250</v>
+      </c>
+      <c r="B22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" t="s">
+        <v>129</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" t="s">
+        <v>65</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>23330051920333</v>
+      </c>
+      <c r="B23" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" t="s">
+        <v>130</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" t="s">
+        <v>65</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>23330051920252</v>
+      </c>
+      <c r="B24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" t="s">
+        <v>131</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" t="s">
+        <v>65</v>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>23330051920256</v>
+      </c>
+      <c r="B25" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" t="s">
+        <v>132</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" t="s">
+        <v>65</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>23330051920257</v>
+      </c>
+      <c r="B26" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26" t="s">
+        <v>133</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" t="s">
+        <v>65</v>
+      </c>
+      <c r="G26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>23330051920260</v>
+      </c>
+      <c r="B27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" t="s">
+        <v>112</v>
+      </c>
+      <c r="D27" t="s">
+        <v>134</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" t="s">
+        <v>65</v>
+      </c>
+      <c r="G27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>23330051920330</v>
+      </c>
+      <c r="B28" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" t="s">
+        <v>90</v>
+      </c>
+      <c r="D28" t="s">
+        <v>135</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" t="s">
+        <v>65</v>
+      </c>
+      <c r="G28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>23330051920272</v>
+      </c>
+      <c r="B29" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" t="s">
+        <v>113</v>
+      </c>
+      <c r="D29" t="s">
+        <v>136</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" t="s">
+        <v>65</v>
+      </c>
+      <c r="G29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>23330051920270</v>
+      </c>
+      <c r="B30" t="s">
+        <v>95</v>
+      </c>
+      <c r="C30" t="s">
+        <v>89</v>
+      </c>
+      <c r="D30" t="s">
+        <v>137</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" t="s">
+        <v>65</v>
+      </c>
+      <c r="G30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>23330051920207</v>
+      </c>
+      <c r="B31" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" t="s">
+        <v>88</v>
+      </c>
+      <c r="D31" t="s">
+        <v>138</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" t="s">
+        <v>65</v>
+      </c>
+      <c r="G31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>23330051920276</v>
+      </c>
+      <c r="B32" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32" t="s">
+        <v>139</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" t="s">
+        <v>65</v>
+      </c>
+      <c r="G32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>23330051920275</v>
+      </c>
+      <c r="B33" t="s">
+        <v>98</v>
+      </c>
+      <c r="C33" t="s">
+        <v>114</v>
+      </c>
+      <c r="D33" t="s">
+        <v>140</v>
+      </c>
+      <c r="E33" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" t="s">
+        <v>65</v>
+      </c>
+      <c r="G33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>23330051920277</v>
+      </c>
+      <c r="B34" t="s">
+        <v>99</v>
+      </c>
+      <c r="C34" t="s">
+        <v>115</v>
+      </c>
+      <c r="D34" t="s">
+        <v>141</v>
+      </c>
+      <c r="E34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" t="s">
+        <v>65</v>
+      </c>
+      <c r="G34">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1BV - Estadisticos 20231.xlsx
+++ b/grupos/1BV - Estadisticos 20231.xlsx
@@ -1037,25 +1037,25 @@
         <v>10</v>
       </c>
       <c r="Z4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG4">
         <v>5</v>
@@ -1138,19 +1138,19 @@
         <v>5</v>
       </c>
       <c r="Z5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE5">
         <v>5</v>
@@ -1239,25 +1239,25 @@
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB6">
         <v>5</v>
       </c>
       <c r="AC6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG6">
         <v>5</v>
@@ -1340,22 +1340,22 @@
         <v>5</v>
       </c>
       <c r="Z7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF7">
         <v>5</v>
@@ -1441,22 +1441,22 @@
         <v>5</v>
       </c>
       <c r="Z8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF8">
         <v>5</v>
@@ -1542,25 +1542,25 @@
         <v>10</v>
       </c>
       <c r="Z9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG9">
         <v>5</v>
@@ -1643,25 +1643,25 @@
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG10">
         <v>5</v>
@@ -1744,22 +1744,22 @@
         <v>5</v>
       </c>
       <c r="Z11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB11">
         <v>5</v>
       </c>
       <c r="AC11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF11">
         <v>5</v>
@@ -1845,22 +1845,22 @@
         <v>10</v>
       </c>
       <c r="Z12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF12">
         <v>5</v>
@@ -1946,25 +1946,25 @@
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG13">
         <v>5</v>
@@ -2047,25 +2047,25 @@
         <v>10</v>
       </c>
       <c r="Z14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG14">
         <v>5</v>
@@ -2148,25 +2148,25 @@
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB15">
         <v>5</v>
       </c>
       <c r="AC15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG15">
         <v>5</v>
@@ -2249,25 +2249,25 @@
         <v>10</v>
       </c>
       <c r="Z16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG16">
         <v>5</v>
@@ -2350,10 +2350,10 @@
         <v>10</v>
       </c>
       <c r="Z17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB17">
         <v>5</v>
@@ -2362,10 +2362,10 @@
         <v>5</v>
       </c>
       <c r="AD17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF17">
         <v>5</v>
@@ -2451,25 +2451,25 @@
         <v>10</v>
       </c>
       <c r="Z18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG18">
         <v>5</v>
@@ -2552,25 +2552,25 @@
         <v>10</v>
       </c>
       <c r="Z19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG19">
         <v>5</v>
@@ -2653,22 +2653,22 @@
         <v>5</v>
       </c>
       <c r="Z20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB20">
         <v>5</v>
       </c>
       <c r="AC20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF20">
         <v>5</v>
@@ -2754,25 +2754,25 @@
         <v>10</v>
       </c>
       <c r="Z21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB21">
         <v>5</v>
       </c>
       <c r="AC21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG21">
         <v>5</v>
@@ -2855,25 +2855,25 @@
         <v>10</v>
       </c>
       <c r="Z22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG22">
         <v>5</v>
@@ -2956,22 +2956,22 @@
         <v>10</v>
       </c>
       <c r="Z23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF23">
         <v>5</v>
@@ -3158,25 +3158,25 @@
         <v>10</v>
       </c>
       <c r="Z25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG25">
         <v>5</v>
@@ -3259,25 +3259,25 @@
         <v>10</v>
       </c>
       <c r="Z26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG26">
         <v>5</v>
@@ -3360,16 +3360,16 @@
         <v>5</v>
       </c>
       <c r="Z27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB27">
         <v>5</v>
       </c>
       <c r="AC27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD27">
         <v>5</v>
@@ -3464,7 +3464,7 @@
         <v>5</v>
       </c>
       <c r="AA28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB28">
         <v>5</v>
@@ -3565,13 +3565,13 @@
         <v>5</v>
       </c>
       <c r="AA29">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB29">
         <v>5</v>
       </c>
       <c r="AC29">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD29">
         <v>5</v>
@@ -3663,25 +3663,25 @@
         <v>10</v>
       </c>
       <c r="Z30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG30">
         <v>5</v>
@@ -3764,10 +3764,10 @@
         <v>10</v>
       </c>
       <c r="Z31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB31">
         <v>5</v>
@@ -3779,7 +3779,7 @@
         <v>5</v>
       </c>
       <c r="AE31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF31">
         <v>5</v>
@@ -3865,25 +3865,25 @@
         <v>10</v>
       </c>
       <c r="Z32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG32">
         <v>5</v>
@@ -3972,10 +3972,10 @@
         <v>10</v>
       </c>
       <c r="AB33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD33">
         <v>10</v>
@@ -3984,7 +3984,7 @@
         <v>10</v>
       </c>
       <c r="AF33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG33">
         <v>5</v>
@@ -4070,13 +4070,13 @@
         <v>5</v>
       </c>
       <c r="AA34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB34">
         <v>5</v>
       </c>
       <c r="AC34">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD34">
         <v>5</v>
@@ -4168,25 +4168,25 @@
         <v>10</v>
       </c>
       <c r="Z35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC35">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE35">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG35">
         <v>5</v>
@@ -4272,19 +4272,19 @@
         <v>5</v>
       </c>
       <c r="AA36">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB36">
         <v>5</v>
       </c>
       <c r="AC36">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF36">
         <v>5</v>
@@ -4370,25 +4370,25 @@
         <v>10</v>
       </c>
       <c r="Z37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA37">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB37">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC37">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD37">
         <v>10</v>
       </c>
       <c r="AE37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF37">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG37">
         <v>5</v>
@@ -4471,25 +4471,25 @@
         <v>10</v>
       </c>
       <c r="Z38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA38">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB38">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC38">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE38">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG38">
         <v>5</v>
@@ -4572,25 +4572,25 @@
         <v>10</v>
       </c>
       <c r="Z39">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE39">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG39">
         <v>5</v>
@@ -4673,10 +4673,10 @@
         <v>10</v>
       </c>
       <c r="Z40">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA40">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB40">
         <v>5</v>
@@ -4685,10 +4685,10 @@
         <v>5</v>
       </c>
       <c r="AD40">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE40">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF40">
         <v>5</v>
@@ -4783,10 +4783,10 @@
         <v>5</v>
       </c>
       <c r="AC41">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD41">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE41">
         <v>5</v>
@@ -4875,22 +4875,22 @@
         <v>5</v>
       </c>
       <c r="Z42">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA42">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB42">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC42">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD42">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE42">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF42">
         <v>5</v>
@@ -8143,7 +8143,7 @@
         <v>46.2</v>
       </c>
       <c r="H3">
-        <v>5.6</v>
+        <v>7.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -8175,7 +8175,7 @@
         <v>38.5</v>
       </c>
       <c r="H4">
-        <v>5.8</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -8207,7 +8207,7 @@
         <v>17.9</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>9.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -8239,7 +8239,7 @@
         <v>15.4</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -8271,7 +8271,7 @@
         <v>15.4</v>
       </c>
       <c r="H7">
-        <v>6.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -8303,7 +8303,7 @@
         <v>12.8</v>
       </c>
       <c r="H8">
-        <v>6.9</v>
+        <v>9.4</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -8335,7 +8335,7 @@
         <v>5.1</v>
       </c>
       <c r="H9">
-        <v>7.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I9">
         <v>0</v>

--- a/grupos/1BV - Estadisticos 20231.xlsx
+++ b/grupos/1BV - Estadisticos 20231.xlsx
@@ -1037,25 +1037,25 @@
         <v>10</v>
       </c>
       <c r="Z4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG4">
         <v>5</v>
@@ -1138,19 +1138,19 @@
         <v>5</v>
       </c>
       <c r="Z5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE5">
         <v>5</v>
@@ -1239,25 +1239,25 @@
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB6">
         <v>5</v>
       </c>
       <c r="AC6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG6">
         <v>5</v>
@@ -1340,22 +1340,22 @@
         <v>5</v>
       </c>
       <c r="Z7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF7">
         <v>5</v>
@@ -1441,22 +1441,22 @@
         <v>5</v>
       </c>
       <c r="Z8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF8">
         <v>5</v>
@@ -1542,25 +1542,25 @@
         <v>10</v>
       </c>
       <c r="Z9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG9">
         <v>5</v>
@@ -1643,25 +1643,25 @@
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG10">
         <v>5</v>
@@ -1744,22 +1744,22 @@
         <v>5</v>
       </c>
       <c r="Z11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB11">
         <v>5</v>
       </c>
       <c r="AC11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF11">
         <v>5</v>
@@ -1845,22 +1845,22 @@
         <v>10</v>
       </c>
       <c r="Z12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF12">
         <v>5</v>
@@ -1946,25 +1946,25 @@
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG13">
         <v>5</v>
@@ -2047,25 +2047,25 @@
         <v>10</v>
       </c>
       <c r="Z14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG14">
         <v>5</v>
@@ -2148,25 +2148,25 @@
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB15">
         <v>5</v>
       </c>
       <c r="AC15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG15">
         <v>5</v>
@@ -2249,25 +2249,25 @@
         <v>10</v>
       </c>
       <c r="Z16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG16">
         <v>5</v>
@@ -2350,10 +2350,10 @@
         <v>10</v>
       </c>
       <c r="Z17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB17">
         <v>5</v>
@@ -2362,10 +2362,10 @@
         <v>5</v>
       </c>
       <c r="AD17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF17">
         <v>5</v>
@@ -2451,25 +2451,25 @@
         <v>10</v>
       </c>
       <c r="Z18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG18">
         <v>5</v>
@@ -2552,25 +2552,25 @@
         <v>10</v>
       </c>
       <c r="Z19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG19">
         <v>5</v>
@@ -2653,22 +2653,22 @@
         <v>5</v>
       </c>
       <c r="Z20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB20">
         <v>5</v>
       </c>
       <c r="AC20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF20">
         <v>5</v>
@@ -2754,25 +2754,25 @@
         <v>10</v>
       </c>
       <c r="Z21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB21">
         <v>5</v>
       </c>
       <c r="AC21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG21">
         <v>5</v>
@@ -2855,25 +2855,25 @@
         <v>10</v>
       </c>
       <c r="Z22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG22">
         <v>5</v>
@@ -2956,22 +2956,22 @@
         <v>10</v>
       </c>
       <c r="Z23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF23">
         <v>5</v>
@@ -3158,25 +3158,25 @@
         <v>10</v>
       </c>
       <c r="Z25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG25">
         <v>5</v>
@@ -3259,25 +3259,25 @@
         <v>10</v>
       </c>
       <c r="Z26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG26">
         <v>5</v>
@@ -3360,16 +3360,16 @@
         <v>5</v>
       </c>
       <c r="Z27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB27">
         <v>5</v>
       </c>
       <c r="AC27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD27">
         <v>5</v>
@@ -3464,7 +3464,7 @@
         <v>5</v>
       </c>
       <c r="AA28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB28">
         <v>5</v>
@@ -3565,13 +3565,13 @@
         <v>5</v>
       </c>
       <c r="AA29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB29">
         <v>5</v>
       </c>
       <c r="AC29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD29">
         <v>5</v>
@@ -3663,25 +3663,25 @@
         <v>10</v>
       </c>
       <c r="Z30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG30">
         <v>5</v>
@@ -3764,10 +3764,10 @@
         <v>10</v>
       </c>
       <c r="Z31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA31">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB31">
         <v>5</v>
@@ -3779,7 +3779,7 @@
         <v>5</v>
       </c>
       <c r="AE31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF31">
         <v>5</v>
@@ -3865,25 +3865,25 @@
         <v>10</v>
       </c>
       <c r="Z32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG32">
         <v>5</v>
@@ -3972,10 +3972,10 @@
         <v>10</v>
       </c>
       <c r="AB33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD33">
         <v>10</v>
@@ -3984,7 +3984,7 @@
         <v>10</v>
       </c>
       <c r="AF33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG33">
         <v>5</v>
@@ -4070,13 +4070,13 @@
         <v>5</v>
       </c>
       <c r="AA34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB34">
         <v>5</v>
       </c>
       <c r="AC34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD34">
         <v>5</v>
@@ -4168,25 +4168,25 @@
         <v>10</v>
       </c>
       <c r="Z35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG35">
         <v>5</v>
@@ -4272,19 +4272,19 @@
         <v>5</v>
       </c>
       <c r="AA36">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB36">
         <v>5</v>
       </c>
       <c r="AC36">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD36">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE36">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF36">
         <v>5</v>
@@ -4370,25 +4370,25 @@
         <v>10</v>
       </c>
       <c r="Z37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC37">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD37">
         <v>10</v>
       </c>
       <c r="AE37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG37">
         <v>5</v>
@@ -4471,25 +4471,25 @@
         <v>10</v>
       </c>
       <c r="Z38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA38">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB38">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC38">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE38">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG38">
         <v>5</v>
@@ -4572,25 +4572,25 @@
         <v>10</v>
       </c>
       <c r="Z39">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE39">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG39">
         <v>5</v>
@@ -4673,10 +4673,10 @@
         <v>10</v>
       </c>
       <c r="Z40">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA40">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB40">
         <v>5</v>
@@ -4685,10 +4685,10 @@
         <v>5</v>
       </c>
       <c r="AD40">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE40">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF40">
         <v>5</v>
@@ -4783,10 +4783,10 @@
         <v>5</v>
       </c>
       <c r="AC41">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD41">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE41">
         <v>5</v>
@@ -4875,22 +4875,22 @@
         <v>5</v>
       </c>
       <c r="Z42">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA42">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB42">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC42">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD42">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE42">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF42">
         <v>5</v>
@@ -5107,7 +5107,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Y4">
-        <v>61.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -5184,7 +5184,7 @@
         <v>81</v>
       </c>
       <c r="Y5">
-        <v>42.3</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -5261,7 +5261,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="Y6">
-        <v>61.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -5415,7 +5415,7 @@
         <v>93.7</v>
       </c>
       <c r="Y8">
-        <v>61.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -5492,7 +5492,7 @@
         <v>95.2</v>
       </c>
       <c r="Y9">
-        <v>61.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -5569,7 +5569,7 @@
         <v>93.7</v>
       </c>
       <c r="Y10">
-        <v>61.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -5646,7 +5646,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Y11">
-        <v>53.8</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -5723,7 +5723,7 @@
         <v>95.2</v>
       </c>
       <c r="Y12">
-        <v>61.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -5800,7 +5800,7 @@
         <v>90.5</v>
       </c>
       <c r="Y13">
-        <v>61.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -5877,7 +5877,7 @@
         <v>93.7</v>
       </c>
       <c r="Y14">
-        <v>61.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -5954,7 +5954,7 @@
         <v>95.2</v>
       </c>
       <c r="Y15">
-        <v>61.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -6031,7 +6031,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="Y16">
-        <v>61.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -6108,7 +6108,7 @@
         <v>60.3</v>
       </c>
       <c r="Y17">
-        <v>53.8</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -6185,7 +6185,7 @@
         <v>93.7</v>
       </c>
       <c r="Y18">
-        <v>61.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -6262,7 +6262,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="Y19">
-        <v>61.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -6339,7 +6339,7 @@
         <v>82.5</v>
       </c>
       <c r="Y20">
-        <v>46.2</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -6416,7 +6416,7 @@
         <v>85.7</v>
       </c>
       <c r="Y21">
-        <v>61.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -6493,7 +6493,7 @@
         <v>96.8</v>
       </c>
       <c r="Y22">
-        <v>61.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -6570,7 +6570,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="Y23">
-        <v>61.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -6647,7 +6647,7 @@
         <v>12.7</v>
       </c>
       <c r="Y24">
-        <v>3.8</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -6724,7 +6724,7 @@
         <v>93.7</v>
       </c>
       <c r="Y25">
-        <v>61.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -6801,7 +6801,7 @@
         <v>96.8</v>
       </c>
       <c r="Y26">
-        <v>61.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -6878,7 +6878,7 @@
         <v>60.3</v>
       </c>
       <c r="Y27">
-        <v>46.2</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -6955,7 +6955,7 @@
         <v>28.6</v>
       </c>
       <c r="Y28">
-        <v>19.2</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -7032,7 +7032,7 @@
         <v>96.8</v>
       </c>
       <c r="Y29">
-        <v>61.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -7109,7 +7109,7 @@
         <v>95.2</v>
       </c>
       <c r="Y30">
-        <v>61.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -7186,7 +7186,7 @@
         <v>81</v>
       </c>
       <c r="Y31">
-        <v>59</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -7263,7 +7263,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="Y32">
-        <v>55.1</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -7340,7 +7340,7 @@
         <v>96.8</v>
       </c>
       <c r="Y33">
-        <v>61.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -7417,7 +7417,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="Y34">
-        <v>32.1</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -7494,7 +7494,7 @@
         <v>100</v>
       </c>
       <c r="Y35">
-        <v>61.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -7571,7 +7571,7 @@
         <v>87.3</v>
       </c>
       <c r="Y36">
-        <v>61.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -7648,7 +7648,7 @@
         <v>96.8</v>
       </c>
       <c r="Y37">
-        <v>57.7</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -7725,7 +7725,7 @@
         <v>96.8</v>
       </c>
       <c r="Y38">
-        <v>61.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -7802,7 +7802,7 @@
         <v>95.2</v>
       </c>
       <c r="Y39">
-        <v>61.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -7879,7 +7879,7 @@
         <v>96.8</v>
       </c>
       <c r="Y40">
-        <v>61.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -7956,7 +7956,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="Y41">
-        <v>57.7</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -8033,7 +8033,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Y42">
-        <v>57.7</v>
+        <v>93.8</v>
       </c>
     </row>
   </sheetData>
@@ -8143,7 +8143,7 @@
         <v>46.2</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>5.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -8175,7 +8175,7 @@
         <v>38.5</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>5.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -8207,7 +8207,7 @@
         <v>17.9</v>
       </c>
       <c r="H5">
-        <v>9.1</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -8239,7 +8239,7 @@
         <v>15.4</v>
       </c>
       <c r="H6">
-        <v>9.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -8271,7 +8271,7 @@
         <v>15.4</v>
       </c>
       <c r="H7">
-        <v>9.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -8303,7 +8303,7 @@
         <v>12.8</v>
       </c>
       <c r="H8">
-        <v>9.4</v>
+        <v>6.9</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -8335,7 +8335,7 @@
         <v>5.1</v>
       </c>
       <c r="H9">
-        <v>9.699999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="I9">
         <v>0</v>
